--- a/artfynd/A 57334-2022 artfynd.xlsx
+++ b/artfynd/A 57334-2022 artfynd.xlsx
@@ -675,53 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126891183</v>
+        <v>126889625</v>
       </c>
       <c r="B2" t="n">
-        <v>98278</v>
+        <v>80114</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>685180</v>
+        <v>685134</v>
       </c>
       <c r="R2" t="n">
-        <v>7106957</v>
+        <v>7106898</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,19 +754,18 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -785,45 +776,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126890609</v>
+        <v>126890318</v>
       </c>
       <c r="B3" t="n">
-        <v>78739</v>
+        <v>80143</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>685141</v>
+        <v>685114</v>
       </c>
       <c r="R3" t="n">
-        <v>7106811</v>
+        <v>7106864</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,12 +861,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Torbjörn Söderquist, Anne Siivola, Lotta Ihse, Jennica Andersson, Hedda Bring, Eleonor Johansson, Gunilla R Burke, kristina stenmarck, Alexandra Astafourova, Elin Kannerby, Lars-Erik Nilsson, Carl Jansson, Beke Regelin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -886,45 +877,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126890318</v>
+        <v>126890609</v>
       </c>
       <c r="B4" t="n">
-        <v>80112</v>
+        <v>78770</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>685114</v>
+        <v>685141</v>
       </c>
       <c r="R4" t="n">
-        <v>7106864</v>
+        <v>7106811</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,12 +962,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -990,7 +981,7 @@
         <v>126889629</v>
       </c>
       <c r="B5" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1088,45 +1079,53 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126889625</v>
+        <v>126891183</v>
       </c>
       <c r="B6" t="n">
-        <v>80083</v>
+        <v>98353</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>685134</v>
+        <v>685180</v>
       </c>
       <c r="R6" t="n">
-        <v>7106898</v>
+        <v>7106957</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1167,18 +1166,19 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1192,7 +1192,7 @@
         <v>126893450</v>
       </c>
       <c r="B7" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>126890610</v>
       </c>
       <c r="B8" t="n">
-        <v>78739</v>
+        <v>78770</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1401,10 +1401,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126890120</v>
+        <v>126890108</v>
       </c>
       <c r="B9" t="n">
-        <v>80955</v>
+        <v>80114</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1412,21 +1412,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1049</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1436,10 +1436,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>685161</v>
+        <v>685100</v>
       </c>
       <c r="R9" t="n">
-        <v>7106837</v>
+        <v>7106931</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1485,17 +1485,17 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1517,10 +1517,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126890108</v>
+        <v>126890120</v>
       </c>
       <c r="B10" t="n">
-        <v>80083</v>
+        <v>80986</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1528,21 +1528,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>1049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1552,10 +1552,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>685100</v>
+        <v>685161</v>
       </c>
       <c r="R10" t="n">
-        <v>7106931</v>
+        <v>7106837</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,17 +1601,17 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1636,7 +1636,7 @@
         <v>126890168</v>
       </c>
       <c r="B11" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1734,10 +1734,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126890596</v>
+        <v>126891396</v>
       </c>
       <c r="B12" t="n">
-        <v>57817</v>
+        <v>80115</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,42 +1745,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>685137</v>
+        <v>685147</v>
       </c>
       <c r="R12" t="n">
-        <v>7106950</v>
+        <v>7106885</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1821,18 +1816,19 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Lars-Erik Nilsson, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1843,10 +1839,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126891396</v>
+        <v>126890596</v>
       </c>
       <c r="B13" t="n">
-        <v>80084</v>
+        <v>57817</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1854,37 +1850,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>685147</v>
+        <v>685137</v>
       </c>
       <c r="R13" t="n">
-        <v>7106885</v>
+        <v>7106950</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1925,19 +1926,18 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1948,45 +1948,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126889636</v>
+        <v>126890153</v>
       </c>
       <c r="B14" t="n">
-        <v>98278</v>
+        <v>79011</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>685270</v>
+        <v>685129</v>
       </c>
       <c r="R14" t="n">
-        <v>7106941</v>
+        <v>7106929</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2033,12 +2033,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2049,45 +2049,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126890124</v>
+        <v>126890186</v>
       </c>
       <c r="B15" t="n">
-        <v>98361</v>
+        <v>80114</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>685176</v>
+        <v>685113</v>
       </c>
       <c r="R15" t="n">
-        <v>7106857</v>
+        <v>7106891</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2122,6 +2122,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2134,12 +2139,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2153,7 +2158,7 @@
         <v>126890112</v>
       </c>
       <c r="B16" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2266,45 +2271,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126890153</v>
+        <v>126889636</v>
       </c>
       <c r="B17" t="n">
-        <v>78980</v>
+        <v>98353</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>685129</v>
+        <v>685270</v>
       </c>
       <c r="R17" t="n">
-        <v>7106929</v>
+        <v>7106941</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2351,12 +2356,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2367,45 +2372,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126890186</v>
+        <v>126890124</v>
       </c>
       <c r="B18" t="n">
-        <v>80083</v>
+        <v>98436</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>685113</v>
+        <v>685176</v>
       </c>
       <c r="R18" t="n">
-        <v>7106891</v>
+        <v>7106857</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2440,11 +2445,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2457,12 +2457,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2476,7 +2476,7 @@
         <v>126890160</v>
       </c>
       <c r="B19" t="n">
-        <v>91506</v>
+        <v>91580</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
         <v>126890113</v>
       </c>
       <c r="B20" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2690,32 +2690,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126890177</v>
+        <v>126890144</v>
       </c>
       <c r="B21" t="n">
-        <v>98278</v>
+        <v>80114</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2725,10 +2725,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>685125</v>
+        <v>685136</v>
       </c>
       <c r="R21" t="n">
-        <v>7106947</v>
+        <v>7106853</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2791,32 +2791,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126890144</v>
+        <v>126890177</v>
       </c>
       <c r="B22" t="n">
-        <v>80083</v>
+        <v>98353</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>685136</v>
+        <v>685125</v>
       </c>
       <c r="R22" t="n">
-        <v>7106853</v>
+        <v>7106947</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2892,10 +2892,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126891171</v>
+        <v>126889628</v>
       </c>
       <c r="B23" t="n">
-        <v>57817</v>
+        <v>79011</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2903,34 +2903,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>685135</v>
+        <v>685180</v>
       </c>
       <c r="R23" t="n">
-        <v>7106966</v>
+        <v>7106844</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2977,12 +2977,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -2993,10 +2993,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126890601</v>
+        <v>126891639</v>
       </c>
       <c r="B24" t="n">
-        <v>57657</v>
+        <v>80114</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3004,34 +3004,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>685168</v>
+        <v>685148</v>
       </c>
       <c r="R24" t="n">
-        <v>7106800</v>
+        <v>7106890</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3078,12 +3078,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3094,10 +3094,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126889628</v>
+        <v>126890601</v>
       </c>
       <c r="B25" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3105,34 +3105,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>685180</v>
+        <v>685168</v>
       </c>
       <c r="R25" t="n">
-        <v>7106844</v>
+        <v>7106800</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3179,12 +3179,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3195,10 +3195,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126891639</v>
+        <v>126891171</v>
       </c>
       <c r="B26" t="n">
-        <v>80083</v>
+        <v>57817</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3206,21 +3206,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3230,10 +3230,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>685148</v>
+        <v>685135</v>
       </c>
       <c r="R26" t="n">
-        <v>7106890</v>
+        <v>7106966</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3280,12 +3280,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3299,7 +3299,7 @@
         <v>126893495</v>
       </c>
       <c r="B27" t="n">
-        <v>98278</v>
+        <v>98353</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3398,10 +3398,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126890152</v>
+        <v>126890121</v>
       </c>
       <c r="B28" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3429,14 +3429,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>685118</v>
+        <v>685160</v>
       </c>
       <c r="R28" t="n">
-        <v>7106922</v>
+        <v>7106836</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3480,15 +3480,30 @@
       <c r="AG28" t="b">
         <v>0</v>
       </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3499,10 +3514,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126890121</v>
+        <v>126890151</v>
       </c>
       <c r="B29" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3530,14 +3545,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>685160</v>
+        <v>685110</v>
       </c>
       <c r="R29" t="n">
-        <v>7106836</v>
+        <v>7106911</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3581,30 +3596,15 @@
       <c r="AG29" t="b">
         <v>0</v>
       </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3615,10 +3615,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126890151</v>
+        <v>126890152</v>
       </c>
       <c r="B30" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3650,10 +3650,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>685110</v>
+        <v>685118</v>
       </c>
       <c r="R30" t="n">
-        <v>7106911</v>
+        <v>7106922</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3716,10 +3716,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126890119</v>
+        <v>126893453</v>
       </c>
       <c r="B31" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3744,17 +3744,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>685161</v>
+        <v>685142</v>
       </c>
       <c r="R31" t="n">
-        <v>7106834</v>
+        <v>7106872</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3789,24 +3793,30 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3817,10 +3827,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126893453</v>
+        <v>126890119</v>
       </c>
       <c r="B32" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3845,21 +3855,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>685142</v>
+        <v>685161</v>
       </c>
       <c r="R32" t="n">
-        <v>7106872</v>
+        <v>7106834</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3894,30 +3900,24 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3931,7 +3931,7 @@
         <v>126889624</v>
       </c>
       <c r="B33" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4032,7 +4032,7 @@
         <v>126890198</v>
       </c>
       <c r="B34" t="n">
-        <v>91506</v>
+        <v>91580</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>126889623</v>
       </c>
       <c r="B35" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4354,10 +4354,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126891641</v>
+        <v>126890167</v>
       </c>
       <c r="B37" t="n">
-        <v>78738</v>
+        <v>80114</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4365,34 +4365,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>685169</v>
+        <v>685168</v>
       </c>
       <c r="R37" t="n">
-        <v>7106940</v>
+        <v>7106810</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4439,12 +4439,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4455,10 +4455,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126890167</v>
+        <v>126891641</v>
       </c>
       <c r="B38" t="n">
-        <v>80083</v>
+        <v>78769</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4466,34 +4466,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>685168</v>
+        <v>685169</v>
       </c>
       <c r="R38" t="n">
-        <v>7106810</v>
+        <v>7106940</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4540,12 +4540,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4556,10 +4556,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126890321</v>
+        <v>126890195</v>
       </c>
       <c r="B39" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4587,14 +4587,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>685165</v>
+        <v>685114</v>
       </c>
       <c r="R39" t="n">
-        <v>7106856</v>
+        <v>7106926</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4641,12 +4641,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4657,10 +4657,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126890195</v>
+        <v>126890321</v>
       </c>
       <c r="B40" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4688,14 +4688,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>685114</v>
+        <v>685165</v>
       </c>
       <c r="R40" t="n">
-        <v>7106926</v>
+        <v>7106856</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4742,12 +4742,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Torbjörn Söderquist, Anne Siivola, Lotta Ihse, Jennica Andersson, Hedda Bring, Eleonor Johansson, Gunilla R Burke, kristina stenmarck, Alexandra Astafourova, Elin Kannerby, Lars-Erik Nilsson, Carl Jansson, Beke Regelin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4761,7 +4761,7 @@
         <v>126890626</v>
       </c>
       <c r="B41" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
         <v>126890187</v>
       </c>
       <c r="B42" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
         <v>126890199</v>
       </c>
       <c r="B43" t="n">
-        <v>92535</v>
+        <v>92609</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5061,10 +5061,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126890585</v>
+        <v>126890107</v>
       </c>
       <c r="B44" t="n">
-        <v>79598</v>
+        <v>79011</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5072,34 +5072,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>685124</v>
+        <v>685123</v>
       </c>
       <c r="R44" t="n">
-        <v>7106964</v>
+        <v>7106920</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5146,12 +5146,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5162,10 +5162,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126890107</v>
+        <v>126890585</v>
       </c>
       <c r="B45" t="n">
-        <v>78980</v>
+        <v>79629</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5173,34 +5173,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>685123</v>
+        <v>685124</v>
       </c>
       <c r="R45" t="n">
-        <v>7106920</v>
+        <v>7106964</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5247,12 +5247,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5266,7 +5266,7 @@
         <v>126890150</v>
       </c>
       <c r="B46" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5367,7 +5367,7 @@
         <v>126890123</v>
       </c>
       <c r="B47" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5480,32 +5480,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126890122</v>
+        <v>126890110</v>
       </c>
       <c r="B48" t="n">
-        <v>98361</v>
+        <v>98353</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5515,10 +5515,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>685170</v>
+        <v>685096</v>
       </c>
       <c r="R48" t="n">
-        <v>7106842</v>
+        <v>7106922</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5581,45 +5581,49 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126890110</v>
+        <v>126893456</v>
       </c>
       <c r="B49" t="n">
-        <v>98278</v>
+        <v>98436</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>685096</v>
+        <v>685136</v>
       </c>
       <c r="R49" t="n">
-        <v>7106922</v>
+        <v>7106940</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5654,24 +5658,30 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5682,10 +5692,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126893456</v>
+        <v>126890193</v>
       </c>
       <c r="B50" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5710,21 +5720,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>685136</v>
+        <v>685111</v>
       </c>
       <c r="R50" t="n">
-        <v>7106940</v>
+        <v>7106903</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5761,7 +5767,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Ca 150-200 plantor</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5770,7 +5776,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5782,7 +5787,7 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5793,10 +5798,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126890193</v>
+        <v>126890122</v>
       </c>
       <c r="B51" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5824,14 +5829,14 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>685111</v>
+        <v>685170</v>
       </c>
       <c r="R51" t="n">
-        <v>7106903</v>
+        <v>7106842</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5866,11 +5871,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ca 150-200 plantor</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -5883,12 +5883,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5899,10 +5899,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126891646</v>
+        <v>126893455</v>
       </c>
       <c r="B52" t="n">
-        <v>78980</v>
+        <v>80114</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5910,34 +5910,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>685108</v>
+        <v>685123</v>
       </c>
       <c r="R52" t="n">
-        <v>7106883</v>
+        <v>7106871</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5972,6 +5972,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -5984,12 +5989,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -6000,45 +6005,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126890116</v>
+        <v>126891646</v>
       </c>
       <c r="B53" t="n">
-        <v>98361</v>
+        <v>79011</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>685140</v>
+        <v>685108</v>
       </c>
       <c r="R53" t="n">
-        <v>7106846</v>
+        <v>7106883</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6085,12 +6090,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6101,10 +6106,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126890115</v>
+        <v>126893452</v>
       </c>
       <c r="B54" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6129,17 +6134,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
         <v>685145</v>
       </c>
       <c r="R54" t="n">
-        <v>7106855</v>
+        <v>7106823</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6174,24 +6183,30 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6202,10 +6217,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126893452</v>
+        <v>126890115</v>
       </c>
       <c r="B55" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6230,21 +6245,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
         <v>685145</v>
       </c>
       <c r="R55" t="n">
-        <v>7106823</v>
+        <v>7106855</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6279,30 +6290,24 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6313,45 +6318,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126893455</v>
+        <v>126890116</v>
       </c>
       <c r="B56" t="n">
-        <v>80083</v>
+        <v>98436</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>685123</v>
+        <v>685140</v>
       </c>
       <c r="R56" t="n">
-        <v>7106871</v>
+        <v>7106846</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6386,11 +6391,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -6403,12 +6403,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6422,7 +6422,7 @@
         <v>126890175</v>
       </c>
       <c r="B57" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6523,7 +6523,7 @@
         <v>126890322</v>
       </c>
       <c r="B58" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6610,7 +6610,7 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Torbjörn Söderquist, Anne Siivola, Lotta Ihse, Jennica Andersson, Hedda Bring, Eleonor Johansson, Gunilla R Burke, kristina stenmarck, Alexandra Astafourova, Elin Kannerby, Lars-Erik Nilsson, Carl Jansson, Beke Regelin</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6624,7 +6624,7 @@
         <v>126890319</v>
       </c>
       <c r="B59" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6716,7 +6716,7 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Torbjörn Söderquist, Anne Siivola, Lotta Ihse, Jennica Andersson, Hedda Bring, Eleonor Johansson, Gunilla R Burke, kristina stenmarck, Alexandra Astafourova, Elin Kannerby, Lars-Erik Nilsson, Carl Jansson, Beke Regelin</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6730,7 +6730,7 @@
         <v>126890106</v>
       </c>
       <c r="B60" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
         <v>126890105</v>
       </c>
       <c r="B61" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6932,7 +6932,7 @@
         <v>126890118</v>
       </c>
       <c r="B62" t="n">
-        <v>81033</v>
+        <v>81064</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7045,10 +7045,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126893492</v>
+        <v>126890114</v>
       </c>
       <c r="B63" t="n">
-        <v>80083</v>
+        <v>79011</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7056,34 +7056,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>685137</v>
+        <v>685143</v>
       </c>
       <c r="R63" t="n">
-        <v>7106892</v>
+        <v>7106862</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7127,15 +7127,30 @@
       <c r="AG63" t="b">
         <v>0</v>
       </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7146,10 +7161,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126890114</v>
+        <v>126893492</v>
       </c>
       <c r="B64" t="n">
-        <v>78980</v>
+        <v>80114</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7157,34 +7172,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>685143</v>
+        <v>685137</v>
       </c>
       <c r="R64" t="n">
-        <v>7106862</v>
+        <v>7106892</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7228,30 +7243,15 @@
       <c r="AG64" t="b">
         <v>0</v>
       </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">

--- a/artfynd/A 57334-2022 artfynd.xlsx
+++ b/artfynd/A 57334-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126889625</v>
       </c>
       <c r="B2" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126890318</v>
       </c>
       <c r="B3" t="n">
-        <v>80143</v>
+        <v>80146</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist, Anne Siivola, Lotta Ihse, Jennica Andersson, Hedda Bring, Eleonor Johansson, Gunilla R Burke, kristina stenmarck, Alexandra Astafourova, Elin Kannerby, Lars-Erik Nilsson, Carl Jansson, Beke Regelin</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126890609</v>
+        <v>126889629</v>
       </c>
       <c r="B4" t="n">
-        <v>78770</v>
+        <v>79014</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,34 +888,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>685141</v>
+        <v>685091</v>
       </c>
       <c r="R4" t="n">
-        <v>7106811</v>
+        <v>7106949</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,12 +962,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -978,45 +978,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126889629</v>
+        <v>126893450</v>
       </c>
       <c r="B5" t="n">
-        <v>79011</v>
+        <v>98442</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>685091</v>
+        <v>685177</v>
       </c>
       <c r="R5" t="n">
-        <v>7106949</v>
+        <v>7106857</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,24 +1055,30 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1082,7 +1092,7 @@
         <v>126891183</v>
       </c>
       <c r="B6" t="n">
-        <v>98353</v>
+        <v>98359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1189,49 +1199,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126893450</v>
+        <v>126890610</v>
       </c>
       <c r="B7" t="n">
-        <v>98436</v>
+        <v>78773</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>685177</v>
+        <v>685137</v>
       </c>
       <c r="R7" t="n">
-        <v>7106857</v>
+        <v>7106950</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,30 +1272,24 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1300,10 +1300,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126890610</v>
+        <v>126890609</v>
       </c>
       <c r="B8" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1335,10 +1335,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>685137</v>
+        <v>685141</v>
       </c>
       <c r="R8" t="n">
-        <v>7106950</v>
+        <v>7106811</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,7 +1404,7 @@
         <v>126890108</v>
       </c>
       <c r="B9" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>126890120</v>
       </c>
       <c r="B10" t="n">
-        <v>80986</v>
+        <v>80989</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>126890168</v>
       </c>
       <c r="B11" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>126891396</v>
       </c>
       <c r="B12" t="n">
-        <v>80115</v>
+        <v>80118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1948,10 +1948,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126890153</v>
+        <v>126890186</v>
       </c>
       <c r="B14" t="n">
-        <v>79011</v>
+        <v>80117</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1959,21 +1959,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1983,10 +1983,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>685129</v>
+        <v>685113</v>
       </c>
       <c r="R14" t="n">
-        <v>7106929</v>
+        <v>7106891</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2019,6 +2019,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2049,10 +2054,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126890186</v>
+        <v>126890112</v>
       </c>
       <c r="B15" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2080,14 +2085,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>685113</v>
+        <v>685116</v>
       </c>
       <c r="R15" t="n">
-        <v>7106891</v>
+        <v>7106932</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2122,11 +2127,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2135,16 +2135,31 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2155,10 +2170,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126890112</v>
+        <v>126890153</v>
       </c>
       <c r="B16" t="n">
-        <v>80114</v>
+        <v>79014</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2166,34 +2181,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>685116</v>
+        <v>685129</v>
       </c>
       <c r="R16" t="n">
-        <v>7106932</v>
+        <v>7106929</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2237,30 +2252,15 @@
       <c r="AG16" t="b">
         <v>0</v>
       </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2271,45 +2271,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126889636</v>
+        <v>126890124</v>
       </c>
       <c r="B17" t="n">
-        <v>98353</v>
+        <v>98442</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>685270</v>
+        <v>685176</v>
       </c>
       <c r="R17" t="n">
-        <v>7106941</v>
+        <v>7106857</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2356,12 +2356,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2372,45 +2372,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126890124</v>
+        <v>126889636</v>
       </c>
       <c r="B18" t="n">
-        <v>98436</v>
+        <v>98359</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>685176</v>
+        <v>685270</v>
       </c>
       <c r="R18" t="n">
-        <v>7106857</v>
+        <v>7106941</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2457,12 +2457,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2476,7 +2476,7 @@
         <v>126890160</v>
       </c>
       <c r="B19" t="n">
-        <v>91580</v>
+        <v>91586</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
         <v>126890113</v>
       </c>
       <c r="B20" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2690,32 +2690,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126890144</v>
+        <v>126890177</v>
       </c>
       <c r="B21" t="n">
-        <v>80114</v>
+        <v>98359</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2725,10 +2725,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>685136</v>
+        <v>685125</v>
       </c>
       <c r="R21" t="n">
-        <v>7106853</v>
+        <v>7106947</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2791,32 +2791,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126890177</v>
+        <v>126890144</v>
       </c>
       <c r="B22" t="n">
-        <v>98353</v>
+        <v>80117</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>685125</v>
+        <v>685136</v>
       </c>
       <c r="R22" t="n">
-        <v>7106947</v>
+        <v>7106853</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2892,10 +2892,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126889628</v>
+        <v>126891639</v>
       </c>
       <c r="B23" t="n">
-        <v>79011</v>
+        <v>80117</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2903,34 +2903,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>685180</v>
+        <v>685148</v>
       </c>
       <c r="R23" t="n">
-        <v>7106844</v>
+        <v>7106890</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2977,12 +2977,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -2993,10 +2993,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126891639</v>
+        <v>126889628</v>
       </c>
       <c r="B24" t="n">
-        <v>80114</v>
+        <v>79014</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3004,34 +3004,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>685148</v>
+        <v>685180</v>
       </c>
       <c r="R24" t="n">
-        <v>7106890</v>
+        <v>7106844</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3078,12 +3078,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3296,45 +3296,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126893495</v>
+        <v>126890151</v>
       </c>
       <c r="B27" t="n">
-        <v>98353</v>
+        <v>79014</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>685133</v>
+        <v>685110</v>
       </c>
       <c r="R27" t="n">
-        <v>7106886</v>
+        <v>7106911</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3375,19 +3375,18 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3401,7 +3400,7 @@
         <v>126890121</v>
       </c>
       <c r="B28" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3514,10 +3513,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126890151</v>
+        <v>126890152</v>
       </c>
       <c r="B29" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3549,10 +3548,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>685110</v>
+        <v>685118</v>
       </c>
       <c r="R29" t="n">
-        <v>7106911</v>
+        <v>7106922</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3615,45 +3614,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126890152</v>
+        <v>126893495</v>
       </c>
       <c r="B30" t="n">
-        <v>79011</v>
+        <v>98359</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>685118</v>
+        <v>685133</v>
       </c>
       <c r="R30" t="n">
-        <v>7106922</v>
+        <v>7106886</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3694,18 +3693,19 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3716,49 +3716,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126893453</v>
+        <v>126889624</v>
       </c>
       <c r="B31" t="n">
-        <v>98436</v>
+        <v>80117</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>685142</v>
+        <v>685145</v>
       </c>
       <c r="R31" t="n">
-        <v>7106872</v>
+        <v>7106886</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3793,30 +3789,24 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3830,7 +3820,7 @@
         <v>126890119</v>
       </c>
       <c r="B32" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3928,45 +3918,49 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126889624</v>
+        <v>126893453</v>
       </c>
       <c r="B33" t="n">
-        <v>80114</v>
+        <v>98442</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>685145</v>
+        <v>685142</v>
       </c>
       <c r="R33" t="n">
-        <v>7106886</v>
+        <v>7106872</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4001,24 +3995,30 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4032,7 +4032,7 @@
         <v>126890198</v>
       </c>
       <c r="B34" t="n">
-        <v>91580</v>
+        <v>91586</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>126889623</v>
       </c>
       <c r="B35" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4354,10 +4354,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126890167</v>
+        <v>126891641</v>
       </c>
       <c r="B37" t="n">
-        <v>80114</v>
+        <v>78772</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4365,34 +4365,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>685168</v>
+        <v>685169</v>
       </c>
       <c r="R37" t="n">
-        <v>7106810</v>
+        <v>7106940</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4439,12 +4439,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4455,10 +4455,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126891641</v>
+        <v>126890167</v>
       </c>
       <c r="B38" t="n">
-        <v>78769</v>
+        <v>80117</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4466,34 +4466,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>685169</v>
+        <v>685168</v>
       </c>
       <c r="R38" t="n">
-        <v>7106940</v>
+        <v>7106810</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4540,12 +4540,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4559,7 +4559,7 @@
         <v>126890195</v>
       </c>
       <c r="B39" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         <v>126890321</v>
       </c>
       <c r="B40" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist, Anne Siivola, Lotta Ihse, Jennica Andersson, Hedda Bring, Eleonor Johansson, Gunilla R Burke, kristina stenmarck, Alexandra Astafourova, Elin Kannerby, Lars-Erik Nilsson, Carl Jansson, Beke Regelin</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4761,7 +4761,7 @@
         <v>126890626</v>
       </c>
       <c r="B41" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
         <v>126890187</v>
       </c>
       <c r="B42" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
         <v>126890199</v>
       </c>
       <c r="B43" t="n">
-        <v>92609</v>
+        <v>92615</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5061,10 +5061,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126890107</v>
+        <v>126890585</v>
       </c>
       <c r="B44" t="n">
-        <v>79011</v>
+        <v>79632</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5072,34 +5072,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>685123</v>
+        <v>685124</v>
       </c>
       <c r="R44" t="n">
-        <v>7106920</v>
+        <v>7106964</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5146,12 +5146,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5162,10 +5162,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126890585</v>
+        <v>126890107</v>
       </c>
       <c r="B45" t="n">
-        <v>79629</v>
+        <v>79014</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5173,34 +5173,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>685124</v>
+        <v>685123</v>
       </c>
       <c r="R45" t="n">
-        <v>7106964</v>
+        <v>7106920</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5247,12 +5247,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5266,7 +5266,7 @@
         <v>126890150</v>
       </c>
       <c r="B46" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5367,7 +5367,7 @@
         <v>126890123</v>
       </c>
       <c r="B47" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5483,7 +5483,7 @@
         <v>126890110</v>
       </c>
       <c r="B48" t="n">
-        <v>98353</v>
+        <v>98359</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5584,7 +5584,7 @@
         <v>126893456</v>
       </c>
       <c r="B49" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5692,10 +5692,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126890193</v>
+        <v>126890122</v>
       </c>
       <c r="B50" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5723,14 +5723,14 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>685111</v>
+        <v>685170</v>
       </c>
       <c r="R50" t="n">
-        <v>7106903</v>
+        <v>7106842</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5765,11 +5765,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ca 150-200 plantor</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -5782,12 +5777,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5798,10 +5793,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126890122</v>
+        <v>126890193</v>
       </c>
       <c r="B51" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5829,14 +5824,14 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>685170</v>
+        <v>685111</v>
       </c>
       <c r="R51" t="n">
-        <v>7106842</v>
+        <v>7106903</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5871,6 +5866,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ca 150-200 plantor</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -5883,12 +5883,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5899,45 +5899,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126893455</v>
+        <v>126890116</v>
       </c>
       <c r="B52" t="n">
-        <v>80114</v>
+        <v>98442</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>685123</v>
+        <v>685140</v>
       </c>
       <c r="R52" t="n">
-        <v>7106871</v>
+        <v>7106846</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5972,11 +5972,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -5989,12 +5984,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -6005,45 +6000,49 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126891646</v>
+        <v>126893452</v>
       </c>
       <c r="B53" t="n">
-        <v>79011</v>
+        <v>98442</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>685108</v>
+        <v>685145</v>
       </c>
       <c r="R53" t="n">
-        <v>7106883</v>
+        <v>7106823</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6078,24 +6077,30 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6106,10 +6111,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126893452</v>
+        <v>126890115</v>
       </c>
       <c r="B54" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6134,21 +6139,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
         <v>685145</v>
       </c>
       <c r="R54" t="n">
-        <v>7106823</v>
+        <v>7106855</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6183,30 +6184,24 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6217,45 +6212,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126890115</v>
+        <v>126893455</v>
       </c>
       <c r="B55" t="n">
-        <v>98436</v>
+        <v>80117</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>685145</v>
+        <v>685123</v>
       </c>
       <c r="R55" t="n">
-        <v>7106855</v>
+        <v>7106871</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6290,6 +6285,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6302,12 +6302,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6318,45 +6318,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126890116</v>
+        <v>126891646</v>
       </c>
       <c r="B56" t="n">
-        <v>98436</v>
+        <v>79014</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>685140</v>
+        <v>685108</v>
       </c>
       <c r="R56" t="n">
-        <v>7106846</v>
+        <v>7106883</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6403,12 +6403,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6422,7 +6422,7 @@
         <v>126890175</v>
       </c>
       <c r="B57" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6520,10 +6520,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126890322</v>
+        <v>126890319</v>
       </c>
       <c r="B58" t="n">
-        <v>79011</v>
+        <v>80117</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6531,21 +6531,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6555,10 +6555,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>685156</v>
+        <v>685113</v>
       </c>
       <c r="R58" t="n">
-        <v>7106959</v>
+        <v>7106871</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6593,6 +6593,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -6610,7 +6615,7 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist, Anne Siivola, Lotta Ihse, Jennica Andersson, Hedda Bring, Eleonor Johansson, Gunilla R Burke, kristina stenmarck, Alexandra Astafourova, Elin Kannerby, Lars-Erik Nilsson, Carl Jansson, Beke Regelin</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6621,10 +6626,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126890319</v>
+        <v>126890322</v>
       </c>
       <c r="B59" t="n">
-        <v>80114</v>
+        <v>79014</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6632,21 +6637,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6656,10 +6661,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>685113</v>
+        <v>685156</v>
       </c>
       <c r="R59" t="n">
-        <v>7106871</v>
+        <v>7106959</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6694,11 +6699,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>På sälg</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -6716,7 +6716,7 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist, Anne Siivola, Lotta Ihse, Jennica Andersson, Hedda Bring, Eleonor Johansson, Gunilla R Burke, kristina stenmarck, Alexandra Astafourova, Elin Kannerby, Lars-Erik Nilsson, Carl Jansson, Beke Regelin</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6727,10 +6727,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126890106</v>
+        <v>126890118</v>
       </c>
       <c r="B60" t="n">
-        <v>79011</v>
+        <v>81067</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6738,21 +6738,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>229558</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Barkporlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pertusaria sommerfeltii</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flörke ex Sommerf.) Fr.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6762,10 +6762,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>685144</v>
+        <v>685153</v>
       </c>
       <c r="R60" t="n">
-        <v>7106929</v>
+        <v>7106835</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6808,6 +6808,21 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -6831,7 +6846,7 @@
         <v>126890105</v>
       </c>
       <c r="B61" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6929,10 +6944,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126890118</v>
+        <v>126890106</v>
       </c>
       <c r="B62" t="n">
-        <v>81064</v>
+        <v>79014</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6940,21 +6955,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>229558</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Barkporlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pertusaria sommerfeltii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Flörke ex Sommerf.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6964,10 +6979,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>685153</v>
+        <v>685144</v>
       </c>
       <c r="R62" t="n">
-        <v>7106835</v>
+        <v>7106929</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7010,21 +7025,6 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -7045,10 +7045,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126890114</v>
+        <v>126893492</v>
       </c>
       <c r="B63" t="n">
-        <v>79011</v>
+        <v>80117</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7056,34 +7056,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>685143</v>
+        <v>685137</v>
       </c>
       <c r="R63" t="n">
-        <v>7106862</v>
+        <v>7106892</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7127,30 +7127,15 @@
       <c r="AG63" t="b">
         <v>0</v>
       </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7161,10 +7146,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126893492</v>
+        <v>126890114</v>
       </c>
       <c r="B64" t="n">
-        <v>80114</v>
+        <v>79014</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7172,34 +7157,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>685137</v>
+        <v>685143</v>
       </c>
       <c r="R64" t="n">
-        <v>7106892</v>
+        <v>7106862</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7243,15 +7228,30 @@
       <c r="AG64" t="b">
         <v>0</v>
       </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">

--- a/artfynd/A 57334-2022 artfynd.xlsx
+++ b/artfynd/A 57334-2022 artfynd.xlsx
@@ -675,45 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126889625</v>
+        <v>126890318</v>
       </c>
       <c r="B2" t="n">
-        <v>80117</v>
+        <v>80146</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>685134</v>
+        <v>685114</v>
       </c>
       <c r="R2" t="n">
-        <v>7106898</v>
+        <v>7106864</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,12 +760,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -776,45 +776,49 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126890318</v>
+        <v>126893450</v>
       </c>
       <c r="B3" t="n">
-        <v>80146</v>
+        <v>98442</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>685114</v>
+        <v>685177</v>
       </c>
       <c r="R3" t="n">
-        <v>7106864</v>
+        <v>7106857</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -849,24 +853,30 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Carl Jansson, Lotta Ihse, Torbjörn Söderquist, kristina stenmarck, Jennica Andersson, Anne Siivola, Lars-Erik Nilsson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Beke Regelin, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -978,49 +988,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126893450</v>
+        <v>126889625</v>
       </c>
       <c r="B5" t="n">
-        <v>98442</v>
+        <v>80117</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>685177</v>
+        <v>685134</v>
       </c>
       <c r="R5" t="n">
-        <v>7106857</v>
+        <v>7106898</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1055,30 +1061,24 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1401,10 +1401,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126890108</v>
+        <v>126890120</v>
       </c>
       <c r="B9" t="n">
-        <v>80117</v>
+        <v>80989</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1412,21 +1412,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>1049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1436,10 +1436,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>685100</v>
+        <v>685161</v>
       </c>
       <c r="R9" t="n">
-        <v>7106931</v>
+        <v>7106837</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1485,17 +1485,17 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1517,10 +1517,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126890120</v>
+        <v>126890108</v>
       </c>
       <c r="B10" t="n">
-        <v>80989</v>
+        <v>80117</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1528,21 +1528,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1049</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1552,10 +1552,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>685161</v>
+        <v>685100</v>
       </c>
       <c r="R10" t="n">
-        <v>7106837</v>
+        <v>7106931</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,17 +1601,17 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1948,10 +1948,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126890186</v>
+        <v>126890153</v>
       </c>
       <c r="B14" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1959,21 +1959,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1983,10 +1983,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>685113</v>
+        <v>685129</v>
       </c>
       <c r="R14" t="n">
-        <v>7106891</v>
+        <v>7106929</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2021,11 +2021,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2043,7 +2038,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Beke Regelin, Torbjörn Söderquist, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, kristina stenmarck, Gunilla R Burke, Elin Kannerby, Carl Jansson, Eleonor Johansson, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2054,7 +2049,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126890112</v>
+        <v>126890186</v>
       </c>
       <c r="B15" t="n">
         <v>80117</v>
@@ -2085,14 +2080,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>685116</v>
+        <v>685113</v>
       </c>
       <c r="R15" t="n">
-        <v>7106932</v>
+        <v>7106891</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2127,6 +2122,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2135,31 +2135,16 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2170,10 +2155,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126890153</v>
+        <v>126890112</v>
       </c>
       <c r="B16" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2181,34 +2166,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>685129</v>
+        <v>685116</v>
       </c>
       <c r="R16" t="n">
-        <v>7106929</v>
+        <v>7106932</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2252,15 +2237,30 @@
       <c r="AG16" t="b">
         <v>0</v>
       </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2271,45 +2271,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126890124</v>
+        <v>126889636</v>
       </c>
       <c r="B17" t="n">
-        <v>98442</v>
+        <v>98359</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>685176</v>
+        <v>685270</v>
       </c>
       <c r="R17" t="n">
-        <v>7106857</v>
+        <v>7106941</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2356,12 +2356,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2372,45 +2372,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126889636</v>
+        <v>126890124</v>
       </c>
       <c r="B18" t="n">
-        <v>98359</v>
+        <v>98442</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>685270</v>
+        <v>685176</v>
       </c>
       <c r="R18" t="n">
-        <v>7106941</v>
+        <v>7106857</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2457,12 +2457,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Beke Regelin, Torbjörn Söderquist, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, kristina stenmarck, Gunilla R Burke, Elin Kannerby, Carl Jansson, Eleonor Johansson, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2690,32 +2690,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126890177</v>
+        <v>126890144</v>
       </c>
       <c r="B21" t="n">
-        <v>98359</v>
+        <v>80117</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2725,10 +2725,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>685125</v>
+        <v>685136</v>
       </c>
       <c r="R21" t="n">
-        <v>7106947</v>
+        <v>7106853</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Beke Regelin, Torbjörn Söderquist, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, kristina stenmarck, Gunilla R Burke, Elin Kannerby, Carl Jansson, Eleonor Johansson, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2791,32 +2791,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126890144</v>
+        <v>126890177</v>
       </c>
       <c r="B22" t="n">
-        <v>80117</v>
+        <v>98359</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>685136</v>
+        <v>685125</v>
       </c>
       <c r="R22" t="n">
-        <v>7106853</v>
+        <v>7106947</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2892,10 +2892,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126891639</v>
+        <v>126891171</v>
       </c>
       <c r="B23" t="n">
-        <v>80117</v>
+        <v>57817</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2903,21 +2903,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2927,10 +2927,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>685148</v>
+        <v>685135</v>
       </c>
       <c r="R23" t="n">
-        <v>7106890</v>
+        <v>7106966</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2977,12 +2977,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3094,10 +3094,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126890601</v>
+        <v>126891639</v>
       </c>
       <c r="B25" t="n">
-        <v>57657</v>
+        <v>80117</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3105,34 +3105,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>685168</v>
+        <v>685148</v>
       </c>
       <c r="R25" t="n">
-        <v>7106800</v>
+        <v>7106890</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3179,12 +3179,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3195,10 +3195,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126891171</v>
+        <v>126890601</v>
       </c>
       <c r="B26" t="n">
-        <v>57817</v>
+        <v>57657</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3206,34 +3206,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>685135</v>
+        <v>685168</v>
       </c>
       <c r="R26" t="n">
-        <v>7106966</v>
+        <v>7106800</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3280,12 +3280,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Beke Regelin, Torbjörn Söderquist, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, kristina stenmarck, Gunilla R Burke, Elin Kannerby, Carl Jansson, Eleonor Johansson, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3603,7 +3603,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Beke Regelin, Torbjörn Söderquist, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, kristina stenmarck, Gunilla R Burke, Elin Kannerby, Carl Jansson, Eleonor Johansson, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -4018,7 +4018,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Alexandra Astafourova, Carl Jansson, Lotta Ihse, Torbjörn Söderquist, kristina stenmarck, Jennica Andersson, Anne Siivola, Lars-Erik Nilsson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Beke Regelin, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Torbjörn Söderquist, Beke Regelin, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, kristina stenmarck, Gunilla R Burke, Elin Kannerby, Carl Jansson, Eleonor Johansson, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4859,32 +4859,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126890187</v>
+        <v>126890199</v>
       </c>
       <c r="B42" t="n">
-        <v>80117</v>
+        <v>92615</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4894,10 +4894,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>685113</v>
+        <v>685175</v>
       </c>
       <c r="R42" t="n">
-        <v>7106903</v>
+        <v>7106946</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4960,32 +4960,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126890199</v>
+        <v>126890187</v>
       </c>
       <c r="B43" t="n">
-        <v>92615</v>
+        <v>80117</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4995,10 +4995,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>685175</v>
+        <v>685113</v>
       </c>
       <c r="R43" t="n">
-        <v>7106946</v>
+        <v>7106903</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5061,10 +5061,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126890585</v>
+        <v>126890107</v>
       </c>
       <c r="B44" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5072,34 +5072,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>685124</v>
+        <v>685123</v>
       </c>
       <c r="R44" t="n">
-        <v>7106964</v>
+        <v>7106920</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5146,12 +5146,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5162,10 +5162,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126890107</v>
+        <v>126890585</v>
       </c>
       <c r="B45" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5173,34 +5173,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>685123</v>
+        <v>685124</v>
       </c>
       <c r="R45" t="n">
-        <v>7106920</v>
+        <v>7106964</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5247,12 +5247,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5263,45 +5263,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126890150</v>
+        <v>126890110</v>
       </c>
       <c r="B46" t="n">
-        <v>79014</v>
+        <v>98359</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>685135</v>
+        <v>685096</v>
       </c>
       <c r="R46" t="n">
-        <v>7106863</v>
+        <v>7106922</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5348,12 +5348,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5364,45 +5364,49 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126890123</v>
+        <v>126893456</v>
       </c>
       <c r="B47" t="n">
-        <v>79014</v>
+        <v>98442</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>685169</v>
+        <v>685136</v>
       </c>
       <c r="R47" t="n">
-        <v>7106843</v>
+        <v>7106940</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5437,39 +5441,30 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Carl Jansson, Lotta Ihse, Torbjörn Söderquist, kristina stenmarck, Jennica Andersson, Anne Siivola, Lars-Erik Nilsson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Beke Regelin, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5480,45 +5475,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126890110</v>
+        <v>126890193</v>
       </c>
       <c r="B48" t="n">
-        <v>98359</v>
+        <v>98442</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>685096</v>
+        <v>685111</v>
       </c>
       <c r="R48" t="n">
-        <v>7106922</v>
+        <v>7106903</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5553,6 +5548,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ca 150-200 plantor</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -5565,12 +5565,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5581,7 +5581,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126893456</v>
+        <v>126890122</v>
       </c>
       <c r="B49" t="n">
         <v>98442</v>
@@ -5609,21 +5609,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>685136</v>
+        <v>685170</v>
       </c>
       <c r="R49" t="n">
-        <v>7106940</v>
+        <v>7106842</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5658,30 +5654,24 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5692,45 +5682,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126890122</v>
+        <v>126890150</v>
       </c>
       <c r="B50" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>685170</v>
+        <v>685135</v>
       </c>
       <c r="R50" t="n">
-        <v>7106842</v>
+        <v>7106863</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5777,12 +5767,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Beke Regelin, Torbjörn Söderquist, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, kristina stenmarck, Gunilla R Burke, Elin Kannerby, Carl Jansson, Eleonor Johansson, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5793,45 +5783,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126890193</v>
+        <v>126890123</v>
       </c>
       <c r="B51" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>685111</v>
+        <v>685169</v>
       </c>
       <c r="R51" t="n">
-        <v>7106903</v>
+        <v>7106843</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5866,11 +5856,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ca 150-200 plantor</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -5879,16 +5864,31 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5899,45 +5899,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126890116</v>
+        <v>126891646</v>
       </c>
       <c r="B52" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>685140</v>
+        <v>685108</v>
       </c>
       <c r="R52" t="n">
-        <v>7106846</v>
+        <v>7106883</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5984,12 +5984,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -6000,49 +6000,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126893452</v>
+        <v>126893455</v>
       </c>
       <c r="B53" t="n">
-        <v>98442</v>
+        <v>80117</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>685145</v>
+        <v>685123</v>
       </c>
       <c r="R53" t="n">
-        <v>7106823</v>
+        <v>7106871</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6088,7 +6084,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6100,7 +6095,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Alexandra Astafourova, Carl Jansson, Lotta Ihse, Torbjörn Söderquist, kristina stenmarck, Jennica Andersson, Anne Siivola, Lars-Erik Nilsson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Beke Regelin, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6212,45 +6207,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126893455</v>
+        <v>126890116</v>
       </c>
       <c r="B55" t="n">
-        <v>80117</v>
+        <v>98442</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>685123</v>
+        <v>685140</v>
       </c>
       <c r="R55" t="n">
-        <v>7106871</v>
+        <v>7106846</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6285,11 +6280,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6302,12 +6292,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6318,45 +6308,49 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126891646</v>
+        <v>126893452</v>
       </c>
       <c r="B56" t="n">
-        <v>79014</v>
+        <v>98442</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>685108</v>
+        <v>685145</v>
       </c>
       <c r="R56" t="n">
-        <v>7106883</v>
+        <v>7106823</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6391,24 +6385,30 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Carl Jansson, Lotta Ihse, Torbjörn Söderquist, kristina stenmarck, Jennica Andersson, Anne Siivola, Lars-Erik Nilsson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Beke Regelin, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6520,10 +6520,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126890319</v>
+        <v>126890322</v>
       </c>
       <c r="B58" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6531,21 +6531,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6555,10 +6555,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>685113</v>
+        <v>685156</v>
       </c>
       <c r="R58" t="n">
-        <v>7106871</v>
+        <v>7106959</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6591,11 +6591,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6626,10 +6621,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126890322</v>
+        <v>126890319</v>
       </c>
       <c r="B59" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6637,21 +6632,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6661,10 +6656,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>685156</v>
+        <v>685113</v>
       </c>
       <c r="R59" t="n">
-        <v>7106959</v>
+        <v>7106871</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6697,6 +6692,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7045,10 +7045,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126893492</v>
+        <v>126890114</v>
       </c>
       <c r="B63" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7056,34 +7056,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>685137</v>
+        <v>685143</v>
       </c>
       <c r="R63" t="n">
-        <v>7106892</v>
+        <v>7106862</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7127,15 +7127,30 @@
       <c r="AG63" t="b">
         <v>0</v>
       </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7146,10 +7161,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126890114</v>
+        <v>126893492</v>
       </c>
       <c r="B64" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7157,34 +7172,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>685143</v>
+        <v>685137</v>
       </c>
       <c r="R64" t="n">
-        <v>7106862</v>
+        <v>7106892</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7228,30 +7243,15 @@
       <c r="AG64" t="b">
         <v>0</v>
       </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">

--- a/artfynd/A 57334-2022 artfynd.xlsx
+++ b/artfynd/A 57334-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126890318</v>
+        <v>126891183</v>
       </c>
       <c r="B2" t="n">
-        <v>80146</v>
+        <v>98359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>685114</v>
+        <v>685180</v>
       </c>
       <c r="R2" t="n">
-        <v>7106864</v>
+        <v>7106957</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,18 +762,19 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -988,45 +997,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126889625</v>
+        <v>126890318</v>
       </c>
       <c r="B5" t="n">
-        <v>80117</v>
+        <v>80146</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>685134</v>
+        <v>685114</v>
       </c>
       <c r="R5" t="n">
-        <v>7106898</v>
+        <v>7106864</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,12 +1082,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1089,53 +1098,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126891183</v>
+        <v>126889625</v>
       </c>
       <c r="B6" t="n">
-        <v>98359</v>
+        <v>80117</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>685180</v>
+        <v>685134</v>
       </c>
       <c r="R6" t="n">
-        <v>7106957</v>
+        <v>7106898</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1176,19 +1177,18 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -2473,45 +2473,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126890160</v>
+        <v>126890113</v>
       </c>
       <c r="B19" t="n">
-        <v>91586</v>
+        <v>79014</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>685113</v>
+        <v>685107</v>
       </c>
       <c r="R19" t="n">
-        <v>7106928</v>
+        <v>7106875</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2555,15 +2555,30 @@
       <c r="AG19" t="b">
         <v>0</v>
       </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Beke Regelin, Torbjörn Söderquist, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, kristina stenmarck, Gunilla R Burke, Elin Kannerby, Carl Jansson, Eleonor Johansson, Jennica Andersson</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2574,45 +2589,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126890113</v>
+        <v>126890160</v>
       </c>
       <c r="B20" t="n">
-        <v>79014</v>
+        <v>91586</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>685107</v>
+        <v>685113</v>
       </c>
       <c r="R20" t="n">
-        <v>7106875</v>
+        <v>7106928</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2656,30 +2671,15 @@
       <c r="AG20" t="b">
         <v>0</v>
       </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Beke Regelin, Torbjörn Söderquist, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, kristina stenmarck, Gunilla R Burke, Elin Kannerby, Carl Jansson, Eleonor Johansson, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -3817,7 +3817,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126890119</v>
+        <v>126893453</v>
       </c>
       <c r="B32" t="n">
         <v>98442</v>
@@ -3845,17 +3845,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>685161</v>
+        <v>685142</v>
       </c>
       <c r="R32" t="n">
-        <v>7106834</v>
+        <v>7106872</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3890,24 +3894,30 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Carl Jansson, Lotta Ihse, Torbjörn Söderquist, kristina stenmarck, Jennica Andersson, Anne Siivola, Lars-Erik Nilsson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Beke Regelin, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3918,7 +3928,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126893453</v>
+        <v>126890119</v>
       </c>
       <c r="B33" t="n">
         <v>98442</v>
@@ -3946,21 +3956,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>685142</v>
+        <v>685161</v>
       </c>
       <c r="R33" t="n">
-        <v>7106872</v>
+        <v>7106834</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3995,30 +4001,24 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Carl Jansson, Lotta Ihse, Torbjörn Söderquist, kristina stenmarck, Jennica Andersson, Anne Siivola, Lars-Erik Nilsson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Beke Regelin, Eleonor Johansson</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -5263,45 +5263,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126890110</v>
+        <v>126890150</v>
       </c>
       <c r="B46" t="n">
-        <v>98359</v>
+        <v>79014</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>685096</v>
+        <v>685135</v>
       </c>
       <c r="R46" t="n">
-        <v>7106922</v>
+        <v>7106863</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5348,12 +5348,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Beke Regelin, Torbjörn Söderquist, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, kristina stenmarck, Gunilla R Burke, Elin Kannerby, Carl Jansson, Eleonor Johansson, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5364,49 +5364,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126893456</v>
+        <v>126890123</v>
       </c>
       <c r="B47" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>685136</v>
+        <v>685169</v>
       </c>
       <c r="R47" t="n">
-        <v>7106940</v>
+        <v>7106843</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5441,30 +5437,39 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Carl Jansson, Lotta Ihse, Torbjörn Söderquist, kristina stenmarck, Jennica Andersson, Anne Siivola, Lars-Erik Nilsson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Beke Regelin, Eleonor Johansson</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5475,45 +5480,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126890193</v>
+        <v>126890110</v>
       </c>
       <c r="B48" t="n">
-        <v>98442</v>
+        <v>98359</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>685111</v>
+        <v>685096</v>
       </c>
       <c r="R48" t="n">
-        <v>7106903</v>
+        <v>7106922</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5548,11 +5553,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ca 150-200 plantor</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -5565,12 +5565,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5581,7 +5581,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126890122</v>
+        <v>126893456</v>
       </c>
       <c r="B49" t="n">
         <v>98442</v>
@@ -5609,17 +5609,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>685170</v>
+        <v>685136</v>
       </c>
       <c r="R49" t="n">
-        <v>7106842</v>
+        <v>7106940</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5654,24 +5658,30 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Carl Jansson, Lotta Ihse, Torbjörn Söderquist, kristina stenmarck, Jennica Andersson, Anne Siivola, Lars-Erik Nilsson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Beke Regelin, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5682,32 +5692,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126890150</v>
+        <v>126890193</v>
       </c>
       <c r="B50" t="n">
-        <v>79014</v>
+        <v>98442</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5717,10 +5727,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>685135</v>
+        <v>685111</v>
       </c>
       <c r="R50" t="n">
-        <v>7106863</v>
+        <v>7106903</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5755,6 +5765,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ca 150-200 plantor</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -5772,7 +5787,7 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Beke Regelin, Torbjörn Söderquist, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, kristina stenmarck, Gunilla R Burke, Elin Kannerby, Carl Jansson, Eleonor Johansson, Jennica Andersson</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5783,32 +5798,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126890123</v>
+        <v>126890122</v>
       </c>
       <c r="B51" t="n">
-        <v>79014</v>
+        <v>98442</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5818,10 +5833,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>685169</v>
+        <v>685170</v>
       </c>
       <c r="R51" t="n">
-        <v>7106843</v>
+        <v>7106842</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5864,21 +5879,6 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -5899,45 +5899,49 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126891646</v>
+        <v>126893452</v>
       </c>
       <c r="B52" t="n">
-        <v>79014</v>
+        <v>98442</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>685108</v>
+        <v>685145</v>
       </c>
       <c r="R52" t="n">
-        <v>7106883</v>
+        <v>7106823</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5972,24 +5976,30 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Carl Jansson, Lotta Ihse, Torbjörn Söderquist, kristina stenmarck, Jennica Andersson, Anne Siivola, Lars-Erik Nilsson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Beke Regelin, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -6000,45 +6010,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126893455</v>
+        <v>126890116</v>
       </c>
       <c r="B53" t="n">
-        <v>80117</v>
+        <v>98442</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>685123</v>
+        <v>685140</v>
       </c>
       <c r="R53" t="n">
-        <v>7106871</v>
+        <v>7106846</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6073,11 +6083,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6090,12 +6095,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Carl Jansson, Lotta Ihse, Torbjörn Söderquist, kristina stenmarck, Jennica Andersson, Anne Siivola, Lars-Erik Nilsson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Beke Regelin, Eleonor Johansson</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6106,45 +6111,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126890115</v>
+        <v>126891646</v>
       </c>
       <c r="B54" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>685145</v>
+        <v>685108</v>
       </c>
       <c r="R54" t="n">
-        <v>7106855</v>
+        <v>7106883</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6191,12 +6196,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6207,45 +6212,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126890116</v>
+        <v>126893455</v>
       </c>
       <c r="B55" t="n">
-        <v>98442</v>
+        <v>80117</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>685140</v>
+        <v>685123</v>
       </c>
       <c r="R55" t="n">
-        <v>7106846</v>
+        <v>7106871</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6280,6 +6285,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6292,12 +6302,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Carl Jansson, Lotta Ihse, Torbjörn Söderquist, kristina stenmarck, Jennica Andersson, Anne Siivola, Lars-Erik Nilsson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Beke Regelin, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6308,7 +6318,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126893452</v>
+        <v>126890115</v>
       </c>
       <c r="B56" t="n">
         <v>98442</v>
@@ -6336,21 +6346,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
         <v>685145</v>
       </c>
       <c r="R56" t="n">
-        <v>7106823</v>
+        <v>7106855</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6385,30 +6391,24 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Carl Jansson, Lotta Ihse, Torbjörn Söderquist, kristina stenmarck, Jennica Andersson, Anne Siivola, Lars-Erik Nilsson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Beke Regelin, Eleonor Johansson</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6419,10 +6419,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126890175</v>
+        <v>126890319</v>
       </c>
       <c r="B57" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6430,34 +6430,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>685138</v>
+        <v>685113</v>
       </c>
       <c r="R57" t="n">
-        <v>7106890</v>
+        <v>7106871</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6492,6 +6492,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -6504,12 +6509,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6520,7 +6525,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126890322</v>
+        <v>126890175</v>
       </c>
       <c r="B58" t="n">
         <v>79014</v>
@@ -6551,14 +6556,14 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>685156</v>
+        <v>685138</v>
       </c>
       <c r="R58" t="n">
-        <v>7106959</v>
+        <v>7106890</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6605,12 +6610,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6621,10 +6626,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126890319</v>
+        <v>126890322</v>
       </c>
       <c r="B59" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6632,21 +6637,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6656,10 +6661,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>685113</v>
+        <v>685156</v>
       </c>
       <c r="R59" t="n">
-        <v>7106871</v>
+        <v>7106959</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6692,11 +6697,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD59" t="b">

--- a/artfynd/A 57334-2022 artfynd.xlsx
+++ b/artfynd/A 57334-2022 artfynd.xlsx
@@ -675,53 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126891183</v>
+        <v>126889629</v>
       </c>
       <c r="B2" t="n">
-        <v>98359</v>
+        <v>79014</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>685180</v>
+        <v>685091</v>
       </c>
       <c r="R2" t="n">
-        <v>7106957</v>
+        <v>7106949</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,19 +754,18 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -785,49 +776,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126893450</v>
+        <v>126889625</v>
       </c>
       <c r="B3" t="n">
-        <v>98442</v>
+        <v>80117</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>685177</v>
+        <v>685134</v>
       </c>
       <c r="R3" t="n">
-        <v>7106857</v>
+        <v>7106898</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,30 +849,24 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Carl Jansson, Lotta Ihse, Torbjörn Söderquist, kristina stenmarck, Jennica Andersson, Anne Siivola, Lars-Erik Nilsson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Beke Regelin, Eleonor Johansson</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -896,45 +877,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126889629</v>
+        <v>126890318</v>
       </c>
       <c r="B4" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>685091</v>
+        <v>685114</v>
       </c>
       <c r="R4" t="n">
-        <v>7106949</v>
+        <v>7106864</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,12 +962,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -997,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126890318</v>
+        <v>126891183</v>
       </c>
       <c r="B5" t="n">
-        <v>80146</v>
+        <v>98360</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1008,34 +989,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>685114</v>
+        <v>685180</v>
       </c>
       <c r="R5" t="n">
-        <v>7106864</v>
+        <v>7106957</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,18 +1065,19 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1098,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126889625</v>
+        <v>126890610</v>
       </c>
       <c r="B6" t="n">
-        <v>80117</v>
+        <v>78773</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1109,34 +1099,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>685134</v>
+        <v>685137</v>
       </c>
       <c r="R6" t="n">
-        <v>7106898</v>
+        <v>7106950</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,12 +1173,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1199,7 +1189,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126890610</v>
+        <v>126890609</v>
       </c>
       <c r="B7" t="n">
         <v>78773</v>
@@ -1234,10 +1224,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>685137</v>
+        <v>685141</v>
       </c>
       <c r="R7" t="n">
-        <v>7106950</v>
+        <v>7106811</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,45 +1290,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126890609</v>
+        <v>126893450</v>
       </c>
       <c r="B8" t="n">
-        <v>78773</v>
+        <v>98443</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>685141</v>
+        <v>685177</v>
       </c>
       <c r="R8" t="n">
-        <v>7106811</v>
+        <v>7106857</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1373,24 +1367,30 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Carl Jansson, Gunilla R Burke, Alexandra Astafourova, Eleonor Johansson, Jennica Andersson, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Beke Regelin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1734,10 +1734,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126891396</v>
+        <v>126890596</v>
       </c>
       <c r="B12" t="n">
-        <v>80118</v>
+        <v>57817</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,37 +1745,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>685147</v>
+        <v>685137</v>
       </c>
       <c r="R12" t="n">
-        <v>7106885</v>
+        <v>7106950</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1816,19 +1821,18 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1839,10 +1843,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126890596</v>
+        <v>126891396</v>
       </c>
       <c r="B13" t="n">
-        <v>57817</v>
+        <v>80118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1850,42 +1854,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>685137</v>
+        <v>685147</v>
       </c>
       <c r="R13" t="n">
-        <v>7106950</v>
+        <v>7106885</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1926,18 +1925,19 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Lars-Erik Nilsson, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2038,7 +2038,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Beke Regelin, Torbjörn Söderquist, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, kristina stenmarck, Gunilla R Burke, Elin Kannerby, Carl Jansson, Eleonor Johansson, Jennica Andersson</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Carl Jansson, Gunilla R Burke, Alexandra Astafourova, Eleonor Johansson, Jennica Andersson, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Beke Regelin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2271,45 +2271,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126889636</v>
+        <v>126890124</v>
       </c>
       <c r="B17" t="n">
-        <v>98359</v>
+        <v>98443</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>685270</v>
+        <v>685176</v>
       </c>
       <c r="R17" t="n">
-        <v>7106941</v>
+        <v>7106857</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2356,12 +2356,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2372,45 +2372,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126890124</v>
+        <v>126889636</v>
       </c>
       <c r="B18" t="n">
-        <v>98442</v>
+        <v>98360</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>685176</v>
+        <v>685270</v>
       </c>
       <c r="R18" t="n">
-        <v>7106857</v>
+        <v>7106941</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2457,12 +2457,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2592,7 +2592,7 @@
         <v>126890160</v>
       </c>
       <c r="B20" t="n">
-        <v>91586</v>
+        <v>91587</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Beke Regelin, Torbjörn Söderquist, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, kristina stenmarck, Gunilla R Burke, Elin Kannerby, Carl Jansson, Eleonor Johansson, Jennica Andersson</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Beke Regelin, Torbjörn Söderquist, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, kristina stenmarck, Gunilla R Burke, Elin Kannerby, Carl Jansson, Eleonor Johansson, Jennica Andersson</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2794,7 +2794,7 @@
         <v>126890177</v>
       </c>
       <c r="B22" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2892,10 +2892,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126891171</v>
+        <v>126890601</v>
       </c>
       <c r="B23" t="n">
-        <v>57817</v>
+        <v>57657</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2903,34 +2903,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>685135</v>
+        <v>685168</v>
       </c>
       <c r="R23" t="n">
-        <v>7106966</v>
+        <v>7106800</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2977,12 +2977,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -2993,10 +2993,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126889628</v>
+        <v>126891639</v>
       </c>
       <c r="B24" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3004,34 +3004,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>685180</v>
+        <v>685148</v>
       </c>
       <c r="R24" t="n">
-        <v>7106844</v>
+        <v>7106890</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3078,12 +3078,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3094,10 +3094,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126891639</v>
+        <v>126891171</v>
       </c>
       <c r="B25" t="n">
-        <v>80117</v>
+        <v>57817</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3105,21 +3105,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3129,10 +3129,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>685148</v>
+        <v>685135</v>
       </c>
       <c r="R25" t="n">
-        <v>7106890</v>
+        <v>7106966</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3179,12 +3179,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3195,10 +3195,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126890601</v>
+        <v>126889628</v>
       </c>
       <c r="B26" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3206,34 +3206,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>685168</v>
+        <v>685180</v>
       </c>
       <c r="R26" t="n">
-        <v>7106800</v>
+        <v>7106844</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3280,12 +3280,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3296,45 +3296,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126890151</v>
+        <v>126893495</v>
       </c>
       <c r="B27" t="n">
-        <v>79014</v>
+        <v>98360</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>685110</v>
+        <v>685133</v>
       </c>
       <c r="R27" t="n">
-        <v>7106911</v>
+        <v>7106886</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3375,18 +3375,19 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Beke Regelin, Torbjörn Söderquist, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, kristina stenmarck, Gunilla R Burke, Elin Kannerby, Carl Jansson, Eleonor Johansson, Jennica Andersson</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3397,7 +3398,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126890121</v>
+        <v>126890151</v>
       </c>
       <c r="B28" t="n">
         <v>79014</v>
@@ -3428,14 +3429,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>685160</v>
+        <v>685110</v>
       </c>
       <c r="R28" t="n">
-        <v>7106836</v>
+        <v>7106911</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3479,30 +3480,15 @@
       <c r="AG28" t="b">
         <v>0</v>
       </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3513,7 +3499,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126890152</v>
+        <v>126890121</v>
       </c>
       <c r="B29" t="n">
         <v>79014</v>
@@ -3544,14 +3530,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>685118</v>
+        <v>685160</v>
       </c>
       <c r="R29" t="n">
-        <v>7106922</v>
+        <v>7106836</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3595,15 +3581,30 @@
       <c r="AG29" t="b">
         <v>0</v>
       </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Beke Regelin, Torbjörn Söderquist, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, kristina stenmarck, Gunilla R Burke, Elin Kannerby, Carl Jansson, Eleonor Johansson, Jennica Andersson</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3614,45 +3615,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126893495</v>
+        <v>126890152</v>
       </c>
       <c r="B30" t="n">
-        <v>98359</v>
+        <v>79014</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>685133</v>
+        <v>685118</v>
       </c>
       <c r="R30" t="n">
-        <v>7106886</v>
+        <v>7106922</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3693,19 +3694,18 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3817,10 +3817,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126893453</v>
+        <v>126890119</v>
       </c>
       <c r="B32" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3845,21 +3845,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>685142</v>
+        <v>685161</v>
       </c>
       <c r="R32" t="n">
-        <v>7106872</v>
+        <v>7106834</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3894,30 +3890,24 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Carl Jansson, Lotta Ihse, Torbjörn Söderquist, kristina stenmarck, Jennica Andersson, Anne Siivola, Lars-Erik Nilsson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Beke Regelin, Eleonor Johansson</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3928,10 +3918,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126890119</v>
+        <v>126893453</v>
       </c>
       <c r="B33" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3956,17 +3946,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>685161</v>
+        <v>685142</v>
       </c>
       <c r="R33" t="n">
-        <v>7106834</v>
+        <v>7106872</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4001,24 +3995,30 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4032,7 +4032,7 @@
         <v>126890198</v>
       </c>
       <c r="B34" t="n">
-        <v>91586</v>
+        <v>91587</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Torbjörn Söderquist, Beke Regelin, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, kristina stenmarck, Gunilla R Burke, Elin Kannerby, Carl Jansson, Eleonor Johansson, Jennica Andersson</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4862,7 +4862,7 @@
         <v>126890199</v>
       </c>
       <c r="B42" t="n">
-        <v>92615</v>
+        <v>92616</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5263,45 +5263,49 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126890150</v>
+        <v>126893456</v>
       </c>
       <c r="B46" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>685135</v>
+        <v>685136</v>
       </c>
       <c r="R46" t="n">
-        <v>7106863</v>
+        <v>7106940</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5336,12 +5340,18 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5353,7 +5363,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Beke Regelin, Torbjörn Söderquist, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, kristina stenmarck, Gunilla R Burke, Elin Kannerby, Carl Jansson, Eleonor Johansson, Jennica Andersson</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5364,45 +5374,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126890123</v>
+        <v>126890193</v>
       </c>
       <c r="B47" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>685169</v>
+        <v>685111</v>
       </c>
       <c r="R47" t="n">
-        <v>7106843</v>
+        <v>7106903</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5437,6 +5447,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ca 150-200 plantor</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5445,31 +5460,16 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5480,32 +5480,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126890110</v>
+        <v>126890122</v>
       </c>
       <c r="B48" t="n">
-        <v>98359</v>
+        <v>98443</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5515,10 +5515,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>685096</v>
+        <v>685170</v>
       </c>
       <c r="R48" t="n">
-        <v>7106922</v>
+        <v>7106842</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5581,49 +5581,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126893456</v>
+        <v>126890110</v>
       </c>
       <c r="B49" t="n">
-        <v>98442</v>
+        <v>98360</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>685136</v>
+        <v>685096</v>
       </c>
       <c r="R49" t="n">
-        <v>7106940</v>
+        <v>7106922</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5658,30 +5654,24 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Carl Jansson, Lotta Ihse, Torbjörn Söderquist, kristina stenmarck, Jennica Andersson, Anne Siivola, Lars-Erik Nilsson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Beke Regelin, Eleonor Johansson</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5692,32 +5682,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126890193</v>
+        <v>126890150</v>
       </c>
       <c r="B50" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5727,10 +5717,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>685111</v>
+        <v>685135</v>
       </c>
       <c r="R50" t="n">
-        <v>7106903</v>
+        <v>7106863</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5763,11 +5753,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ca 150-200 plantor</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5798,32 +5783,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126890122</v>
+        <v>126890123</v>
       </c>
       <c r="B51" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5833,10 +5818,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>685170</v>
+        <v>685169</v>
       </c>
       <c r="R51" t="n">
-        <v>7106842</v>
+        <v>7106843</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5880,6 +5865,21 @@
       <c r="AG51" t="b">
         <v>0</v>
       </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
@@ -5888,7 +5888,7 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Carl Jansson, Gunilla R Burke, Alexandra Astafourova, Eleonor Johansson, Jennica Andersson, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Beke Regelin</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5899,49 +5899,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126893452</v>
+        <v>126893455</v>
       </c>
       <c r="B52" t="n">
-        <v>98442</v>
+        <v>80117</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>685145</v>
+        <v>685123</v>
       </c>
       <c r="R52" t="n">
-        <v>7106823</v>
+        <v>7106871</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5987,7 +5983,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5999,7 +5994,7 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Carl Jansson, Lotta Ihse, Torbjörn Söderquist, kristina stenmarck, Jennica Andersson, Anne Siivola, Lars-Erik Nilsson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Beke Regelin, Eleonor Johansson</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -6010,10 +6005,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126890116</v>
+        <v>126893452</v>
       </c>
       <c r="B53" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6038,17 +6033,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>685140</v>
+        <v>685145</v>
       </c>
       <c r="R53" t="n">
-        <v>7106846</v>
+        <v>7106823</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6083,24 +6082,30 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6212,45 +6217,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126893455</v>
+        <v>126890115</v>
       </c>
       <c r="B55" t="n">
-        <v>80117</v>
+        <v>98443</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>685123</v>
+        <v>685145</v>
       </c>
       <c r="R55" t="n">
-        <v>7106871</v>
+        <v>7106855</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6285,11 +6290,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6302,12 +6302,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Carl Jansson, Lotta Ihse, Torbjörn Söderquist, kristina stenmarck, Jennica Andersson, Anne Siivola, Lars-Erik Nilsson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Beke Regelin, Eleonor Johansson</t>
+          <t>Carl Jansson, Gunilla R Burke, Alexandra Astafourova, Eleonor Johansson, Jennica Andersson, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Beke Regelin</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6318,10 +6318,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126890115</v>
+        <v>126890116</v>
       </c>
       <c r="B56" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6353,10 +6353,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>685145</v>
+        <v>685140</v>
       </c>
       <c r="R56" t="n">
-        <v>7106855</v>
+        <v>7106846</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6419,10 +6419,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126890319</v>
+        <v>126890175</v>
       </c>
       <c r="B57" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6430,34 +6430,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>685113</v>
+        <v>685138</v>
       </c>
       <c r="R57" t="n">
-        <v>7106871</v>
+        <v>7106890</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6492,11 +6492,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>På sälg</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -6509,12 +6504,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6525,7 +6520,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126890175</v>
+        <v>126890322</v>
       </c>
       <c r="B58" t="n">
         <v>79014</v>
@@ -6556,14 +6551,14 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>685138</v>
+        <v>685156</v>
       </c>
       <c r="R58" t="n">
-        <v>7106890</v>
+        <v>7106959</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6610,12 +6605,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6626,10 +6621,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126890322</v>
+        <v>126890319</v>
       </c>
       <c r="B59" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6637,21 +6632,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6661,10 +6656,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>685156</v>
+        <v>685113</v>
       </c>
       <c r="R59" t="n">
-        <v>7106959</v>
+        <v>7106871</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6697,6 +6692,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6727,10 +6727,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126890118</v>
+        <v>126890106</v>
       </c>
       <c r="B60" t="n">
-        <v>81067</v>
+        <v>79014</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6738,21 +6738,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>229558</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Barkporlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pertusaria sommerfeltii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Flörke ex Sommerf.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6762,10 +6762,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>685153</v>
+        <v>685144</v>
       </c>
       <c r="R60" t="n">
-        <v>7106835</v>
+        <v>7106929</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6809,21 +6809,6 @@
       <c r="AG60" t="b">
         <v>0</v>
       </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
@@ -6832,7 +6817,7 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Carl Jansson, Gunilla R Burke, Alexandra Astafourova, Eleonor Johansson, Jennica Andersson, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Beke Regelin</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -6944,10 +6929,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126890106</v>
+        <v>126890118</v>
       </c>
       <c r="B62" t="n">
-        <v>79014</v>
+        <v>81067</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6955,21 +6940,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>229558</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Barkporlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pertusaria sommerfeltii</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flörke ex Sommerf.) Fr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6979,10 +6964,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>685144</v>
+        <v>685153</v>
       </c>
       <c r="R62" t="n">
-        <v>7106929</v>
+        <v>7106835</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7025,6 +7010,21 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -7045,10 +7045,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126890114</v>
+        <v>126893492</v>
       </c>
       <c r="B63" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7056,34 +7056,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>685143</v>
+        <v>685137</v>
       </c>
       <c r="R63" t="n">
-        <v>7106862</v>
+        <v>7106892</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7127,30 +7127,15 @@
       <c r="AG63" t="b">
         <v>0</v>
       </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7161,10 +7146,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126893492</v>
+        <v>126890114</v>
       </c>
       <c r="B64" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7172,34 +7157,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>685137</v>
+        <v>685143</v>
       </c>
       <c r="R64" t="n">
-        <v>7106892</v>
+        <v>7106862</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7243,15 +7228,30 @@
       <c r="AG64" t="b">
         <v>0</v>
       </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Carl Jansson, Gunilla R Burke, Alexandra Astafourova, Eleonor Johansson, Jennica Andersson, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Beke Regelin</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">

--- a/artfynd/A 57334-2022 artfynd.xlsx
+++ b/artfynd/A 57334-2022 artfynd.xlsx
@@ -2993,10 +2993,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126891639</v>
+        <v>126889628</v>
       </c>
       <c r="B24" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3004,34 +3004,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>685148</v>
+        <v>685180</v>
       </c>
       <c r="R24" t="n">
-        <v>7106890</v>
+        <v>7106844</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3078,12 +3078,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3094,10 +3094,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126891171</v>
+        <v>126891639</v>
       </c>
       <c r="B25" t="n">
-        <v>57817</v>
+        <v>80117</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3105,21 +3105,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3129,10 +3129,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>685135</v>
+        <v>685148</v>
       </c>
       <c r="R25" t="n">
-        <v>7106966</v>
+        <v>7106890</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3179,12 +3179,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3195,10 +3195,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126889628</v>
+        <v>126891171</v>
       </c>
       <c r="B26" t="n">
-        <v>79014</v>
+        <v>57817</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3206,34 +3206,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>685180</v>
+        <v>685135</v>
       </c>
       <c r="R26" t="n">
-        <v>7106844</v>
+        <v>7106966</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3280,12 +3280,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3716,45 +3716,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126889624</v>
+        <v>126890119</v>
       </c>
       <c r="B31" t="n">
-        <v>80117</v>
+        <v>98443</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>685145</v>
+        <v>685161</v>
       </c>
       <c r="R31" t="n">
-        <v>7106886</v>
+        <v>7106834</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3801,12 +3801,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3817,45 +3817,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126890119</v>
+        <v>126889624</v>
       </c>
       <c r="B32" t="n">
-        <v>98443</v>
+        <v>80117</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>685161</v>
+        <v>685145</v>
       </c>
       <c r="R32" t="n">
-        <v>7106834</v>
+        <v>7106886</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3902,12 +3902,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -4135,10 +4135,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126889623</v>
+        <v>126890183</v>
       </c>
       <c r="B35" t="n">
-        <v>80117</v>
+        <v>57654</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4146,34 +4146,46 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>685088</v>
+        <v>685138</v>
       </c>
       <c r="R35" t="n">
-        <v>7106936</v>
+        <v>7106859</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4208,6 +4220,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Hackhål</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4220,12 +4237,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4236,10 +4253,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126890183</v>
+        <v>126889623</v>
       </c>
       <c r="B36" t="n">
-        <v>57654</v>
+        <v>80117</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4247,46 +4264,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>685138</v>
+        <v>685088</v>
       </c>
       <c r="R36" t="n">
-        <v>7106859</v>
+        <v>7106936</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4321,11 +4326,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Hackhål</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4338,12 +4338,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -6005,7 +6005,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126893452</v>
+        <v>126890115</v>
       </c>
       <c r="B53" t="n">
         <v>98443</v>
@@ -6033,21 +6033,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
         <v>685145</v>
       </c>
       <c r="R53" t="n">
-        <v>7106823</v>
+        <v>7106855</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6082,30 +6078,24 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Carl Jansson, Gunilla R Burke, Alexandra Astafourova, Eleonor Johansson, Jennica Andersson, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Beke Regelin</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6116,45 +6106,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126891646</v>
+        <v>126890116</v>
       </c>
       <c r="B54" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>685108</v>
+        <v>685140</v>
       </c>
       <c r="R54" t="n">
-        <v>7106883</v>
+        <v>7106846</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6201,12 +6191,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6217,7 +6207,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126890115</v>
+        <v>126893452</v>
       </c>
       <c r="B55" t="n">
         <v>98443</v>
@@ -6245,17 +6235,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
         <v>685145</v>
       </c>
       <c r="R55" t="n">
-        <v>7106855</v>
+        <v>7106823</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6290,24 +6284,30 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Carl Jansson, Gunilla R Burke, Alexandra Astafourova, Eleonor Johansson, Jennica Andersson, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Beke Regelin</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6318,45 +6318,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126890116</v>
+        <v>126891646</v>
       </c>
       <c r="B56" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>685140</v>
+        <v>685108</v>
       </c>
       <c r="R56" t="n">
-        <v>7106846</v>
+        <v>7106883</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6403,12 +6403,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6727,7 +6727,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126890106</v>
+        <v>126890105</v>
       </c>
       <c r="B60" t="n">
         <v>79014</v>
@@ -6762,10 +6762,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>685144</v>
+        <v>685155</v>
       </c>
       <c r="R60" t="n">
-        <v>7106929</v>
+        <v>7106940</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6817,7 +6817,7 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Carl Jansson, Gunilla R Burke, Alexandra Astafourova, Eleonor Johansson, Jennica Andersson, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -6828,7 +6828,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126890105</v>
+        <v>126890106</v>
       </c>
       <c r="B61" t="n">
         <v>79014</v>
@@ -6863,10 +6863,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>685155</v>
+        <v>685144</v>
       </c>
       <c r="R61" t="n">
-        <v>7106940</v>
+        <v>7106929</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6918,7 +6918,7 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Carl Jansson, Gunilla R Burke, Alexandra Astafourova, Eleonor Johansson, Jennica Andersson, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Beke Regelin</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">

--- a/artfynd/A 57334-2022 artfynd.xlsx
+++ b/artfynd/A 57334-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126889629</v>
+        <v>126889625</v>
       </c>
       <c r="B2" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>685091</v>
+        <v>685134</v>
       </c>
       <c r="R2" t="n">
-        <v>7106949</v>
+        <v>7106898</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,45 +776,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126889625</v>
+        <v>126890318</v>
       </c>
       <c r="B3" t="n">
-        <v>80117</v>
+        <v>80146</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>685134</v>
+        <v>685114</v>
       </c>
       <c r="R3" t="n">
-        <v>7106898</v>
+        <v>7106864</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,12 +861,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -877,45 +877,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126890318</v>
+        <v>126889629</v>
       </c>
       <c r="B4" t="n">
-        <v>80146</v>
+        <v>79014</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>685114</v>
+        <v>685091</v>
       </c>
       <c r="R4" t="n">
-        <v>7106864</v>
+        <v>7106949</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,12 +962,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Carl Jansson, Gunilla R Burke, Alexandra Astafourova, Eleonor Johansson, Jennica Andersson, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1517,7 +1517,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126890108</v>
+        <v>126890168</v>
       </c>
       <c r="B10" t="n">
         <v>80117</v>
@@ -1548,14 +1548,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>685100</v>
+        <v>685184</v>
       </c>
       <c r="R10" t="n">
-        <v>7106931</v>
+        <v>7106798</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1599,30 +1599,15 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1633,7 +1618,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126890168</v>
+        <v>126890108</v>
       </c>
       <c r="B11" t="n">
         <v>80117</v>
@@ -1664,14 +1649,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>685184</v>
+        <v>685100</v>
       </c>
       <c r="R11" t="n">
-        <v>7106798</v>
+        <v>7106931</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1715,15 +1700,30 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1734,10 +1734,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126890596</v>
+        <v>126891396</v>
       </c>
       <c r="B12" t="n">
-        <v>57817</v>
+        <v>80118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,42 +1745,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>685137</v>
+        <v>685147</v>
       </c>
       <c r="R12" t="n">
-        <v>7106950</v>
+        <v>7106885</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1821,18 +1816,19 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Lars-Erik Nilsson, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1843,10 +1839,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126891396</v>
+        <v>126890596</v>
       </c>
       <c r="B13" t="n">
-        <v>80118</v>
+        <v>57817</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1854,37 +1850,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>685147</v>
+        <v>685137</v>
       </c>
       <c r="R13" t="n">
-        <v>7106885</v>
+        <v>7106950</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1925,19 +1926,18 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Carl Jansson, Gunilla R Burke, Alexandra Astafourova, Eleonor Johansson, Jennica Andersson, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2271,45 +2271,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126890124</v>
+        <v>126889636</v>
       </c>
       <c r="B17" t="n">
-        <v>98443</v>
+        <v>98360</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>685176</v>
+        <v>685270</v>
       </c>
       <c r="R17" t="n">
-        <v>7106857</v>
+        <v>7106941</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2356,12 +2356,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2372,45 +2372,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126889636</v>
+        <v>126890124</v>
       </c>
       <c r="B18" t="n">
-        <v>98360</v>
+        <v>98443</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>685270</v>
+        <v>685176</v>
       </c>
       <c r="R18" t="n">
-        <v>7106941</v>
+        <v>7106857</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2457,12 +2457,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2473,45 +2473,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126890113</v>
+        <v>126890160</v>
       </c>
       <c r="B19" t="n">
-        <v>79014</v>
+        <v>91587</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>685107</v>
+        <v>685113</v>
       </c>
       <c r="R19" t="n">
-        <v>7106875</v>
+        <v>7106928</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2555,30 +2555,15 @@
       <c r="AG19" t="b">
         <v>0</v>
       </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2589,45 +2574,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126890160</v>
+        <v>126890113</v>
       </c>
       <c r="B20" t="n">
-        <v>91587</v>
+        <v>79014</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>685113</v>
+        <v>685107</v>
       </c>
       <c r="R20" t="n">
-        <v>7106928</v>
+        <v>7106875</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2671,15 +2656,30 @@
       <c r="AG20" t="b">
         <v>0</v>
       </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2892,10 +2892,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126890601</v>
+        <v>126889628</v>
       </c>
       <c r="B23" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2903,34 +2903,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>685168</v>
+        <v>685180</v>
       </c>
       <c r="R23" t="n">
-        <v>7106800</v>
+        <v>7106844</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2977,12 +2977,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -2993,10 +2993,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126889628</v>
+        <v>126891639</v>
       </c>
       <c r="B24" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3004,34 +3004,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>685180</v>
+        <v>685148</v>
       </c>
       <c r="R24" t="n">
-        <v>7106844</v>
+        <v>7106890</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3078,12 +3078,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3094,10 +3094,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126891639</v>
+        <v>126891171</v>
       </c>
       <c r="B25" t="n">
-        <v>80117</v>
+        <v>57817</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3105,21 +3105,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3129,10 +3129,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>685148</v>
+        <v>685135</v>
       </c>
       <c r="R25" t="n">
-        <v>7106890</v>
+        <v>7106966</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3179,12 +3179,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3195,10 +3195,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126891171</v>
+        <v>126890601</v>
       </c>
       <c r="B26" t="n">
-        <v>57817</v>
+        <v>57657</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3206,34 +3206,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>685135</v>
+        <v>685168</v>
       </c>
       <c r="R26" t="n">
-        <v>7106966</v>
+        <v>7106800</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3280,12 +3280,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3296,45 +3296,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126893495</v>
+        <v>126890151</v>
       </c>
       <c r="B27" t="n">
-        <v>98360</v>
+        <v>79014</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>685133</v>
+        <v>685110</v>
       </c>
       <c r="R27" t="n">
-        <v>7106886</v>
+        <v>7106911</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3375,19 +3375,18 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3398,7 +3397,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126890151</v>
+        <v>126890152</v>
       </c>
       <c r="B28" t="n">
         <v>79014</v>
@@ -3433,10 +3432,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>685110</v>
+        <v>685118</v>
       </c>
       <c r="R28" t="n">
-        <v>7106911</v>
+        <v>7106922</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3615,45 +3614,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126890152</v>
+        <v>126893495</v>
       </c>
       <c r="B30" t="n">
-        <v>79014</v>
+        <v>98360</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>685118</v>
+        <v>685133</v>
       </c>
       <c r="R30" t="n">
-        <v>7106922</v>
+        <v>7106886</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3694,18 +3693,19 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3716,45 +3716,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126890119</v>
+        <v>126889624</v>
       </c>
       <c r="B31" t="n">
-        <v>98443</v>
+        <v>80117</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>685161</v>
+        <v>685145</v>
       </c>
       <c r="R31" t="n">
-        <v>7106834</v>
+        <v>7106886</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3801,12 +3801,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3817,45 +3817,49 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126889624</v>
+        <v>126893453</v>
       </c>
       <c r="B32" t="n">
-        <v>80117</v>
+        <v>98443</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>685145</v>
+        <v>685142</v>
       </c>
       <c r="R32" t="n">
-        <v>7106886</v>
+        <v>7106872</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3890,24 +3894,30 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3918,7 +3928,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126893453</v>
+        <v>126890119</v>
       </c>
       <c r="B33" t="n">
         <v>98443</v>
@@ -3946,21 +3956,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>685142</v>
+        <v>685161</v>
       </c>
       <c r="R33" t="n">
-        <v>7106872</v>
+        <v>7106834</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3995,30 +4001,24 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4135,10 +4135,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126890183</v>
+        <v>126889623</v>
       </c>
       <c r="B35" t="n">
-        <v>57654</v>
+        <v>80117</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4146,46 +4146,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>685138</v>
+        <v>685088</v>
       </c>
       <c r="R35" t="n">
-        <v>7106859</v>
+        <v>7106936</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4220,11 +4208,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Hackhål</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4237,12 +4220,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4253,10 +4236,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126889623</v>
+        <v>126890183</v>
       </c>
       <c r="B36" t="n">
-        <v>80117</v>
+        <v>57654</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4264,34 +4247,46 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>685088</v>
+        <v>685138</v>
       </c>
       <c r="R36" t="n">
-        <v>7106936</v>
+        <v>7106859</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4326,6 +4321,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Hackhål</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4338,12 +4338,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4657,7 +4657,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126890321</v>
+        <v>126890626</v>
       </c>
       <c r="B40" t="n">
         <v>79014</v>
@@ -4688,14 +4688,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>685165</v>
+        <v>685132</v>
       </c>
       <c r="R40" t="n">
-        <v>7106856</v>
+        <v>7106962</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4742,12 +4742,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4758,7 +4758,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126890626</v>
+        <v>126890321</v>
       </c>
       <c r="B41" t="n">
         <v>79014</v>
@@ -4789,14 +4789,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>685132</v>
+        <v>685165</v>
       </c>
       <c r="R41" t="n">
-        <v>7106962</v>
+        <v>7106856</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4843,12 +4843,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -4859,32 +4859,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126890199</v>
+        <v>126890187</v>
       </c>
       <c r="B42" t="n">
-        <v>92616</v>
+        <v>80117</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4894,10 +4894,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>685175</v>
+        <v>685113</v>
       </c>
       <c r="R42" t="n">
-        <v>7106946</v>
+        <v>7106903</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4960,32 +4960,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126890187</v>
+        <v>126890199</v>
       </c>
       <c r="B43" t="n">
-        <v>80117</v>
+        <v>92616</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4995,10 +4995,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>685113</v>
+        <v>685175</v>
       </c>
       <c r="R43" t="n">
-        <v>7106903</v>
+        <v>7106946</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5263,49 +5263,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126893456</v>
+        <v>126890150</v>
       </c>
       <c r="B46" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>685136</v>
+        <v>685135</v>
       </c>
       <c r="R46" t="n">
-        <v>7106940</v>
+        <v>7106863</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5340,18 +5336,12 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5363,7 +5353,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5374,45 +5364,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126890193</v>
+        <v>126890123</v>
       </c>
       <c r="B47" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>685111</v>
+        <v>685169</v>
       </c>
       <c r="R47" t="n">
-        <v>7106903</v>
+        <v>7106843</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5447,11 +5437,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ca 150-200 plantor</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5460,16 +5445,31 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5480,32 +5480,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126890122</v>
+        <v>126890110</v>
       </c>
       <c r="B48" t="n">
-        <v>98443</v>
+        <v>98360</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5515,10 +5515,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>685170</v>
+        <v>685096</v>
       </c>
       <c r="R48" t="n">
-        <v>7106842</v>
+        <v>7106922</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5581,45 +5581,49 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126890110</v>
+        <v>126893456</v>
       </c>
       <c r="B49" t="n">
-        <v>98360</v>
+        <v>98443</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>685096</v>
+        <v>685136</v>
       </c>
       <c r="R49" t="n">
-        <v>7106922</v>
+        <v>7106940</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5654,24 +5658,30 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5682,32 +5692,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126890150</v>
+        <v>126890193</v>
       </c>
       <c r="B50" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5717,10 +5727,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>685135</v>
+        <v>685111</v>
       </c>
       <c r="R50" t="n">
-        <v>7106863</v>
+        <v>7106903</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5753,6 +5763,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ca 150-200 plantor</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5783,32 +5798,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126890123</v>
+        <v>126890122</v>
       </c>
       <c r="B51" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5818,10 +5833,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>685169</v>
+        <v>685170</v>
       </c>
       <c r="R51" t="n">
-        <v>7106843</v>
+        <v>7106842</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5865,21 +5880,6 @@
       <c r="AG51" t="b">
         <v>0</v>
       </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
@@ -5888,7 +5888,7 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Carl Jansson, Gunilla R Burke, Alexandra Astafourova, Eleonor Johansson, Jennica Andersson, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5899,10 +5899,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126893455</v>
+        <v>126891646</v>
       </c>
       <c r="B52" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5910,34 +5910,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>685123</v>
+        <v>685108</v>
       </c>
       <c r="R52" t="n">
-        <v>7106871</v>
+        <v>7106883</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5972,11 +5972,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -5989,12 +5984,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -6005,45 +6000,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126890115</v>
+        <v>126893455</v>
       </c>
       <c r="B53" t="n">
-        <v>98443</v>
+        <v>80117</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>685145</v>
+        <v>685123</v>
       </c>
       <c r="R53" t="n">
-        <v>7106855</v>
+        <v>7106871</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6078,6 +6073,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6090,12 +6090,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Carl Jansson, Gunilla R Burke, Alexandra Astafourova, Eleonor Johansson, Jennica Andersson, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Beke Regelin</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6106,7 +6106,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126890116</v>
+        <v>126890115</v>
       </c>
       <c r="B54" t="n">
         <v>98443</v>
@@ -6141,10 +6141,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>685140</v>
+        <v>685145</v>
       </c>
       <c r="R54" t="n">
-        <v>7106846</v>
+        <v>7106855</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6207,7 +6207,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126893452</v>
+        <v>126890116</v>
       </c>
       <c r="B55" t="n">
         <v>98443</v>
@@ -6235,21 +6235,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>685145</v>
+        <v>685140</v>
       </c>
       <c r="R55" t="n">
-        <v>7106823</v>
+        <v>7106846</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6284,30 +6280,24 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6318,45 +6308,49 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126891646</v>
+        <v>126893452</v>
       </c>
       <c r="B56" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>685108</v>
+        <v>685145</v>
       </c>
       <c r="R56" t="n">
-        <v>7106883</v>
+        <v>7106823</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6391,24 +6385,30 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6520,10 +6520,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126890322</v>
+        <v>126890319</v>
       </c>
       <c r="B58" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6531,21 +6531,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6555,10 +6555,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>685156</v>
+        <v>685113</v>
       </c>
       <c r="R58" t="n">
-        <v>7106959</v>
+        <v>7106871</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6591,6 +6591,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6621,10 +6626,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126890319</v>
+        <v>126890322</v>
       </c>
       <c r="B59" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6632,21 +6637,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6656,10 +6661,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>685113</v>
+        <v>685156</v>
       </c>
       <c r="R59" t="n">
-        <v>7106871</v>
+        <v>7106959</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6692,11 +6697,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6727,7 +6727,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126890105</v>
+        <v>126890106</v>
       </c>
       <c r="B60" t="n">
         <v>79014</v>
@@ -6762,10 +6762,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>685155</v>
+        <v>685144</v>
       </c>
       <c r="R60" t="n">
-        <v>7106940</v>
+        <v>7106929</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6828,10 +6828,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126890106</v>
+        <v>126890118</v>
       </c>
       <c r="B61" t="n">
-        <v>79014</v>
+        <v>81067</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6839,21 +6839,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>229558</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Barkporlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pertusaria sommerfeltii</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flörke ex Sommerf.) Fr.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6863,10 +6863,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>685144</v>
+        <v>685153</v>
       </c>
       <c r="R61" t="n">
-        <v>7106929</v>
+        <v>7106835</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6910,6 +6910,21 @@
       <c r="AG61" t="b">
         <v>0</v>
       </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
@@ -6918,7 +6933,7 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Carl Jansson, Gunilla R Burke, Alexandra Astafourova, Eleonor Johansson, Jennica Andersson, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -6929,10 +6944,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126890118</v>
+        <v>126890105</v>
       </c>
       <c r="B62" t="n">
-        <v>81067</v>
+        <v>79014</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6940,21 +6955,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>229558</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Barkporlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pertusaria sommerfeltii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Flörke ex Sommerf.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6964,10 +6979,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>685153</v>
+        <v>685155</v>
       </c>
       <c r="R62" t="n">
-        <v>7106835</v>
+        <v>7106940</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7010,21 +7025,6 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -7045,10 +7045,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126893492</v>
+        <v>126890114</v>
       </c>
       <c r="B63" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7056,34 +7056,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>685137</v>
+        <v>685143</v>
       </c>
       <c r="R63" t="n">
-        <v>7106892</v>
+        <v>7106862</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7127,15 +7127,30 @@
       <c r="AG63" t="b">
         <v>0</v>
       </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7146,10 +7161,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126890114</v>
+        <v>126893492</v>
       </c>
       <c r="B64" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7157,34 +7172,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>685143</v>
+        <v>685137</v>
       </c>
       <c r="R64" t="n">
-        <v>7106862</v>
+        <v>7106892</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7228,30 +7243,15 @@
       <c r="AG64" t="b">
         <v>0</v>
       </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Carl Jansson, Gunilla R Burke, Alexandra Astafourova, Eleonor Johansson, Jennica Andersson, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Beke Regelin</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">

--- a/artfynd/A 57334-2022 artfynd.xlsx
+++ b/artfynd/A 57334-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126889625</v>
+        <v>126889629</v>
       </c>
       <c r="B2" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>685134</v>
+        <v>685091</v>
       </c>
       <c r="R2" t="n">
-        <v>7106898</v>
+        <v>7106949</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,45 +776,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126890318</v>
+        <v>126889625</v>
       </c>
       <c r="B3" t="n">
-        <v>80146</v>
+        <v>80117</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>685114</v>
+        <v>685134</v>
       </c>
       <c r="R3" t="n">
-        <v>7106864</v>
+        <v>7106898</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,12 +861,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -877,45 +877,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126889629</v>
+        <v>126890318</v>
       </c>
       <c r="B4" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>685091</v>
+        <v>685114</v>
       </c>
       <c r="R4" t="n">
-        <v>7106949</v>
+        <v>7106864</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,12 +962,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1734,10 +1734,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126891396</v>
+        <v>126890596</v>
       </c>
       <c r="B12" t="n">
-        <v>80118</v>
+        <v>57817</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,37 +1745,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>685147</v>
+        <v>685137</v>
       </c>
       <c r="R12" t="n">
-        <v>7106885</v>
+        <v>7106950</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1816,19 +1821,18 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1839,10 +1843,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126890596</v>
+        <v>126891396</v>
       </c>
       <c r="B13" t="n">
-        <v>57817</v>
+        <v>80118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1850,42 +1854,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>685137</v>
+        <v>685147</v>
       </c>
       <c r="R13" t="n">
-        <v>7106950</v>
+        <v>7106885</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1926,18 +1925,19 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Lars-Erik Nilsson, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2892,10 +2892,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126889628</v>
+        <v>126891171</v>
       </c>
       <c r="B23" t="n">
-        <v>79014</v>
+        <v>57817</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2903,34 +2903,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>685180</v>
+        <v>685135</v>
       </c>
       <c r="R23" t="n">
-        <v>7106844</v>
+        <v>7106966</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2977,12 +2977,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -2993,10 +2993,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126891639</v>
+        <v>126889628</v>
       </c>
       <c r="B24" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3004,34 +3004,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>685148</v>
+        <v>685180</v>
       </c>
       <c r="R24" t="n">
-        <v>7106890</v>
+        <v>7106844</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3078,12 +3078,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3094,10 +3094,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126891171</v>
+        <v>126891639</v>
       </c>
       <c r="B25" t="n">
-        <v>57817</v>
+        <v>80117</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3105,21 +3105,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3129,10 +3129,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>685135</v>
+        <v>685148</v>
       </c>
       <c r="R25" t="n">
-        <v>7106966</v>
+        <v>7106890</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3179,12 +3179,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -5480,45 +5480,49 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126890110</v>
+        <v>126893456</v>
       </c>
       <c r="B48" t="n">
-        <v>98360</v>
+        <v>98443</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>685096</v>
+        <v>685136</v>
       </c>
       <c r="R48" t="n">
-        <v>7106922</v>
+        <v>7106940</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5553,24 +5557,30 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5581,7 +5591,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126893456</v>
+        <v>126890193</v>
       </c>
       <c r="B49" t="n">
         <v>98443</v>
@@ -5609,21 +5619,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>685136</v>
+        <v>685111</v>
       </c>
       <c r="R49" t="n">
-        <v>7106940</v>
+        <v>7106903</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5660,7 +5666,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Ca 150-200 plantor</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5669,7 +5675,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5681,7 +5686,7 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5692,7 +5697,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126890193</v>
+        <v>126890122</v>
       </c>
       <c r="B50" t="n">
         <v>98443</v>
@@ -5723,14 +5728,14 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>685111</v>
+        <v>685170</v>
       </c>
       <c r="R50" t="n">
-        <v>7106903</v>
+        <v>7106842</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5765,11 +5770,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ca 150-200 plantor</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -5782,12 +5782,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5798,32 +5798,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126890122</v>
+        <v>126890110</v>
       </c>
       <c r="B51" t="n">
-        <v>98443</v>
+        <v>98360</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5833,10 +5833,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>685170</v>
+        <v>685096</v>
       </c>
       <c r="R51" t="n">
-        <v>7106842</v>
+        <v>7106922</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>

--- a/artfynd/A 57334-2022 artfynd.xlsx
+++ b/artfynd/A 57334-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126889629</v>
+        <v>126889625</v>
       </c>
       <c r="B2" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>685091</v>
+        <v>685134</v>
       </c>
       <c r="R2" t="n">
-        <v>7106949</v>
+        <v>7106898</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,45 +776,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126889625</v>
+        <v>126890318</v>
       </c>
       <c r="B3" t="n">
-        <v>80117</v>
+        <v>80146</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>685134</v>
+        <v>685114</v>
       </c>
       <c r="R3" t="n">
-        <v>7106898</v>
+        <v>7106864</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,12 +861,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -877,45 +877,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126890318</v>
+        <v>126889629</v>
       </c>
       <c r="B4" t="n">
-        <v>80146</v>
+        <v>79014</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>685114</v>
+        <v>685091</v>
       </c>
       <c r="R4" t="n">
-        <v>7106864</v>
+        <v>7106949</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,12 +962,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -2892,10 +2892,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126891171</v>
+        <v>126889628</v>
       </c>
       <c r="B23" t="n">
-        <v>57817</v>
+        <v>79014</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2903,34 +2903,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>685135</v>
+        <v>685180</v>
       </c>
       <c r="R23" t="n">
-        <v>7106966</v>
+        <v>7106844</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2977,12 +2977,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -2993,10 +2993,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126889628</v>
+        <v>126891639</v>
       </c>
       <c r="B24" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3004,34 +3004,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>685180</v>
+        <v>685148</v>
       </c>
       <c r="R24" t="n">
-        <v>7106844</v>
+        <v>7106890</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3078,12 +3078,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3094,10 +3094,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126891639</v>
+        <v>126891171</v>
       </c>
       <c r="B25" t="n">
-        <v>80117</v>
+        <v>57817</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3105,21 +3105,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3129,10 +3129,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>685148</v>
+        <v>685135</v>
       </c>
       <c r="R25" t="n">
-        <v>7106890</v>
+        <v>7106966</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3179,12 +3179,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -5480,49 +5480,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126893456</v>
+        <v>126890110</v>
       </c>
       <c r="B48" t="n">
-        <v>98443</v>
+        <v>98360</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>685136</v>
+        <v>685096</v>
       </c>
       <c r="R48" t="n">
-        <v>7106940</v>
+        <v>7106922</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5557,30 +5553,24 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5591,7 +5581,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126890193</v>
+        <v>126893456</v>
       </c>
       <c r="B49" t="n">
         <v>98443</v>
@@ -5619,17 +5609,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>685111</v>
+        <v>685136</v>
       </c>
       <c r="R49" t="n">
-        <v>7106903</v>
+        <v>7106940</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5666,7 +5660,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ca 150-200 plantor</t>
+          <t>None</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5675,6 +5669,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5686,7 +5681,7 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5697,7 +5692,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126890122</v>
+        <v>126890193</v>
       </c>
       <c r="B50" t="n">
         <v>98443</v>
@@ -5728,14 +5723,14 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>685170</v>
+        <v>685111</v>
       </c>
       <c r="R50" t="n">
-        <v>7106842</v>
+        <v>7106903</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5770,6 +5765,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ca 150-200 plantor</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -5782,12 +5782,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5798,32 +5798,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126890110</v>
+        <v>126890122</v>
       </c>
       <c r="B51" t="n">
-        <v>98360</v>
+        <v>98443</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5833,10 +5833,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>685096</v>
+        <v>685170</v>
       </c>
       <c r="R51" t="n">
-        <v>7106922</v>
+        <v>7106842</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6419,10 +6419,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126890175</v>
+        <v>126890319</v>
       </c>
       <c r="B57" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6430,34 +6430,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>685138</v>
+        <v>685113</v>
       </c>
       <c r="R57" t="n">
-        <v>7106890</v>
+        <v>7106871</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6492,6 +6492,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -6504,12 +6509,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6520,10 +6525,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126890319</v>
+        <v>126890322</v>
       </c>
       <c r="B58" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6531,21 +6536,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6555,10 +6560,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>685113</v>
+        <v>685156</v>
       </c>
       <c r="R58" t="n">
-        <v>7106871</v>
+        <v>7106959</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6591,11 +6596,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6626,7 +6626,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126890322</v>
+        <v>126890175</v>
       </c>
       <c r="B59" t="n">
         <v>79014</v>
@@ -6657,14 +6657,14 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>685156</v>
+        <v>685138</v>
       </c>
       <c r="R59" t="n">
-        <v>7106959</v>
+        <v>7106890</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6711,12 +6711,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6727,7 +6727,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126890106</v>
+        <v>126890105</v>
       </c>
       <c r="B60" t="n">
         <v>79014</v>
@@ -6762,10 +6762,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>685144</v>
+        <v>685155</v>
       </c>
       <c r="R60" t="n">
-        <v>7106929</v>
+        <v>7106940</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6828,10 +6828,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126890118</v>
+        <v>126890106</v>
       </c>
       <c r="B61" t="n">
-        <v>81067</v>
+        <v>79014</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6839,21 +6839,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>229558</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Barkporlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pertusaria sommerfeltii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Flörke ex Sommerf.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6863,10 +6863,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>685153</v>
+        <v>685144</v>
       </c>
       <c r="R61" t="n">
-        <v>7106835</v>
+        <v>7106929</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6909,21 +6909,6 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -6944,10 +6929,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126890105</v>
+        <v>126890118</v>
       </c>
       <c r="B62" t="n">
-        <v>79014</v>
+        <v>81067</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6955,21 +6940,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>229558</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Barkporlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pertusaria sommerfeltii</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flörke ex Sommerf.) Fr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6979,10 +6964,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>685155</v>
+        <v>685153</v>
       </c>
       <c r="R62" t="n">
-        <v>7106940</v>
+        <v>7106835</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7025,6 +7010,21 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -7045,10 +7045,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126890114</v>
+        <v>126893492</v>
       </c>
       <c r="B63" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7056,34 +7056,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>685143</v>
+        <v>685137</v>
       </c>
       <c r="R63" t="n">
-        <v>7106862</v>
+        <v>7106892</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7127,30 +7127,15 @@
       <c r="AG63" t="b">
         <v>0</v>
       </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7161,10 +7146,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126893492</v>
+        <v>126890114</v>
       </c>
       <c r="B64" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7172,34 +7157,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>685137</v>
+        <v>685143</v>
       </c>
       <c r="R64" t="n">
-        <v>7106892</v>
+        <v>7106862</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7243,15 +7228,30 @@
       <c r="AG64" t="b">
         <v>0</v>
       </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">

--- a/artfynd/A 57334-2022 artfynd.xlsx
+++ b/artfynd/A 57334-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126889625</v>
+        <v>126889629</v>
       </c>
       <c r="B2" t="n">
-        <v>80117</v>
+        <v>79018</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>685134</v>
+        <v>685091</v>
       </c>
       <c r="R2" t="n">
-        <v>7106898</v>
+        <v>7106949</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126890318</v>
+        <v>126891183</v>
       </c>
       <c r="B3" t="n">
-        <v>80146</v>
+        <v>98364</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,34 +787,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>685114</v>
+        <v>685180</v>
       </c>
       <c r="R3" t="n">
-        <v>7106864</v>
+        <v>7106957</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,18 +863,19 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -877,45 +886,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126889629</v>
+        <v>126893450</v>
       </c>
       <c r="B4" t="n">
-        <v>79014</v>
+        <v>98447</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>685091</v>
+        <v>685177</v>
       </c>
       <c r="R4" t="n">
-        <v>7106949</v>
+        <v>7106857</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -950,24 +963,30 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -978,53 +997,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126891183</v>
+        <v>126890610</v>
       </c>
       <c r="B5" t="n">
-        <v>98360</v>
+        <v>78777</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>685180</v>
+        <v>685137</v>
       </c>
       <c r="R5" t="n">
-        <v>7106957</v>
+        <v>7106950</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1065,19 +1076,18 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1088,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126890610</v>
+        <v>126890609</v>
       </c>
       <c r="B6" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1123,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>685137</v>
+        <v>685141</v>
       </c>
       <c r="R6" t="n">
-        <v>7106950</v>
+        <v>7106811</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,10 +1199,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126890609</v>
+        <v>126889625</v>
       </c>
       <c r="B7" t="n">
-        <v>78773</v>
+        <v>80121</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1200,34 +1210,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>685141</v>
+        <v>685134</v>
       </c>
       <c r="R7" t="n">
-        <v>7106811</v>
+        <v>7106898</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1274,12 +1284,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1290,49 +1300,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126893450</v>
+        <v>126890318</v>
       </c>
       <c r="B8" t="n">
-        <v>98443</v>
+        <v>80150</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>685177</v>
+        <v>685114</v>
       </c>
       <c r="R8" t="n">
-        <v>7106857</v>
+        <v>7106864</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1367,30 +1373,24 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1404,7 +1404,7 @@
         <v>126890120</v>
       </c>
       <c r="B9" t="n">
-        <v>80989</v>
+        <v>80993</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1517,10 +1517,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126890168</v>
+        <v>126890108</v>
       </c>
       <c r="B10" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1548,14 +1548,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>685184</v>
+        <v>685100</v>
       </c>
       <c r="R10" t="n">
-        <v>7106798</v>
+        <v>7106931</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1599,15 +1599,30 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1618,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126890108</v>
+        <v>126890168</v>
       </c>
       <c r="B11" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1649,14 +1664,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>685100</v>
+        <v>685184</v>
       </c>
       <c r="R11" t="n">
-        <v>7106931</v>
+        <v>7106798</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1700,30 +1715,15 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1737,7 +1737,7 @@
         <v>126890596</v>
       </c>
       <c r="B12" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>126891396</v>
       </c>
       <c r="B13" t="n">
-        <v>80118</v>
+        <v>80122</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1948,45 +1948,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126890153</v>
+        <v>126889636</v>
       </c>
       <c r="B14" t="n">
-        <v>79014</v>
+        <v>98364</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>685129</v>
+        <v>685270</v>
       </c>
       <c r="R14" t="n">
-        <v>7106929</v>
+        <v>7106941</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2033,12 +2033,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2049,45 +2049,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126890186</v>
+        <v>126890124</v>
       </c>
       <c r="B15" t="n">
-        <v>80117</v>
+        <v>98447</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>685113</v>
+        <v>685176</v>
       </c>
       <c r="R15" t="n">
-        <v>7106891</v>
+        <v>7106857</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2122,11 +2122,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2139,12 +2134,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2155,10 +2150,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126890112</v>
+        <v>126890186</v>
       </c>
       <c r="B16" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2186,14 +2181,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>685116</v>
+        <v>685113</v>
       </c>
       <c r="R16" t="n">
-        <v>7106932</v>
+        <v>7106891</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2228,6 +2223,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2236,31 +2236,16 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2271,45 +2256,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126889636</v>
+        <v>126890112</v>
       </c>
       <c r="B17" t="n">
-        <v>98360</v>
+        <v>80121</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>685270</v>
+        <v>685116</v>
       </c>
       <c r="R17" t="n">
-        <v>7106941</v>
+        <v>7106932</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2353,15 +2338,30 @@
       <c r="AG17" t="b">
         <v>0</v>
       </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2372,45 +2372,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126890124</v>
+        <v>126890153</v>
       </c>
       <c r="B18" t="n">
-        <v>98443</v>
+        <v>79018</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>685176</v>
+        <v>685129</v>
       </c>
       <c r="R18" t="n">
-        <v>7106857</v>
+        <v>7106929</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2457,12 +2457,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2476,7 +2476,7 @@
         <v>126890160</v>
       </c>
       <c r="B19" t="n">
-        <v>91587</v>
+        <v>91591</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
         <v>126890113</v>
       </c>
       <c r="B20" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
         <v>126890144</v>
       </c>
       <c r="B21" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>126890177</v>
       </c>
       <c r="B22" t="n">
-        <v>98360</v>
+        <v>98364</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>126889628</v>
       </c>
       <c r="B23" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2993,10 +2993,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126891639</v>
+        <v>126891171</v>
       </c>
       <c r="B24" t="n">
-        <v>80117</v>
+        <v>57821</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3004,21 +3004,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3028,10 +3028,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>685148</v>
+        <v>685135</v>
       </c>
       <c r="R24" t="n">
-        <v>7106890</v>
+        <v>7106966</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3078,12 +3078,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3094,10 +3094,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126891171</v>
+        <v>126891639</v>
       </c>
       <c r="B25" t="n">
-        <v>57817</v>
+        <v>80121</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3105,21 +3105,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3129,10 +3129,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>685135</v>
+        <v>685148</v>
       </c>
       <c r="R25" t="n">
-        <v>7106966</v>
+        <v>7106890</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3179,12 +3179,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3198,7 +3198,7 @@
         <v>126890601</v>
       </c>
       <c r="B26" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>126890151</v>
       </c>
       <c r="B27" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3397,10 +3397,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126890152</v>
+        <v>126890121</v>
       </c>
       <c r="B28" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3428,14 +3428,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>685118</v>
+        <v>685160</v>
       </c>
       <c r="R28" t="n">
-        <v>7106922</v>
+        <v>7106836</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3479,15 +3479,30 @@
       <c r="AG28" t="b">
         <v>0</v>
       </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3498,10 +3513,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126890121</v>
+        <v>126890152</v>
       </c>
       <c r="B29" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3529,14 +3544,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>685160</v>
+        <v>685118</v>
       </c>
       <c r="R29" t="n">
-        <v>7106836</v>
+        <v>7106922</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3580,30 +3595,15 @@
       <c r="AG29" t="b">
         <v>0</v>
       </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3617,7 +3617,7 @@
         <v>126893495</v>
       </c>
       <c r="B30" t="n">
-        <v>98360</v>
+        <v>98364</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>126889624</v>
       </c>
       <c r="B31" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         <v>126893453</v>
       </c>
       <c r="B32" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>126890119</v>
       </c>
       <c r="B33" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4032,7 +4032,7 @@
         <v>126890198</v>
       </c>
       <c r="B34" t="n">
-        <v>91587</v>
+        <v>91591</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>126889623</v>
       </c>
       <c r="B35" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
         <v>126890183</v>
       </c>
       <c r="B36" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4357,7 +4357,7 @@
         <v>126891641</v>
       </c>
       <c r="B37" t="n">
-        <v>78772</v>
+        <v>78776</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>126890167</v>
       </c>
       <c r="B38" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4559,7 +4559,7 @@
         <v>126890195</v>
       </c>
       <c r="B39" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4657,10 +4657,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126890626</v>
+        <v>126890321</v>
       </c>
       <c r="B40" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4688,14 +4688,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>685132</v>
+        <v>685165</v>
       </c>
       <c r="R40" t="n">
-        <v>7106962</v>
+        <v>7106856</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4742,12 +4742,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4758,10 +4758,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126890321</v>
+        <v>126890626</v>
       </c>
       <c r="B41" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4789,14 +4789,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>685165</v>
+        <v>685132</v>
       </c>
       <c r="R41" t="n">
-        <v>7106856</v>
+        <v>7106962</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4843,12 +4843,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -4859,32 +4859,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126890187</v>
+        <v>126890199</v>
       </c>
       <c r="B42" t="n">
-        <v>80117</v>
+        <v>92620</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4894,10 +4894,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>685113</v>
+        <v>685175</v>
       </c>
       <c r="R42" t="n">
-        <v>7106903</v>
+        <v>7106946</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Beke Regelin, Torbjörn Söderquist, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -4960,32 +4960,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126890199</v>
+        <v>126890187</v>
       </c>
       <c r="B43" t="n">
-        <v>92616</v>
+        <v>80121</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4995,10 +4995,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>685175</v>
+        <v>685113</v>
       </c>
       <c r="R43" t="n">
-        <v>7106946</v>
+        <v>7106903</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5064,7 +5064,7 @@
         <v>126890107</v>
       </c>
       <c r="B44" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5165,7 +5165,7 @@
         <v>126890585</v>
       </c>
       <c r="B45" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5266,7 +5266,7 @@
         <v>126890150</v>
       </c>
       <c r="B46" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5367,7 +5367,7 @@
         <v>126890123</v>
       </c>
       <c r="B47" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5483,7 +5483,7 @@
         <v>126890110</v>
       </c>
       <c r="B48" t="n">
-        <v>98360</v>
+        <v>98364</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5584,7 +5584,7 @@
         <v>126893456</v>
       </c>
       <c r="B49" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5695,7 +5695,7 @@
         <v>126890193</v>
       </c>
       <c r="B50" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5801,7 +5801,7 @@
         <v>126890122</v>
       </c>
       <c r="B51" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5899,45 +5899,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126891646</v>
+        <v>126890115</v>
       </c>
       <c r="B52" t="n">
-        <v>79014</v>
+        <v>98447</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>685108</v>
+        <v>685145</v>
       </c>
       <c r="R52" t="n">
-        <v>7106883</v>
+        <v>7106855</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5984,12 +5984,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -6000,45 +6000,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126893455</v>
+        <v>126890116</v>
       </c>
       <c r="B53" t="n">
-        <v>80117</v>
+        <v>98447</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>685123</v>
+        <v>685140</v>
       </c>
       <c r="R53" t="n">
-        <v>7106871</v>
+        <v>7106846</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6073,11 +6073,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6090,12 +6085,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6106,10 +6101,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126890115</v>
+        <v>126893452</v>
       </c>
       <c r="B54" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6134,17 +6129,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
         <v>685145</v>
       </c>
       <c r="R54" t="n">
-        <v>7106855</v>
+        <v>7106823</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6179,24 +6178,30 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6207,45 +6212,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126890116</v>
+        <v>126893455</v>
       </c>
       <c r="B55" t="n">
-        <v>98443</v>
+        <v>80121</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>685140</v>
+        <v>685123</v>
       </c>
       <c r="R55" t="n">
-        <v>7106846</v>
+        <v>7106871</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6280,6 +6285,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6292,12 +6302,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6308,49 +6318,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126893452</v>
+        <v>126891646</v>
       </c>
       <c r="B56" t="n">
-        <v>98443</v>
+        <v>79018</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>685145</v>
+        <v>685108</v>
       </c>
       <c r="R56" t="n">
-        <v>7106823</v>
+        <v>7106883</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6385,30 +6391,24 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6419,10 +6419,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126890319</v>
+        <v>126890175</v>
       </c>
       <c r="B57" t="n">
-        <v>80117</v>
+        <v>79018</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6430,34 +6430,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>685113</v>
+        <v>685138</v>
       </c>
       <c r="R57" t="n">
-        <v>7106871</v>
+        <v>7106890</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6492,11 +6492,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>På sälg</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -6509,12 +6504,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6528,7 +6523,7 @@
         <v>126890322</v>
       </c>
       <c r="B58" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6626,10 +6621,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126890175</v>
+        <v>126890319</v>
       </c>
       <c r="B59" t="n">
-        <v>79014</v>
+        <v>80121</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6637,34 +6632,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>685138</v>
+        <v>685113</v>
       </c>
       <c r="R59" t="n">
-        <v>7106890</v>
+        <v>7106871</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6699,6 +6694,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -6711,12 +6711,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6730,7 +6730,7 @@
         <v>126890105</v>
       </c>
       <c r="B60" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
         <v>126890106</v>
       </c>
       <c r="B61" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6932,7 +6932,7 @@
         <v>126890118</v>
       </c>
       <c r="B62" t="n">
-        <v>81067</v>
+        <v>81071</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7048,7 +7048,7 @@
         <v>126893492</v>
       </c>
       <c r="B63" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7149,7 +7149,7 @@
         <v>126890114</v>
       </c>
       <c r="B64" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 57334-2022 artfynd.xlsx
+++ b/artfynd/A 57334-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126889629</v>
+        <v>126889625</v>
       </c>
       <c r="B2" t="n">
-        <v>79018</v>
+        <v>80121</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>685091</v>
+        <v>685134</v>
       </c>
       <c r="R2" t="n">
-        <v>7106949</v>
+        <v>7106898</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,53 +776,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126891183</v>
+        <v>126889629</v>
       </c>
       <c r="B3" t="n">
-        <v>98364</v>
+        <v>79018</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>685180</v>
+        <v>685091</v>
       </c>
       <c r="R3" t="n">
-        <v>7106957</v>
+        <v>7106949</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -863,19 +855,18 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -886,49 +877,53 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126893450</v>
+        <v>126891183</v>
       </c>
       <c r="B4" t="n">
-        <v>98447</v>
+        <v>98364</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>685177</v>
+        <v>685180</v>
       </c>
       <c r="R4" t="n">
-        <v>7106857</v>
+        <v>7106957</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,11 +958,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -981,12 +971,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -997,45 +987,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126890610</v>
+        <v>126890318</v>
       </c>
       <c r="B5" t="n">
-        <v>78777</v>
+        <v>80150</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>685137</v>
+        <v>685114</v>
       </c>
       <c r="R5" t="n">
-        <v>7106950</v>
+        <v>7106864</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1082,12 +1072,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1098,45 +1088,49 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126890609</v>
+        <v>126893450</v>
       </c>
       <c r="B6" t="n">
-        <v>78777</v>
+        <v>98447</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>685141</v>
+        <v>685177</v>
       </c>
       <c r="R6" t="n">
-        <v>7106811</v>
+        <v>7106857</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1171,24 +1165,30 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1199,10 +1199,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126889625</v>
+        <v>126890610</v>
       </c>
       <c r="B7" t="n">
-        <v>80121</v>
+        <v>78777</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1210,34 +1210,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>685134</v>
+        <v>685137</v>
       </c>
       <c r="R7" t="n">
-        <v>7106898</v>
+        <v>7106950</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1284,12 +1284,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1300,45 +1300,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126890318</v>
+        <v>126890609</v>
       </c>
       <c r="B8" t="n">
-        <v>80150</v>
+        <v>78777</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>685114</v>
+        <v>685141</v>
       </c>
       <c r="R8" t="n">
-        <v>7106864</v>
+        <v>7106811</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1385,12 +1385,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1734,10 +1734,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126890596</v>
+        <v>126891396</v>
       </c>
       <c r="B12" t="n">
-        <v>57821</v>
+        <v>80122</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,42 +1745,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>685137</v>
+        <v>685147</v>
       </c>
       <c r="R12" t="n">
-        <v>7106950</v>
+        <v>7106885</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1821,18 +1816,19 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Lars-Erik Nilsson, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1843,10 +1839,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126891396</v>
+        <v>126890596</v>
       </c>
       <c r="B13" t="n">
-        <v>80122</v>
+        <v>57821</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1854,37 +1850,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>685147</v>
+        <v>685137</v>
       </c>
       <c r="R13" t="n">
-        <v>7106885</v>
+        <v>7106950</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1925,19 +1926,18 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1948,45 +1948,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126889636</v>
+        <v>126890153</v>
       </c>
       <c r="B14" t="n">
-        <v>98364</v>
+        <v>79018</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>685270</v>
+        <v>685129</v>
       </c>
       <c r="R14" t="n">
-        <v>7106941</v>
+        <v>7106929</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2033,12 +2033,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2049,45 +2049,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126890124</v>
+        <v>126889636</v>
       </c>
       <c r="B15" t="n">
-        <v>98447</v>
+        <v>98364</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>685176</v>
+        <v>685270</v>
       </c>
       <c r="R15" t="n">
-        <v>7106857</v>
+        <v>7106941</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2134,12 +2134,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2150,45 +2150,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126890186</v>
+        <v>126890124</v>
       </c>
       <c r="B16" t="n">
-        <v>80121</v>
+        <v>98447</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>685113</v>
+        <v>685176</v>
       </c>
       <c r="R16" t="n">
-        <v>7106891</v>
+        <v>7106857</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2223,11 +2223,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2240,12 +2235,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2256,7 +2251,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126890112</v>
+        <v>126890186</v>
       </c>
       <c r="B17" t="n">
         <v>80121</v>
@@ -2287,14 +2282,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>685116</v>
+        <v>685113</v>
       </c>
       <c r="R17" t="n">
-        <v>7106932</v>
+        <v>7106891</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2329,6 +2324,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2337,31 +2337,16 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2372,10 +2357,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126890153</v>
+        <v>126890112</v>
       </c>
       <c r="B18" t="n">
-        <v>79018</v>
+        <v>80121</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2383,34 +2368,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>685129</v>
+        <v>685116</v>
       </c>
       <c r="R18" t="n">
-        <v>7106929</v>
+        <v>7106932</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2454,15 +2439,30 @@
       <c r="AG18" t="b">
         <v>0</v>
       </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2473,45 +2473,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126890160</v>
+        <v>126890113</v>
       </c>
       <c r="B19" t="n">
-        <v>91591</v>
+        <v>79018</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>685113</v>
+        <v>685107</v>
       </c>
       <c r="R19" t="n">
-        <v>7106928</v>
+        <v>7106875</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2555,15 +2555,30 @@
       <c r="AG19" t="b">
         <v>0</v>
       </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2574,45 +2589,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126890113</v>
+        <v>126890160</v>
       </c>
       <c r="B20" t="n">
-        <v>79018</v>
+        <v>91591</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>685107</v>
+        <v>685113</v>
       </c>
       <c r="R20" t="n">
-        <v>7106875</v>
+        <v>7106928</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2656,30 +2671,15 @@
       <c r="AG20" t="b">
         <v>0</v>
       </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2993,10 +2993,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126891171</v>
+        <v>126890601</v>
       </c>
       <c r="B24" t="n">
-        <v>57821</v>
+        <v>57661</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3004,34 +3004,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>685135</v>
+        <v>685168</v>
       </c>
       <c r="R24" t="n">
-        <v>7106966</v>
+        <v>7106800</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3078,12 +3078,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3195,10 +3195,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126890601</v>
+        <v>126891171</v>
       </c>
       <c r="B26" t="n">
-        <v>57661</v>
+        <v>57821</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3206,34 +3206,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>685168</v>
+        <v>685135</v>
       </c>
       <c r="R26" t="n">
-        <v>7106800</v>
+        <v>7106966</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3280,12 +3280,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3716,45 +3716,49 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126889624</v>
+        <v>126893453</v>
       </c>
       <c r="B31" t="n">
-        <v>80121</v>
+        <v>98447</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>685145</v>
+        <v>685142</v>
       </c>
       <c r="R31" t="n">
-        <v>7106886</v>
+        <v>7106872</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3789,24 +3793,30 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3817,7 +3827,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126893453</v>
+        <v>126890119</v>
       </c>
       <c r="B32" t="n">
         <v>98447</v>
@@ -3845,21 +3855,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>685142</v>
+        <v>685161</v>
       </c>
       <c r="R32" t="n">
-        <v>7106872</v>
+        <v>7106834</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3894,30 +3900,24 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3928,45 +3928,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126890119</v>
+        <v>126889624</v>
       </c>
       <c r="B33" t="n">
-        <v>98447</v>
+        <v>80121</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>685161</v>
+        <v>685145</v>
       </c>
       <c r="R33" t="n">
-        <v>7106834</v>
+        <v>7106886</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4013,12 +4013,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4556,7 +4556,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126890195</v>
+        <v>126890321</v>
       </c>
       <c r="B39" t="n">
         <v>79018</v>
@@ -4587,14 +4587,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>685114</v>
+        <v>685165</v>
       </c>
       <c r="R39" t="n">
-        <v>7106926</v>
+        <v>7106856</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4641,12 +4641,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4657,7 +4657,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126890321</v>
+        <v>126890195</v>
       </c>
       <c r="B40" t="n">
         <v>79018</v>
@@ -4688,14 +4688,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>685165</v>
+        <v>685114</v>
       </c>
       <c r="R40" t="n">
-        <v>7106856</v>
+        <v>7106926</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4742,12 +4742,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Beke Regelin, Torbjörn Söderquist, Lotta Ihse</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -5061,10 +5061,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126890107</v>
+        <v>126890585</v>
       </c>
       <c r="B44" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5072,34 +5072,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>685123</v>
+        <v>685124</v>
       </c>
       <c r="R44" t="n">
-        <v>7106920</v>
+        <v>7106964</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5146,12 +5146,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5162,10 +5162,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126890585</v>
+        <v>126890107</v>
       </c>
       <c r="B45" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5173,34 +5173,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>685124</v>
+        <v>685123</v>
       </c>
       <c r="R45" t="n">
-        <v>7106964</v>
+        <v>7106920</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5247,12 +5247,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5480,45 +5480,49 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126890110</v>
+        <v>126893456</v>
       </c>
       <c r="B48" t="n">
-        <v>98364</v>
+        <v>98447</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>685096</v>
+        <v>685136</v>
       </c>
       <c r="R48" t="n">
-        <v>7106922</v>
+        <v>7106940</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5553,24 +5557,30 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5581,7 +5591,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126893456</v>
+        <v>126890193</v>
       </c>
       <c r="B49" t="n">
         <v>98447</v>
@@ -5609,21 +5619,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>685136</v>
+        <v>685111</v>
       </c>
       <c r="R49" t="n">
-        <v>7106940</v>
+        <v>7106903</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5660,7 +5666,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Ca 150-200 plantor</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5669,7 +5675,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5681,7 +5686,7 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5692,7 +5697,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126890193</v>
+        <v>126890122</v>
       </c>
       <c r="B50" t="n">
         <v>98447</v>
@@ -5723,14 +5728,14 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>685111</v>
+        <v>685170</v>
       </c>
       <c r="R50" t="n">
-        <v>7106903</v>
+        <v>7106842</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5765,11 +5770,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ca 150-200 plantor</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -5782,12 +5782,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5798,32 +5798,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126890122</v>
+        <v>126890110</v>
       </c>
       <c r="B51" t="n">
-        <v>98447</v>
+        <v>98364</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5833,10 +5833,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>685170</v>
+        <v>685096</v>
       </c>
       <c r="R51" t="n">
-        <v>7106842</v>
+        <v>7106922</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5899,45 +5899,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126890115</v>
+        <v>126893455</v>
       </c>
       <c r="B52" t="n">
-        <v>98447</v>
+        <v>80121</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>685145</v>
+        <v>685123</v>
       </c>
       <c r="R52" t="n">
-        <v>7106855</v>
+        <v>7106871</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5972,6 +5972,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -5984,12 +5989,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -6000,45 +6005,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126890116</v>
+        <v>126891646</v>
       </c>
       <c r="B53" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>685140</v>
+        <v>685108</v>
       </c>
       <c r="R53" t="n">
-        <v>7106846</v>
+        <v>7106883</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6085,12 +6090,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6101,7 +6106,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126893452</v>
+        <v>126890115</v>
       </c>
       <c r="B54" t="n">
         <v>98447</v>
@@ -6129,21 +6134,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
         <v>685145</v>
       </c>
       <c r="R54" t="n">
-        <v>7106823</v>
+        <v>7106855</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6178,30 +6179,24 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6212,45 +6207,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126893455</v>
+        <v>126890116</v>
       </c>
       <c r="B55" t="n">
-        <v>80121</v>
+        <v>98447</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>685123</v>
+        <v>685140</v>
       </c>
       <c r="R55" t="n">
-        <v>7106871</v>
+        <v>7106846</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6285,11 +6280,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6302,12 +6292,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6318,45 +6308,49 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126891646</v>
+        <v>126893452</v>
       </c>
       <c r="B56" t="n">
-        <v>79018</v>
+        <v>98447</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>685108</v>
+        <v>685145</v>
       </c>
       <c r="R56" t="n">
-        <v>7106883</v>
+        <v>7106823</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6391,24 +6385,30 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6419,7 +6419,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126890175</v>
+        <v>126890322</v>
       </c>
       <c r="B57" t="n">
         <v>79018</v>
@@ -6450,14 +6450,14 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>685138</v>
+        <v>685156</v>
       </c>
       <c r="R57" t="n">
-        <v>7106890</v>
+        <v>7106959</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6504,12 +6504,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6520,10 +6520,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126890322</v>
+        <v>126890319</v>
       </c>
       <c r="B58" t="n">
-        <v>79018</v>
+        <v>80121</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6531,21 +6531,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6555,10 +6555,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>685156</v>
+        <v>685113</v>
       </c>
       <c r="R58" t="n">
-        <v>7106959</v>
+        <v>7106871</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6591,6 +6591,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6621,10 +6626,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126890319</v>
+        <v>126890175</v>
       </c>
       <c r="B59" t="n">
-        <v>80121</v>
+        <v>79018</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6632,34 +6637,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>685113</v>
+        <v>685138</v>
       </c>
       <c r="R59" t="n">
-        <v>7106871</v>
+        <v>7106890</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6694,11 +6699,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>På sälg</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -6711,12 +6711,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">

--- a/artfynd/A 57334-2022 artfynd.xlsx
+++ b/artfynd/A 57334-2022 artfynd.xlsx
@@ -776,45 +776,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126889629</v>
+        <v>126890318</v>
       </c>
       <c r="B3" t="n">
-        <v>79018</v>
+        <v>80150</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>685091</v>
+        <v>685114</v>
       </c>
       <c r="R3" t="n">
-        <v>7106949</v>
+        <v>7106864</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,12 +861,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -987,45 +987,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126890318</v>
+        <v>126893450</v>
       </c>
       <c r="B5" t="n">
-        <v>80150</v>
+        <v>98447</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>685114</v>
+        <v>685177</v>
       </c>
       <c r="R5" t="n">
-        <v>7106864</v>
+        <v>7106857</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1060,24 +1064,30 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1088,49 +1098,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126893450</v>
+        <v>126890610</v>
       </c>
       <c r="B6" t="n">
-        <v>98447</v>
+        <v>78777</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>685177</v>
+        <v>685137</v>
       </c>
       <c r="R6" t="n">
-        <v>7106857</v>
+        <v>7106950</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,30 +1171,24 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1199,7 +1199,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126890610</v>
+        <v>126890609</v>
       </c>
       <c r="B7" t="n">
         <v>78777</v>
@@ -1234,10 +1234,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>685137</v>
+        <v>685141</v>
       </c>
       <c r="R7" t="n">
-        <v>7106950</v>
+        <v>7106811</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,10 +1300,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126890609</v>
+        <v>126889629</v>
       </c>
       <c r="B8" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1311,34 +1311,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>685141</v>
+        <v>685091</v>
       </c>
       <c r="R8" t="n">
-        <v>7106811</v>
+        <v>7106949</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1385,12 +1385,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1948,10 +1948,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126890153</v>
+        <v>126890186</v>
       </c>
       <c r="B14" t="n">
-        <v>79018</v>
+        <v>80121</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1959,21 +1959,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1983,10 +1983,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>685129</v>
+        <v>685113</v>
       </c>
       <c r="R14" t="n">
-        <v>7106929</v>
+        <v>7106891</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2019,6 +2019,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2049,45 +2054,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126889636</v>
+        <v>126890112</v>
       </c>
       <c r="B15" t="n">
-        <v>98364</v>
+        <v>80121</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>685270</v>
+        <v>685116</v>
       </c>
       <c r="R15" t="n">
-        <v>7106941</v>
+        <v>7106932</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2131,15 +2136,30 @@
       <c r="AG15" t="b">
         <v>0</v>
       </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2150,45 +2170,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126890124</v>
+        <v>126890153</v>
       </c>
       <c r="B16" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>685176</v>
+        <v>685129</v>
       </c>
       <c r="R16" t="n">
-        <v>7106857</v>
+        <v>7106929</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2235,12 +2255,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2251,45 +2271,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126890186</v>
+        <v>126889636</v>
       </c>
       <c r="B17" t="n">
-        <v>80121</v>
+        <v>98364</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>685113</v>
+        <v>685270</v>
       </c>
       <c r="R17" t="n">
-        <v>7106891</v>
+        <v>7106941</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2324,11 +2344,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2341,12 +2356,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2357,32 +2372,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126890112</v>
+        <v>126890124</v>
       </c>
       <c r="B18" t="n">
-        <v>80121</v>
+        <v>98447</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2392,10 +2407,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>685116</v>
+        <v>685176</v>
       </c>
       <c r="R18" t="n">
-        <v>7106932</v>
+        <v>7106857</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2438,21 +2453,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2892,10 +2892,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126889628</v>
+        <v>126891639</v>
       </c>
       <c r="B23" t="n">
-        <v>79018</v>
+        <v>80121</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2903,34 +2903,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>685180</v>
+        <v>685148</v>
       </c>
       <c r="R23" t="n">
-        <v>7106844</v>
+        <v>7106890</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2977,12 +2977,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -2993,10 +2993,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126890601</v>
+        <v>126889628</v>
       </c>
       <c r="B24" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3004,34 +3004,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>685168</v>
+        <v>685180</v>
       </c>
       <c r="R24" t="n">
-        <v>7106800</v>
+        <v>7106844</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3078,12 +3078,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3094,10 +3094,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126891639</v>
+        <v>126890601</v>
       </c>
       <c r="B25" t="n">
-        <v>80121</v>
+        <v>57661</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3105,34 +3105,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>685148</v>
+        <v>685168</v>
       </c>
       <c r="R25" t="n">
-        <v>7106890</v>
+        <v>7106800</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3179,12 +3179,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -4135,10 +4135,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126889623</v>
+        <v>126890183</v>
       </c>
       <c r="B35" t="n">
-        <v>80121</v>
+        <v>57658</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4146,34 +4146,46 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>685088</v>
+        <v>685138</v>
       </c>
       <c r="R35" t="n">
-        <v>7106936</v>
+        <v>7106859</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4208,6 +4220,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Hackhål</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4220,12 +4237,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4236,10 +4253,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126890183</v>
+        <v>126889623</v>
       </c>
       <c r="B36" t="n">
-        <v>57658</v>
+        <v>80121</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4247,46 +4264,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>685138</v>
+        <v>685088</v>
       </c>
       <c r="R36" t="n">
-        <v>7106859</v>
+        <v>7106936</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4321,11 +4326,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Hackhål</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4338,12 +4338,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -6419,10 +6419,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126890322</v>
+        <v>126890319</v>
       </c>
       <c r="B57" t="n">
-        <v>79018</v>
+        <v>80121</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6430,21 +6430,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6454,10 +6454,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>685156</v>
+        <v>685113</v>
       </c>
       <c r="R57" t="n">
-        <v>7106959</v>
+        <v>7106871</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6490,6 +6490,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6520,10 +6525,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126890319</v>
+        <v>126890322</v>
       </c>
       <c r="B58" t="n">
-        <v>80121</v>
+        <v>79018</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6531,21 +6536,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6555,10 +6560,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>685113</v>
+        <v>685156</v>
       </c>
       <c r="R58" t="n">
-        <v>7106871</v>
+        <v>7106959</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6591,11 +6596,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6727,10 +6727,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126890105</v>
+        <v>126890118</v>
       </c>
       <c r="B60" t="n">
-        <v>79018</v>
+        <v>81071</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6738,21 +6738,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>229558</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Barkporlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pertusaria sommerfeltii</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flörke ex Sommerf.) Fr.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6762,10 +6762,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>685155</v>
+        <v>685153</v>
       </c>
       <c r="R60" t="n">
-        <v>7106940</v>
+        <v>7106835</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6808,6 +6808,21 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -6828,7 +6843,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126890106</v>
+        <v>126890105</v>
       </c>
       <c r="B61" t="n">
         <v>79018</v>
@@ -6863,10 +6878,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>685144</v>
+        <v>685155</v>
       </c>
       <c r="R61" t="n">
-        <v>7106929</v>
+        <v>7106940</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6929,10 +6944,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126890118</v>
+        <v>126890106</v>
       </c>
       <c r="B62" t="n">
-        <v>81071</v>
+        <v>79018</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6940,21 +6955,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>229558</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Barkporlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pertusaria sommerfeltii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Flörke ex Sommerf.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6964,10 +6979,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>685153</v>
+        <v>685144</v>
       </c>
       <c r="R62" t="n">
-        <v>7106835</v>
+        <v>7106929</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7010,21 +7025,6 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">

--- a/artfynd/A 57334-2022 artfynd.xlsx
+++ b/artfynd/A 57334-2022 artfynd.xlsx
@@ -2473,45 +2473,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126890113</v>
+        <v>126890160</v>
       </c>
       <c r="B19" t="n">
-        <v>79018</v>
+        <v>91591</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>685107</v>
+        <v>685113</v>
       </c>
       <c r="R19" t="n">
-        <v>7106875</v>
+        <v>7106928</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2555,30 +2555,15 @@
       <c r="AG19" t="b">
         <v>0</v>
       </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2589,45 +2574,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126890160</v>
+        <v>126890113</v>
       </c>
       <c r="B20" t="n">
-        <v>91591</v>
+        <v>79018</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>685113</v>
+        <v>685107</v>
       </c>
       <c r="R20" t="n">
-        <v>7106928</v>
+        <v>7106875</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2671,15 +2656,30 @@
       <c r="AG20" t="b">
         <v>0</v>
       </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2892,10 +2892,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126891639</v>
+        <v>126889628</v>
       </c>
       <c r="B23" t="n">
-        <v>80121</v>
+        <v>79018</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2903,34 +2903,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>685148</v>
+        <v>685180</v>
       </c>
       <c r="R23" t="n">
-        <v>7106890</v>
+        <v>7106844</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2977,12 +2977,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -2993,10 +2993,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126889628</v>
+        <v>126890601</v>
       </c>
       <c r="B24" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3004,34 +3004,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>685180</v>
+        <v>685168</v>
       </c>
       <c r="R24" t="n">
-        <v>7106844</v>
+        <v>7106800</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3078,12 +3078,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3094,10 +3094,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126890601</v>
+        <v>126891639</v>
       </c>
       <c r="B25" t="n">
-        <v>57661</v>
+        <v>80121</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3105,34 +3105,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>685168</v>
+        <v>685148</v>
       </c>
       <c r="R25" t="n">
-        <v>7106800</v>
+        <v>7106890</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3179,12 +3179,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -5061,10 +5061,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126890585</v>
+        <v>126890107</v>
       </c>
       <c r="B44" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5072,34 +5072,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>685124</v>
+        <v>685123</v>
       </c>
       <c r="R44" t="n">
-        <v>7106964</v>
+        <v>7106920</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5146,12 +5146,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5162,10 +5162,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126890107</v>
+        <v>126890585</v>
       </c>
       <c r="B45" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5173,34 +5173,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>685123</v>
+        <v>685124</v>
       </c>
       <c r="R45" t="n">
-        <v>7106920</v>
+        <v>7106964</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5247,12 +5247,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">

--- a/artfynd/A 57334-2022 artfynd.xlsx
+++ b/artfynd/A 57334-2022 artfynd.xlsx
@@ -675,45 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126889625</v>
+        <v>126893450</v>
       </c>
       <c r="B2" t="n">
-        <v>80121</v>
+        <v>98448</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>685134</v>
+        <v>685177</v>
       </c>
       <c r="R2" t="n">
-        <v>7106898</v>
+        <v>7106857</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,24 +752,30 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -776,45 +786,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126890318</v>
+        <v>126889625</v>
       </c>
       <c r="B3" t="n">
-        <v>80150</v>
+        <v>80121</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>685114</v>
+        <v>685134</v>
       </c>
       <c r="R3" t="n">
-        <v>7106864</v>
+        <v>7106898</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,12 +871,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -877,53 +887,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126891183</v>
+        <v>126889629</v>
       </c>
       <c r="B4" t="n">
-        <v>98364</v>
+        <v>79018</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>685180</v>
+        <v>685091</v>
       </c>
       <c r="R4" t="n">
-        <v>7106957</v>
+        <v>7106949</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,19 +966,18 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -987,49 +988,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126893450</v>
+        <v>126890318</v>
       </c>
       <c r="B5" t="n">
-        <v>98447</v>
+        <v>80150</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>685177</v>
+        <v>685114</v>
       </c>
       <c r="R5" t="n">
-        <v>7106857</v>
+        <v>7106864</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1064,30 +1061,24 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1098,45 +1089,53 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126890610</v>
+        <v>126891183</v>
       </c>
       <c r="B6" t="n">
-        <v>78777</v>
+        <v>98365</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>685137</v>
+        <v>685180</v>
       </c>
       <c r="R6" t="n">
-        <v>7106950</v>
+        <v>7106957</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1177,18 +1176,19 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1199,7 +1199,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126890609</v>
+        <v>126890610</v>
       </c>
       <c r="B7" t="n">
         <v>78777</v>
@@ -1234,10 +1234,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>685141</v>
+        <v>685137</v>
       </c>
       <c r="R7" t="n">
-        <v>7106811</v>
+        <v>7106950</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,10 +1300,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126889629</v>
+        <v>126890609</v>
       </c>
       <c r="B8" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1311,34 +1311,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>685091</v>
+        <v>685141</v>
       </c>
       <c r="R8" t="n">
-        <v>7106949</v>
+        <v>7106811</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1385,12 +1385,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Beke Regelin, Torbjörn Söderquist, Anne Siivola, Lotta Ihse, Jennica Andersson, Hedda Bring, Eleonor Johansson, Gunilla R Burke, kristina stenmarck, Alexandra Astafourova, Elin Kannerby, Carl Jansson, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1948,10 +1948,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126890186</v>
+        <v>126890153</v>
       </c>
       <c r="B14" t="n">
-        <v>80121</v>
+        <v>79018</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1959,21 +1959,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1983,10 +1983,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>685113</v>
+        <v>685129</v>
       </c>
       <c r="R14" t="n">
-        <v>7106891</v>
+        <v>7106929</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2019,11 +2019,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Sälg</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2054,7 +2049,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126890112</v>
+        <v>126890186</v>
       </c>
       <c r="B15" t="n">
         <v>80121</v>
@@ -2085,14 +2080,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>685116</v>
+        <v>685113</v>
       </c>
       <c r="R15" t="n">
-        <v>7106932</v>
+        <v>7106891</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2127,6 +2122,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2135,31 +2135,16 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2170,10 +2155,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126890153</v>
+        <v>126890112</v>
       </c>
       <c r="B16" t="n">
-        <v>79018</v>
+        <v>80121</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2181,34 +2166,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>685129</v>
+        <v>685116</v>
       </c>
       <c r="R16" t="n">
-        <v>7106929</v>
+        <v>7106932</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2252,15 +2237,30 @@
       <c r="AG16" t="b">
         <v>0</v>
       </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2274,7 +2274,7 @@
         <v>126889636</v>
       </c>
       <c r="B17" t="n">
-        <v>98364</v>
+        <v>98365</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>126890124</v>
       </c>
       <c r="B18" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>126890177</v>
       </c>
       <c r="B22" t="n">
-        <v>98364</v>
+        <v>98365</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2892,10 +2892,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126889628</v>
+        <v>126891639</v>
       </c>
       <c r="B23" t="n">
-        <v>79018</v>
+        <v>80121</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2903,34 +2903,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>685180</v>
+        <v>685148</v>
       </c>
       <c r="R23" t="n">
-        <v>7106844</v>
+        <v>7106890</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2977,12 +2977,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -2993,10 +2993,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126890601</v>
+        <v>126889628</v>
       </c>
       <c r="B24" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3004,34 +3004,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>685168</v>
+        <v>685180</v>
       </c>
       <c r="R24" t="n">
-        <v>7106800</v>
+        <v>7106844</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3078,12 +3078,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3094,10 +3094,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126891639</v>
+        <v>126890601</v>
       </c>
       <c r="B25" t="n">
-        <v>80121</v>
+        <v>57661</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3105,34 +3105,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>685148</v>
+        <v>685168</v>
       </c>
       <c r="R25" t="n">
-        <v>7106890</v>
+        <v>7106800</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3179,12 +3179,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3296,7 +3296,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126890151</v>
+        <v>126890121</v>
       </c>
       <c r="B27" t="n">
         <v>79018</v>
@@ -3327,14 +3327,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>685110</v>
+        <v>685160</v>
       </c>
       <c r="R27" t="n">
-        <v>7106911</v>
+        <v>7106836</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3378,15 +3378,30 @@
       <c r="AG27" t="b">
         <v>0</v>
       </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3397,7 +3412,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126890121</v>
+        <v>126890152</v>
       </c>
       <c r="B28" t="n">
         <v>79018</v>
@@ -3428,14 +3443,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>685160</v>
+        <v>685118</v>
       </c>
       <c r="R28" t="n">
-        <v>7106836</v>
+        <v>7106922</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3479,30 +3494,15 @@
       <c r="AG28" t="b">
         <v>0</v>
       </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3513,7 +3513,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126890152</v>
+        <v>126890151</v>
       </c>
       <c r="B29" t="n">
         <v>79018</v>
@@ -3548,10 +3548,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>685118</v>
+        <v>685110</v>
       </c>
       <c r="R29" t="n">
-        <v>7106922</v>
+        <v>7106911</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3617,7 +3617,7 @@
         <v>126893495</v>
       </c>
       <c r="B30" t="n">
-        <v>98364</v>
+        <v>98365</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3716,49 +3716,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126893453</v>
+        <v>126889624</v>
       </c>
       <c r="B31" t="n">
-        <v>98447</v>
+        <v>80121</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>685142</v>
+        <v>685145</v>
       </c>
       <c r="R31" t="n">
-        <v>7106872</v>
+        <v>7106886</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3793,30 +3789,24 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3827,10 +3817,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126890119</v>
+        <v>126893453</v>
       </c>
       <c r="B32" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3855,17 +3845,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>685161</v>
+        <v>685142</v>
       </c>
       <c r="R32" t="n">
-        <v>7106834</v>
+        <v>7106872</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3900,24 +3894,30 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3928,45 +3928,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126889624</v>
+        <v>126890119</v>
       </c>
       <c r="B33" t="n">
-        <v>80121</v>
+        <v>98448</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>685145</v>
+        <v>685161</v>
       </c>
       <c r="R33" t="n">
-        <v>7106886</v>
+        <v>7106834</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4013,12 +4013,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4556,7 +4556,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126890321</v>
+        <v>126890195</v>
       </c>
       <c r="B39" t="n">
         <v>79018</v>
@@ -4587,14 +4587,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>685165</v>
+        <v>685114</v>
       </c>
       <c r="R39" t="n">
-        <v>7106856</v>
+        <v>7106926</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4641,12 +4641,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4657,7 +4657,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126890195</v>
+        <v>126890321</v>
       </c>
       <c r="B40" t="n">
         <v>79018</v>
@@ -4688,14 +4688,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>685114</v>
+        <v>685165</v>
       </c>
       <c r="R40" t="n">
-        <v>7106926</v>
+        <v>7106856</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4742,12 +4742,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -5263,7 +5263,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126890150</v>
+        <v>126890123</v>
       </c>
       <c r="B46" t="n">
         <v>79018</v>
@@ -5294,14 +5294,14 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>685135</v>
+        <v>685169</v>
       </c>
       <c r="R46" t="n">
-        <v>7106863</v>
+        <v>7106843</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5345,15 +5345,30 @@
       <c r="AG46" t="b">
         <v>0</v>
       </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5364,45 +5379,49 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126890123</v>
+        <v>126893456</v>
       </c>
       <c r="B47" t="n">
-        <v>79018</v>
+        <v>98448</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>685169</v>
+        <v>685136</v>
       </c>
       <c r="R47" t="n">
-        <v>7106843</v>
+        <v>7106940</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5437,39 +5456,30 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5480,49 +5490,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126893456</v>
+        <v>126890150</v>
       </c>
       <c r="B48" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>685136</v>
+        <v>685135</v>
       </c>
       <c r="R48" t="n">
-        <v>7106940</v>
+        <v>7106863</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5557,18 +5563,12 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5580,7 +5580,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5591,45 +5591,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126890193</v>
+        <v>126890110</v>
       </c>
       <c r="B49" t="n">
-        <v>98447</v>
+        <v>98365</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>685111</v>
+        <v>685096</v>
       </c>
       <c r="R49" t="n">
-        <v>7106903</v>
+        <v>7106922</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5664,11 +5664,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ca 150-200 plantor</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -5681,12 +5676,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5700,7 +5695,7 @@
         <v>126890122</v>
       </c>
       <c r="B50" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5798,45 +5793,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126890110</v>
+        <v>126890193</v>
       </c>
       <c r="B51" t="n">
-        <v>98364</v>
+        <v>98448</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>685096</v>
+        <v>685111</v>
       </c>
       <c r="R51" t="n">
-        <v>7106922</v>
+        <v>7106903</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5871,6 +5866,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ca 150-200 plantor</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -5883,12 +5883,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5899,10 +5899,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126893455</v>
+        <v>126891646</v>
       </c>
       <c r="B52" t="n">
-        <v>80121</v>
+        <v>79018</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5910,34 +5910,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>685123</v>
+        <v>685108</v>
       </c>
       <c r="R52" t="n">
-        <v>7106871</v>
+        <v>7106883</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5972,11 +5972,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -5989,12 +5984,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -6005,10 +6000,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126891646</v>
+        <v>126893455</v>
       </c>
       <c r="B53" t="n">
-        <v>79018</v>
+        <v>80121</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6016,34 +6011,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>685108</v>
+        <v>685123</v>
       </c>
       <c r="R53" t="n">
-        <v>7106883</v>
+        <v>7106871</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6078,6 +6073,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6090,12 +6090,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6109,7 +6109,7 @@
         <v>126890115</v>
       </c>
       <c r="B54" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6210,7 +6210,7 @@
         <v>126890116</v>
       </c>
       <c r="B55" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         <v>126893452</v>
       </c>
       <c r="B56" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6419,10 +6419,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126890319</v>
+        <v>126890175</v>
       </c>
       <c r="B57" t="n">
-        <v>80121</v>
+        <v>79018</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6430,34 +6430,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>685113</v>
+        <v>685138</v>
       </c>
       <c r="R57" t="n">
-        <v>7106871</v>
+        <v>7106890</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6492,11 +6492,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>På sälg</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -6509,12 +6504,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6626,10 +6621,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126890175</v>
+        <v>126890319</v>
       </c>
       <c r="B59" t="n">
-        <v>79018</v>
+        <v>80121</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6637,34 +6632,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>685138</v>
+        <v>685113</v>
       </c>
       <c r="R59" t="n">
-        <v>7106890</v>
+        <v>7106871</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6699,6 +6694,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -6711,12 +6711,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -7045,10 +7045,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126893492</v>
+        <v>126890114</v>
       </c>
       <c r="B63" t="n">
-        <v>80121</v>
+        <v>79018</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7056,34 +7056,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>685137</v>
+        <v>685143</v>
       </c>
       <c r="R63" t="n">
-        <v>7106892</v>
+        <v>7106862</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7127,15 +7127,30 @@
       <c r="AG63" t="b">
         <v>0</v>
       </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7146,10 +7161,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126890114</v>
+        <v>126893492</v>
       </c>
       <c r="B64" t="n">
-        <v>79018</v>
+        <v>80121</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7157,34 +7172,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>685143</v>
+        <v>685137</v>
       </c>
       <c r="R64" t="n">
-        <v>7106862</v>
+        <v>7106892</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7228,30 +7243,15 @@
       <c r="AG64" t="b">
         <v>0</v>
       </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">

--- a/artfynd/A 57334-2022 artfynd.xlsx
+++ b/artfynd/A 57334-2022 artfynd.xlsx
@@ -675,49 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126893450</v>
+        <v>126891183</v>
       </c>
       <c r="B2" t="n">
-        <v>98448</v>
+        <v>98365</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>685177</v>
+        <v>685180</v>
       </c>
       <c r="R2" t="n">
-        <v>7106857</v>
+        <v>7106957</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,11 +756,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -770,12 +769,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -786,45 +785,49 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126889625</v>
+        <v>126893450</v>
       </c>
       <c r="B3" t="n">
-        <v>80121</v>
+        <v>98448</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>685134</v>
+        <v>685177</v>
       </c>
       <c r="R3" t="n">
-        <v>7106898</v>
+        <v>7106857</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -859,24 +862,30 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -887,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126889629</v>
+        <v>126890610</v>
       </c>
       <c r="B4" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,34 +907,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>685091</v>
+        <v>685137</v>
       </c>
       <c r="R4" t="n">
-        <v>7106949</v>
+        <v>7106950</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,12 +981,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -988,45 +997,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126890318</v>
+        <v>126890609</v>
       </c>
       <c r="B5" t="n">
-        <v>80150</v>
+        <v>78777</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>685114</v>
+        <v>685141</v>
       </c>
       <c r="R5" t="n">
-        <v>7106864</v>
+        <v>7106811</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,12 +1082,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1089,53 +1098,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126891183</v>
+        <v>126889625</v>
       </c>
       <c r="B6" t="n">
-        <v>98365</v>
+        <v>80121</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>685180</v>
+        <v>685134</v>
       </c>
       <c r="R6" t="n">
-        <v>7106957</v>
+        <v>7106898</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1176,19 +1177,18 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1199,10 +1199,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126890610</v>
+        <v>126889629</v>
       </c>
       <c r="B7" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1210,34 +1210,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>685137</v>
+        <v>685091</v>
       </c>
       <c r="R7" t="n">
-        <v>7106950</v>
+        <v>7106949</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1284,12 +1284,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1300,45 +1300,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126890609</v>
+        <v>126890318</v>
       </c>
       <c r="B8" t="n">
-        <v>78777</v>
+        <v>80150</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>685141</v>
+        <v>685114</v>
       </c>
       <c r="R8" t="n">
-        <v>7106811</v>
+        <v>7106864</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1385,12 +1385,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -3296,7 +3296,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126890121</v>
+        <v>126890151</v>
       </c>
       <c r="B27" t="n">
         <v>79018</v>
@@ -3327,14 +3327,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>685160</v>
+        <v>685110</v>
       </c>
       <c r="R27" t="n">
-        <v>7106836</v>
+        <v>7106911</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3378,30 +3378,15 @@
       <c r="AG27" t="b">
         <v>0</v>
       </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3412,45 +3397,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126890152</v>
+        <v>126893495</v>
       </c>
       <c r="B28" t="n">
-        <v>79018</v>
+        <v>98365</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>685118</v>
+        <v>685133</v>
       </c>
       <c r="R28" t="n">
-        <v>7106922</v>
+        <v>7106886</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3491,18 +3476,19 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3513,7 +3499,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126890151</v>
+        <v>126890121</v>
       </c>
       <c r="B29" t="n">
         <v>79018</v>
@@ -3544,14 +3530,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>685110</v>
+        <v>685160</v>
       </c>
       <c r="R29" t="n">
-        <v>7106911</v>
+        <v>7106836</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3595,15 +3581,30 @@
       <c r="AG29" t="b">
         <v>0</v>
       </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3614,45 +3615,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126893495</v>
+        <v>126890152</v>
       </c>
       <c r="B30" t="n">
-        <v>98365</v>
+        <v>79018</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>685133</v>
+        <v>685118</v>
       </c>
       <c r="R30" t="n">
-        <v>7106886</v>
+        <v>7106922</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3693,19 +3694,18 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -5061,10 +5061,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126890107</v>
+        <v>126890585</v>
       </c>
       <c r="B44" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5072,34 +5072,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>685123</v>
+        <v>685124</v>
       </c>
       <c r="R44" t="n">
-        <v>7106920</v>
+        <v>7106964</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5146,12 +5146,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5162,10 +5162,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126890585</v>
+        <v>126890107</v>
       </c>
       <c r="B45" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5173,34 +5173,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>685124</v>
+        <v>685123</v>
       </c>
       <c r="R45" t="n">
-        <v>7106964</v>
+        <v>7106920</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5247,12 +5247,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5263,7 +5263,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126890123</v>
+        <v>126890150</v>
       </c>
       <c r="B46" t="n">
         <v>79018</v>
@@ -5294,14 +5294,14 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>685169</v>
+        <v>685135</v>
       </c>
       <c r="R46" t="n">
-        <v>7106843</v>
+        <v>7106863</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5345,30 +5345,15 @@
       <c r="AG46" t="b">
         <v>0</v>
       </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5379,49 +5364,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126893456</v>
+        <v>126890110</v>
       </c>
       <c r="B47" t="n">
-        <v>98448</v>
+        <v>98365</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>685136</v>
+        <v>685096</v>
       </c>
       <c r="R47" t="n">
-        <v>7106940</v>
+        <v>7106922</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5456,30 +5437,24 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5490,45 +5465,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126890150</v>
+        <v>126890122</v>
       </c>
       <c r="B48" t="n">
-        <v>79018</v>
+        <v>98448</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>685135</v>
+        <v>685170</v>
       </c>
       <c r="R48" t="n">
-        <v>7106863</v>
+        <v>7106842</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5575,12 +5550,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5591,45 +5566,49 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126890110</v>
+        <v>126893456</v>
       </c>
       <c r="B49" t="n">
-        <v>98365</v>
+        <v>98448</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>685096</v>
+        <v>685136</v>
       </c>
       <c r="R49" t="n">
-        <v>7106922</v>
+        <v>7106940</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5664,24 +5643,30 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5692,7 +5677,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126890122</v>
+        <v>126890193</v>
       </c>
       <c r="B50" t="n">
         <v>98448</v>
@@ -5723,14 +5708,14 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>685170</v>
+        <v>685111</v>
       </c>
       <c r="R50" t="n">
-        <v>7106842</v>
+        <v>7106903</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5765,6 +5750,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ca 150-200 plantor</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -5777,12 +5767,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5793,45 +5783,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126890193</v>
+        <v>126890123</v>
       </c>
       <c r="B51" t="n">
-        <v>98448</v>
+        <v>79018</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>685111</v>
+        <v>685169</v>
       </c>
       <c r="R51" t="n">
-        <v>7106903</v>
+        <v>7106843</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5866,11 +5856,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ca 150-200 plantor</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -5879,16 +5864,31 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -6419,10 +6419,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126890175</v>
+        <v>126890319</v>
       </c>
       <c r="B57" t="n">
-        <v>79018</v>
+        <v>80121</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6430,34 +6430,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>685138</v>
+        <v>685113</v>
       </c>
       <c r="R57" t="n">
-        <v>7106890</v>
+        <v>7106871</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6492,6 +6492,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -6504,12 +6509,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6520,7 +6525,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126890322</v>
+        <v>126890175</v>
       </c>
       <c r="B58" t="n">
         <v>79018</v>
@@ -6551,14 +6556,14 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>685156</v>
+        <v>685138</v>
       </c>
       <c r="R58" t="n">
-        <v>7106959</v>
+        <v>7106890</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6605,12 +6610,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6621,10 +6626,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126890319</v>
+        <v>126890322</v>
       </c>
       <c r="B59" t="n">
-        <v>80121</v>
+        <v>79018</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6632,21 +6637,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6656,10 +6661,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>685113</v>
+        <v>685156</v>
       </c>
       <c r="R59" t="n">
-        <v>7106871</v>
+        <v>7106959</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6692,11 +6697,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6727,10 +6727,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126890118</v>
+        <v>126890105</v>
       </c>
       <c r="B60" t="n">
-        <v>81071</v>
+        <v>79018</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6738,21 +6738,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>229558</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Barkporlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pertusaria sommerfeltii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Flörke ex Sommerf.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6762,10 +6762,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>685153</v>
+        <v>685155</v>
       </c>
       <c r="R60" t="n">
-        <v>7106835</v>
+        <v>7106940</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6808,21 +6808,6 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -6843,7 +6828,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126890105</v>
+        <v>126890106</v>
       </c>
       <c r="B61" t="n">
         <v>79018</v>
@@ -6878,10 +6863,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>685155</v>
+        <v>685144</v>
       </c>
       <c r="R61" t="n">
-        <v>7106940</v>
+        <v>7106929</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6944,10 +6929,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126890106</v>
+        <v>126890118</v>
       </c>
       <c r="B62" t="n">
-        <v>79018</v>
+        <v>81071</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6955,21 +6940,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>229558</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Barkporlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pertusaria sommerfeltii</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flörke ex Sommerf.) Fr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6979,10 +6964,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>685144</v>
+        <v>685153</v>
       </c>
       <c r="R62" t="n">
-        <v>7106929</v>
+        <v>7106835</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7025,6 +7010,21 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -7045,10 +7045,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126890114</v>
+        <v>126893492</v>
       </c>
       <c r="B63" t="n">
-        <v>79018</v>
+        <v>80121</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7056,34 +7056,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>685143</v>
+        <v>685137</v>
       </c>
       <c r="R63" t="n">
-        <v>7106862</v>
+        <v>7106892</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7127,30 +7127,15 @@
       <c r="AG63" t="b">
         <v>0</v>
       </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7161,10 +7146,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126893492</v>
+        <v>126890114</v>
       </c>
       <c r="B64" t="n">
-        <v>80121</v>
+        <v>79018</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7172,34 +7157,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>685137</v>
+        <v>685143</v>
       </c>
       <c r="R64" t="n">
-        <v>7106892</v>
+        <v>7106862</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7243,15 +7228,30 @@
       <c r="AG64" t="b">
         <v>0</v>
       </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">

--- a/artfynd/A 57334-2022 artfynd.xlsx
+++ b/artfynd/A 57334-2022 artfynd.xlsx
@@ -675,53 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126891183</v>
+        <v>126889629</v>
       </c>
       <c r="B2" t="n">
-        <v>98365</v>
+        <v>79020</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>685180</v>
+        <v>685091</v>
       </c>
       <c r="R2" t="n">
-        <v>7106957</v>
+        <v>7106949</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,19 +754,18 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -785,49 +776,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126893450</v>
+        <v>126889625</v>
       </c>
       <c r="B3" t="n">
-        <v>98448</v>
+        <v>80123</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>685177</v>
+        <v>685134</v>
       </c>
       <c r="R3" t="n">
-        <v>7106857</v>
+        <v>7106898</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,30 +849,24 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -896,45 +877,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126890610</v>
+        <v>126893450</v>
       </c>
       <c r="B4" t="n">
-        <v>78777</v>
+        <v>98450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>685137</v>
+        <v>685177</v>
       </c>
       <c r="R4" t="n">
-        <v>7106950</v>
+        <v>7106857</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,24 +954,30 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Carl Jansson, Lotta Ihse, Torbjörn Söderquist, kristina stenmarck, Jennica Andersson, Anne Siivola, Lars-Erik Nilsson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Beke Regelin, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -997,10 +988,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126890609</v>
+        <v>126890610</v>
       </c>
       <c r="B5" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1032,10 +1023,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>685141</v>
+        <v>685137</v>
       </c>
       <c r="R5" t="n">
-        <v>7106811</v>
+        <v>7106950</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,10 +1089,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126889625</v>
+        <v>126890609</v>
       </c>
       <c r="B6" t="n">
-        <v>80121</v>
+        <v>78779</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1109,34 +1100,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>685134</v>
+        <v>685141</v>
       </c>
       <c r="R6" t="n">
-        <v>7106898</v>
+        <v>7106811</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,12 +1174,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1199,45 +1190,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126889629</v>
+        <v>126890318</v>
       </c>
       <c r="B7" t="n">
-        <v>79018</v>
+        <v>80152</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>685091</v>
+        <v>685114</v>
       </c>
       <c r="R7" t="n">
-        <v>7106949</v>
+        <v>7106864</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1284,12 +1275,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1300,10 +1291,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126890318</v>
+        <v>126891183</v>
       </c>
       <c r="B8" t="n">
-        <v>80150</v>
+        <v>98367</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1311,34 +1302,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>219790</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>685114</v>
+        <v>685180</v>
       </c>
       <c r="R8" t="n">
-        <v>7106864</v>
+        <v>7106957</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1379,18 +1378,19 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1401,10 +1401,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126890120</v>
+        <v>126890108</v>
       </c>
       <c r="B9" t="n">
-        <v>80993</v>
+        <v>80123</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1412,21 +1412,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1049</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1436,10 +1436,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>685161</v>
+        <v>685100</v>
       </c>
       <c r="R9" t="n">
-        <v>7106837</v>
+        <v>7106931</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1485,17 +1485,17 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1517,10 +1517,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126890108</v>
+        <v>126890168</v>
       </c>
       <c r="B10" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1548,14 +1548,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>685100</v>
+        <v>685184</v>
       </c>
       <c r="R10" t="n">
-        <v>7106931</v>
+        <v>7106798</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1599,30 +1599,15 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1633,10 +1618,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126890168</v>
+        <v>126890120</v>
       </c>
       <c r="B11" t="n">
-        <v>80121</v>
+        <v>80995</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1644,34 +1629,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>1049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>685184</v>
+        <v>685161</v>
       </c>
       <c r="R11" t="n">
-        <v>7106798</v>
+        <v>7106837</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1715,15 +1700,30 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1737,7 +1737,7 @@
         <v>126891396</v>
       </c>
       <c r="B12" t="n">
-        <v>80122</v>
+        <v>80124</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Beke Regelin, Torbjörn Söderquist, Anne Siivola, Lotta Ihse, Jennica Andersson, Hedda Bring, Eleonor Johansson, Gunilla R Burke, kristina stenmarck, Alexandra Astafourova, Elin Kannerby, Carl Jansson, Lars-Erik Nilsson</t>
+          <t>Lars-Erik Nilsson, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1842,7 +1842,7 @@
         <v>126890596</v>
       </c>
       <c r="B13" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1948,10 +1948,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126890153</v>
+        <v>126890186</v>
       </c>
       <c r="B14" t="n">
-        <v>79018</v>
+        <v>80123</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1959,21 +1959,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1983,10 +1983,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>685129</v>
+        <v>685113</v>
       </c>
       <c r="R14" t="n">
-        <v>7106929</v>
+        <v>7106891</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2019,6 +2019,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2049,10 +2054,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126890186</v>
+        <v>126890112</v>
       </c>
       <c r="B15" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2080,14 +2085,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>685113</v>
+        <v>685116</v>
       </c>
       <c r="R15" t="n">
-        <v>7106891</v>
+        <v>7106932</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2122,11 +2127,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2135,16 +2135,31 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2155,10 +2170,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126890112</v>
+        <v>126890153</v>
       </c>
       <c r="B16" t="n">
-        <v>80121</v>
+        <v>79020</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2166,34 +2181,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>685116</v>
+        <v>685129</v>
       </c>
       <c r="R16" t="n">
-        <v>7106932</v>
+        <v>7106929</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2237,30 +2252,15 @@
       <c r="AG16" t="b">
         <v>0</v>
       </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2274,7 +2274,7 @@
         <v>126889636</v>
       </c>
       <c r="B17" t="n">
-        <v>98365</v>
+        <v>98367</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>126890124</v>
       </c>
       <c r="B18" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>126890160</v>
       </c>
       <c r="B19" t="n">
-        <v>91591</v>
+        <v>91593</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
         <v>126890113</v>
       </c>
       <c r="B20" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
         <v>126890144</v>
       </c>
       <c r="B21" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>126890177</v>
       </c>
       <c r="B22" t="n">
-        <v>98365</v>
+        <v>98367</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2892,10 +2892,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126891639</v>
+        <v>126889628</v>
       </c>
       <c r="B23" t="n">
-        <v>80121</v>
+        <v>79020</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2903,34 +2903,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>685148</v>
+        <v>685180</v>
       </c>
       <c r="R23" t="n">
-        <v>7106890</v>
+        <v>7106844</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2977,12 +2977,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -2993,10 +2993,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126889628</v>
+        <v>126891171</v>
       </c>
       <c r="B24" t="n">
-        <v>79018</v>
+        <v>57823</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3004,34 +3004,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>685180</v>
+        <v>685135</v>
       </c>
       <c r="R24" t="n">
-        <v>7106844</v>
+        <v>7106966</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3078,12 +3078,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3094,10 +3094,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126890601</v>
+        <v>126891639</v>
       </c>
       <c r="B25" t="n">
-        <v>57661</v>
+        <v>80123</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3105,34 +3105,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>685168</v>
+        <v>685148</v>
       </c>
       <c r="R25" t="n">
-        <v>7106800</v>
+        <v>7106890</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3179,12 +3179,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3195,10 +3195,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126891171</v>
+        <v>126890601</v>
       </c>
       <c r="B26" t="n">
-        <v>57821</v>
+        <v>57663</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3206,34 +3206,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>685135</v>
+        <v>685168</v>
       </c>
       <c r="R26" t="n">
-        <v>7106966</v>
+        <v>7106800</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3280,12 +3280,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3296,45 +3296,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126890151</v>
+        <v>126893495</v>
       </c>
       <c r="B27" t="n">
-        <v>79018</v>
+        <v>98367</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>685110</v>
+        <v>685133</v>
       </c>
       <c r="R27" t="n">
-        <v>7106911</v>
+        <v>7106886</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3375,18 +3375,19 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3397,45 +3398,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126893495</v>
+        <v>126890152</v>
       </c>
       <c r="B28" t="n">
-        <v>98365</v>
+        <v>79020</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>685133</v>
+        <v>685118</v>
       </c>
       <c r="R28" t="n">
-        <v>7106886</v>
+        <v>7106922</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3476,19 +3477,18 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3499,10 +3499,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126890121</v>
+        <v>126890151</v>
       </c>
       <c r="B29" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3530,14 +3530,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>685160</v>
+        <v>685110</v>
       </c>
       <c r="R29" t="n">
-        <v>7106836</v>
+        <v>7106911</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3581,30 +3581,15 @@
       <c r="AG29" t="b">
         <v>0</v>
       </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3615,10 +3600,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126890152</v>
+        <v>126890121</v>
       </c>
       <c r="B30" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3646,14 +3631,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>685118</v>
+        <v>685160</v>
       </c>
       <c r="R30" t="n">
-        <v>7106922</v>
+        <v>7106836</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3697,15 +3682,30 @@
       <c r="AG30" t="b">
         <v>0</v>
       </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3719,7 +3719,7 @@
         <v>126889624</v>
       </c>
       <c r="B31" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         <v>126893453</v>
       </c>
       <c r="B32" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3917,7 +3917,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Alexandra Astafourova, Carl Jansson, Lotta Ihse, Torbjörn Söderquist, kristina stenmarck, Jennica Andersson, Anne Siivola, Lars-Erik Nilsson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Beke Regelin, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3931,7 +3931,7 @@
         <v>126890119</v>
       </c>
       <c r="B33" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4032,7 +4032,7 @@
         <v>126890198</v>
       </c>
       <c r="B34" t="n">
-        <v>91591</v>
+        <v>91593</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>126890183</v>
       </c>
       <c r="B35" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>126889623</v>
       </c>
       <c r="B36" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4357,7 +4357,7 @@
         <v>126891641</v>
       </c>
       <c r="B37" t="n">
-        <v>78776</v>
+        <v>78778</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>126890167</v>
       </c>
       <c r="B38" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4556,10 +4556,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126890195</v>
+        <v>126890626</v>
       </c>
       <c r="B39" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4587,14 +4587,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>685114</v>
+        <v>685132</v>
       </c>
       <c r="R39" t="n">
-        <v>7106926</v>
+        <v>7106962</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4641,12 +4641,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4657,10 +4657,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126890321</v>
+        <v>126890195</v>
       </c>
       <c r="B40" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4688,14 +4688,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>685165</v>
+        <v>685114</v>
       </c>
       <c r="R40" t="n">
-        <v>7106856</v>
+        <v>7106926</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4742,12 +4742,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4758,10 +4758,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126890626</v>
+        <v>126890321</v>
       </c>
       <c r="B41" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4789,14 +4789,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>685132</v>
+        <v>685165</v>
       </c>
       <c r="R41" t="n">
-        <v>7106962</v>
+        <v>7106856</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4843,12 +4843,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -4862,7 +4862,7 @@
         <v>126890199</v>
       </c>
       <c r="B42" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
         <v>126890187</v>
       </c>
       <c r="B43" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5061,10 +5061,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126890585</v>
+        <v>126890107</v>
       </c>
       <c r="B44" t="n">
-        <v>79636</v>
+        <v>79020</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5072,34 +5072,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>685124</v>
+        <v>685123</v>
       </c>
       <c r="R44" t="n">
-        <v>7106964</v>
+        <v>7106920</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5146,12 +5146,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5162,10 +5162,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126890107</v>
+        <v>126890585</v>
       </c>
       <c r="B45" t="n">
-        <v>79018</v>
+        <v>79638</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5173,34 +5173,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>685123</v>
+        <v>685124</v>
       </c>
       <c r="R45" t="n">
-        <v>7106920</v>
+        <v>7106964</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5247,12 +5247,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5263,45 +5263,49 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126890150</v>
+        <v>126893456</v>
       </c>
       <c r="B46" t="n">
-        <v>79018</v>
+        <v>98450</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>685135</v>
+        <v>685136</v>
       </c>
       <c r="R46" t="n">
-        <v>7106863</v>
+        <v>7106940</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5336,12 +5340,18 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5353,7 +5363,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Carl Jansson, Lotta Ihse, Torbjörn Söderquist, kristina stenmarck, Jennica Andersson, Anne Siivola, Lars-Erik Nilsson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Beke Regelin, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5364,45 +5374,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126890110</v>
+        <v>126890193</v>
       </c>
       <c r="B47" t="n">
-        <v>98365</v>
+        <v>98450</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>685096</v>
+        <v>685111</v>
       </c>
       <c r="R47" t="n">
-        <v>7106922</v>
+        <v>7106903</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5437,6 +5447,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ca 150-200 plantor</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5449,12 +5464,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5468,7 +5483,7 @@
         <v>126890122</v>
       </c>
       <c r="B48" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5566,49 +5581,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126893456</v>
+        <v>126890123</v>
       </c>
       <c r="B49" t="n">
-        <v>98448</v>
+        <v>79020</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>685136</v>
+        <v>685169</v>
       </c>
       <c r="R49" t="n">
-        <v>7106940</v>
+        <v>7106843</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5643,30 +5654,39 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5677,32 +5697,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126890193</v>
+        <v>126890150</v>
       </c>
       <c r="B50" t="n">
-        <v>98448</v>
+        <v>79020</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5712,10 +5732,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>685111</v>
+        <v>685135</v>
       </c>
       <c r="R50" t="n">
-        <v>7106903</v>
+        <v>7106863</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5748,11 +5768,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ca 150-200 plantor</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5783,32 +5798,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126890123</v>
+        <v>126890110</v>
       </c>
       <c r="B51" t="n">
-        <v>79018</v>
+        <v>98367</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5818,10 +5833,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>685169</v>
+        <v>685096</v>
       </c>
       <c r="R51" t="n">
-        <v>7106843</v>
+        <v>7106922</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5864,21 +5879,6 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -5902,7 +5902,7 @@
         <v>126891646</v>
       </c>
       <c r="B52" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6003,7 +6003,7 @@
         <v>126893455</v>
       </c>
       <c r="B53" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6095,7 +6095,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Alexandra Astafourova, Carl Jansson, Lotta Ihse, Torbjörn Söderquist, kristina stenmarck, Jennica Andersson, Anne Siivola, Lars-Erik Nilsson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Beke Regelin, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6109,7 +6109,7 @@
         <v>126890115</v>
       </c>
       <c r="B54" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6210,7 +6210,7 @@
         <v>126890116</v>
       </c>
       <c r="B55" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         <v>126893452</v>
       </c>
       <c r="B56" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6408,7 +6408,7 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Alexandra Astafourova, Carl Jansson, Lotta Ihse, Torbjörn Söderquist, kristina stenmarck, Jennica Andersson, Anne Siivola, Lars-Erik Nilsson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Beke Regelin, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6419,10 +6419,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126890319</v>
+        <v>126890322</v>
       </c>
       <c r="B57" t="n">
-        <v>80121</v>
+        <v>79020</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6430,21 +6430,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6454,10 +6454,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>685113</v>
+        <v>685156</v>
       </c>
       <c r="R57" t="n">
-        <v>7106871</v>
+        <v>7106959</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6490,11 +6490,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6525,10 +6520,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126890175</v>
+        <v>126890319</v>
       </c>
       <c r="B58" t="n">
-        <v>79018</v>
+        <v>80123</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6536,34 +6531,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>685138</v>
+        <v>685113</v>
       </c>
       <c r="R58" t="n">
-        <v>7106890</v>
+        <v>7106871</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6598,6 +6593,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -6610,12 +6610,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6626,10 +6626,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126890322</v>
+        <v>126890175</v>
       </c>
       <c r="B59" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6657,14 +6657,14 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>685156</v>
+        <v>685138</v>
       </c>
       <c r="R59" t="n">
-        <v>7106959</v>
+        <v>7106890</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6711,12 +6711,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6727,10 +6727,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126890105</v>
+        <v>126890106</v>
       </c>
       <c r="B60" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6762,10 +6762,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>685155</v>
+        <v>685144</v>
       </c>
       <c r="R60" t="n">
-        <v>7106940</v>
+        <v>7106929</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6828,10 +6828,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126890106</v>
+        <v>126890105</v>
       </c>
       <c r="B61" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6863,10 +6863,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>685144</v>
+        <v>685155</v>
       </c>
       <c r="R61" t="n">
-        <v>7106929</v>
+        <v>7106940</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6932,7 +6932,7 @@
         <v>126890118</v>
       </c>
       <c r="B62" t="n">
-        <v>81071</v>
+        <v>81073</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7045,10 +7045,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126893492</v>
+        <v>126890114</v>
       </c>
       <c r="B63" t="n">
-        <v>80121</v>
+        <v>79020</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7056,34 +7056,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>685137</v>
+        <v>685143</v>
       </c>
       <c r="R63" t="n">
-        <v>7106892</v>
+        <v>7106862</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7127,15 +7127,30 @@
       <c r="AG63" t="b">
         <v>0</v>
       </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7146,10 +7161,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126890114</v>
+        <v>126893492</v>
       </c>
       <c r="B64" t="n">
-        <v>79018</v>
+        <v>80123</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7157,34 +7172,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>685143</v>
+        <v>685137</v>
       </c>
       <c r="R64" t="n">
-        <v>7106862</v>
+        <v>7106892</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7228,30 +7243,15 @@
       <c r="AG64" t="b">
         <v>0</v>
       </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">

--- a/artfynd/A 57334-2022 artfynd.xlsx
+++ b/artfynd/A 57334-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126889629</v>
+        <v>126889625</v>
       </c>
       <c r="B2" t="n">
-        <v>79020</v>
+        <v>80114</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>685091</v>
+        <v>685134</v>
       </c>
       <c r="R2" t="n">
-        <v>7106949</v>
+        <v>7106898</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,45 +776,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126889625</v>
+        <v>126890318</v>
       </c>
       <c r="B3" t="n">
-        <v>80123</v>
+        <v>80143</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>685134</v>
+        <v>685114</v>
       </c>
       <c r="R3" t="n">
-        <v>7106898</v>
+        <v>7106864</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,12 +861,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Torbjörn Söderquist, Anne Siivola, Lotta Ihse, Jennica Andersson, Hedda Bring, Eleonor Johansson, Gunilla R Burke, kristina stenmarck, Alexandra Astafourova, Elin Kannerby, Lars-Erik Nilsson, Carl Jansson, Beke Regelin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -877,49 +877,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126893450</v>
+        <v>126890609</v>
       </c>
       <c r="B4" t="n">
-        <v>98450</v>
+        <v>78770</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>685177</v>
+        <v>685141</v>
       </c>
       <c r="R4" t="n">
-        <v>7106857</v>
+        <v>7106811</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,30 +950,24 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Carl Jansson, Lotta Ihse, Torbjörn Söderquist, kristina stenmarck, Jennica Andersson, Anne Siivola, Lars-Erik Nilsson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Beke Regelin, Eleonor Johansson</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -988,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126890610</v>
+        <v>126889629</v>
       </c>
       <c r="B5" t="n">
-        <v>78779</v>
+        <v>79011</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -999,34 +989,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>685137</v>
+        <v>685091</v>
       </c>
       <c r="R5" t="n">
-        <v>7106950</v>
+        <v>7106949</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,12 +1063,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1089,45 +1079,53 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126890609</v>
+        <v>126891183</v>
       </c>
       <c r="B6" t="n">
-        <v>78779</v>
+        <v>98353</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>685141</v>
+        <v>685180</v>
       </c>
       <c r="R6" t="n">
-        <v>7106811</v>
+        <v>7106957</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,18 +1166,19 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1190,45 +1189,49 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126890318</v>
+        <v>126893450</v>
       </c>
       <c r="B7" t="n">
-        <v>80152</v>
+        <v>98436</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>685114</v>
+        <v>685177</v>
       </c>
       <c r="R7" t="n">
-        <v>7106864</v>
+        <v>7106857</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1263,24 +1266,30 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1291,53 +1300,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126891183</v>
+        <v>126890610</v>
       </c>
       <c r="B8" t="n">
-        <v>98367</v>
+        <v>78770</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219790</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>685180</v>
+        <v>685137</v>
       </c>
       <c r="R8" t="n">
-        <v>7106957</v>
+        <v>7106950</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1378,19 +1379,18 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1404,7 +1404,7 @@
         <v>126890108</v>
       </c>
       <c r="B9" t="n">
-        <v>80123</v>
+        <v>80114</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1517,10 +1517,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126890168</v>
+        <v>126890120</v>
       </c>
       <c r="B10" t="n">
-        <v>80123</v>
+        <v>80986</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1528,34 +1528,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>1049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>685184</v>
+        <v>685161</v>
       </c>
       <c r="R10" t="n">
-        <v>7106798</v>
+        <v>7106837</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1599,15 +1599,30 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1618,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126890120</v>
+        <v>126890168</v>
       </c>
       <c r="B11" t="n">
-        <v>80995</v>
+        <v>80114</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1629,34 +1644,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1049</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>685161</v>
+        <v>685184</v>
       </c>
       <c r="R11" t="n">
-        <v>7106837</v>
+        <v>7106798</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1700,30 +1715,15 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1737,7 +1737,7 @@
         <v>126891396</v>
       </c>
       <c r="B12" t="n">
-        <v>80124</v>
+        <v>80115</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>126890596</v>
       </c>
       <c r="B13" t="n">
-        <v>57823</v>
+        <v>57817</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1948,10 +1948,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126890186</v>
+        <v>126890153</v>
       </c>
       <c r="B14" t="n">
-        <v>80123</v>
+        <v>79011</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1959,21 +1959,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1983,10 +1983,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>685113</v>
+        <v>685129</v>
       </c>
       <c r="R14" t="n">
-        <v>7106891</v>
+        <v>7106929</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2019,11 +2019,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Sälg</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2054,10 +2049,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126890112</v>
+        <v>126890186</v>
       </c>
       <c r="B15" t="n">
-        <v>80123</v>
+        <v>80114</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2085,14 +2080,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>685116</v>
+        <v>685113</v>
       </c>
       <c r="R15" t="n">
-        <v>7106932</v>
+        <v>7106891</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2127,6 +2122,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2135,31 +2135,16 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2170,10 +2155,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126890153</v>
+        <v>126890112</v>
       </c>
       <c r="B16" t="n">
-        <v>79020</v>
+        <v>80114</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2181,34 +2166,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>685129</v>
+        <v>685116</v>
       </c>
       <c r="R16" t="n">
-        <v>7106929</v>
+        <v>7106932</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2252,15 +2237,30 @@
       <c r="AG16" t="b">
         <v>0</v>
       </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2274,7 +2274,7 @@
         <v>126889636</v>
       </c>
       <c r="B17" t="n">
-        <v>98367</v>
+        <v>98353</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>126890124</v>
       </c>
       <c r="B18" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>126890160</v>
       </c>
       <c r="B19" t="n">
-        <v>91593</v>
+        <v>91580</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
         <v>126890113</v>
       </c>
       <c r="B20" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
         <v>126890144</v>
       </c>
       <c r="B21" t="n">
-        <v>80123</v>
+        <v>80114</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>126890177</v>
       </c>
       <c r="B22" t="n">
-        <v>98367</v>
+        <v>98353</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>126889628</v>
       </c>
       <c r="B23" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2993,10 +2993,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126891171</v>
+        <v>126891639</v>
       </c>
       <c r="B24" t="n">
-        <v>57823</v>
+        <v>80114</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3004,21 +3004,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3028,10 +3028,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>685135</v>
+        <v>685148</v>
       </c>
       <c r="R24" t="n">
-        <v>7106966</v>
+        <v>7106890</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3078,12 +3078,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3094,10 +3094,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126891639</v>
+        <v>126890601</v>
       </c>
       <c r="B25" t="n">
-        <v>80123</v>
+        <v>57657</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3105,34 +3105,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>685148</v>
+        <v>685168</v>
       </c>
       <c r="R25" t="n">
-        <v>7106890</v>
+        <v>7106800</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3179,12 +3179,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3195,10 +3195,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126890601</v>
+        <v>126891171</v>
       </c>
       <c r="B26" t="n">
-        <v>57663</v>
+        <v>57817</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3206,34 +3206,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>685168</v>
+        <v>685135</v>
       </c>
       <c r="R26" t="n">
-        <v>7106800</v>
+        <v>7106966</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3280,12 +3280,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3299,7 +3299,7 @@
         <v>126893495</v>
       </c>
       <c r="B27" t="n">
-        <v>98367</v>
+        <v>98353</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3398,10 +3398,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126890152</v>
+        <v>126890121</v>
       </c>
       <c r="B28" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3429,14 +3429,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>685118</v>
+        <v>685160</v>
       </c>
       <c r="R28" t="n">
-        <v>7106922</v>
+        <v>7106836</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3480,15 +3480,30 @@
       <c r="AG28" t="b">
         <v>0</v>
       </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3502,7 +3517,7 @@
         <v>126890151</v>
       </c>
       <c r="B29" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3600,10 +3615,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126890121</v>
+        <v>126890152</v>
       </c>
       <c r="B30" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3631,14 +3646,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>685160</v>
+        <v>685118</v>
       </c>
       <c r="R30" t="n">
-        <v>7106836</v>
+        <v>7106922</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3682,30 +3697,15 @@
       <c r="AG30" t="b">
         <v>0</v>
       </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3716,45 +3716,49 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126889624</v>
+        <v>126893453</v>
       </c>
       <c r="B31" t="n">
-        <v>80123</v>
+        <v>98436</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>685145</v>
+        <v>685142</v>
       </c>
       <c r="R31" t="n">
-        <v>7106886</v>
+        <v>7106872</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3789,24 +3793,30 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3817,10 +3827,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126893453</v>
+        <v>126890119</v>
       </c>
       <c r="B32" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3845,21 +3855,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>685142</v>
+        <v>685161</v>
       </c>
       <c r="R32" t="n">
-        <v>7106872</v>
+        <v>7106834</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3894,30 +3900,24 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Carl Jansson, Lotta Ihse, Torbjörn Söderquist, kristina stenmarck, Jennica Andersson, Anne Siivola, Lars-Erik Nilsson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Beke Regelin, Eleonor Johansson</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3928,45 +3928,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126890119</v>
+        <v>126889624</v>
       </c>
       <c r="B33" t="n">
-        <v>98450</v>
+        <v>80114</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>685161</v>
+        <v>685145</v>
       </c>
       <c r="R33" t="n">
-        <v>7106834</v>
+        <v>7106886</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4013,12 +4013,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4032,7 +4032,7 @@
         <v>126890198</v>
       </c>
       <c r="B34" t="n">
-        <v>91593</v>
+        <v>91580</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4135,10 +4135,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126890183</v>
+        <v>126889623</v>
       </c>
       <c r="B35" t="n">
-        <v>57660</v>
+        <v>80114</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4146,46 +4146,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>685138</v>
+        <v>685088</v>
       </c>
       <c r="R35" t="n">
-        <v>7106859</v>
+        <v>7106936</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4220,11 +4208,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Hackhål</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4237,12 +4220,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4253,10 +4236,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126889623</v>
+        <v>126890183</v>
       </c>
       <c r="B36" t="n">
-        <v>80123</v>
+        <v>57654</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4264,34 +4247,46 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>685088</v>
+        <v>685138</v>
       </c>
       <c r="R36" t="n">
-        <v>7106936</v>
+        <v>7106859</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4326,6 +4321,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Hackhål</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4338,12 +4338,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4354,10 +4354,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126891641</v>
+        <v>126890167</v>
       </c>
       <c r="B37" t="n">
-        <v>78778</v>
+        <v>80114</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4365,34 +4365,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>685169</v>
+        <v>685168</v>
       </c>
       <c r="R37" t="n">
-        <v>7106940</v>
+        <v>7106810</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4439,12 +4439,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4455,10 +4455,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126890167</v>
+        <v>126891641</v>
       </c>
       <c r="B38" t="n">
-        <v>80123</v>
+        <v>78769</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4466,34 +4466,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>685168</v>
+        <v>685169</v>
       </c>
       <c r="R38" t="n">
-        <v>7106810</v>
+        <v>7106940</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4540,12 +4540,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4556,10 +4556,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126890626</v>
+        <v>126890195</v>
       </c>
       <c r="B39" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4587,14 +4587,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>685132</v>
+        <v>685114</v>
       </c>
       <c r="R39" t="n">
-        <v>7106962</v>
+        <v>7106926</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4641,12 +4641,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4657,10 +4657,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126890195</v>
+        <v>126890321</v>
       </c>
       <c r="B40" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4688,14 +4688,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>685114</v>
+        <v>685165</v>
       </c>
       <c r="R40" t="n">
-        <v>7106926</v>
+        <v>7106856</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4742,12 +4742,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Torbjörn Söderquist, Anne Siivola, Lotta Ihse, Jennica Andersson, Hedda Bring, Eleonor Johansson, Gunilla R Burke, kristina stenmarck, Alexandra Astafourova, Elin Kannerby, Lars-Erik Nilsson, Carl Jansson, Beke Regelin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4758,10 +4758,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126890321</v>
+        <v>126890626</v>
       </c>
       <c r="B41" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4789,14 +4789,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>685165</v>
+        <v>685132</v>
       </c>
       <c r="R41" t="n">
-        <v>7106856</v>
+        <v>7106962</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4843,12 +4843,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -4859,32 +4859,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126890199</v>
+        <v>126890187</v>
       </c>
       <c r="B42" t="n">
-        <v>92622</v>
+        <v>80114</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4894,10 +4894,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>685175</v>
+        <v>685113</v>
       </c>
       <c r="R42" t="n">
-        <v>7106946</v>
+        <v>7106903</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4960,32 +4960,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126890187</v>
+        <v>126890199</v>
       </c>
       <c r="B43" t="n">
-        <v>80123</v>
+        <v>92609</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4995,10 +4995,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>685113</v>
+        <v>685175</v>
       </c>
       <c r="R43" t="n">
-        <v>7106903</v>
+        <v>7106946</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5064,7 +5064,7 @@
         <v>126890107</v>
       </c>
       <c r="B44" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5165,7 +5165,7 @@
         <v>126890585</v>
       </c>
       <c r="B45" t="n">
-        <v>79638</v>
+        <v>79629</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5263,49 +5263,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126893456</v>
+        <v>126890150</v>
       </c>
       <c r="B46" t="n">
-        <v>98450</v>
+        <v>79011</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>685136</v>
+        <v>685135</v>
       </c>
       <c r="R46" t="n">
-        <v>7106940</v>
+        <v>7106863</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5340,18 +5336,12 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5363,7 +5353,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Carl Jansson, Lotta Ihse, Torbjörn Söderquist, kristina stenmarck, Jennica Andersson, Anne Siivola, Lars-Erik Nilsson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Beke Regelin, Eleonor Johansson</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5374,45 +5364,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126890193</v>
+        <v>126890123</v>
       </c>
       <c r="B47" t="n">
-        <v>98450</v>
+        <v>79011</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>685111</v>
+        <v>685169</v>
       </c>
       <c r="R47" t="n">
-        <v>7106903</v>
+        <v>7106843</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5447,11 +5437,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ca 150-200 plantor</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5460,16 +5445,31 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5480,32 +5480,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126890122</v>
+        <v>126890110</v>
       </c>
       <c r="B48" t="n">
-        <v>98450</v>
+        <v>98353</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5515,10 +5515,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>685170</v>
+        <v>685096</v>
       </c>
       <c r="R48" t="n">
-        <v>7106842</v>
+        <v>7106922</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5581,45 +5581,49 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126890123</v>
+        <v>126893456</v>
       </c>
       <c r="B49" t="n">
-        <v>79020</v>
+        <v>98436</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>685169</v>
+        <v>685136</v>
       </c>
       <c r="R49" t="n">
-        <v>7106843</v>
+        <v>7106940</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5654,39 +5658,30 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5697,32 +5692,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126890150</v>
+        <v>126890193</v>
       </c>
       <c r="B50" t="n">
-        <v>79020</v>
+        <v>98436</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5732,10 +5727,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>685135</v>
+        <v>685111</v>
       </c>
       <c r="R50" t="n">
-        <v>7106863</v>
+        <v>7106903</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5768,6 +5763,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ca 150-200 plantor</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5798,32 +5798,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126890110</v>
+        <v>126890122</v>
       </c>
       <c r="B51" t="n">
-        <v>98367</v>
+        <v>98436</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5833,10 +5833,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>685096</v>
+        <v>685170</v>
       </c>
       <c r="R51" t="n">
-        <v>7106922</v>
+        <v>7106842</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5899,10 +5899,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126891646</v>
+        <v>126893455</v>
       </c>
       <c r="B52" t="n">
-        <v>79020</v>
+        <v>80114</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5910,34 +5910,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>685108</v>
+        <v>685123</v>
       </c>
       <c r="R52" t="n">
-        <v>7106883</v>
+        <v>7106871</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5972,6 +5972,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -5984,12 +5989,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -6000,10 +6005,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126893455</v>
+        <v>126891646</v>
       </c>
       <c r="B53" t="n">
-        <v>80123</v>
+        <v>79011</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6011,34 +6016,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>685123</v>
+        <v>685108</v>
       </c>
       <c r="R53" t="n">
-        <v>7106871</v>
+        <v>7106883</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6073,11 +6078,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6090,12 +6090,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Carl Jansson, Lotta Ihse, Torbjörn Söderquist, kristina stenmarck, Jennica Andersson, Anne Siivola, Lars-Erik Nilsson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Beke Regelin, Eleonor Johansson</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6106,10 +6106,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126890115</v>
+        <v>126893452</v>
       </c>
       <c r="B54" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6134,17 +6134,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
         <v>685145</v>
       </c>
       <c r="R54" t="n">
-        <v>7106855</v>
+        <v>7106823</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6179,24 +6183,30 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6207,10 +6217,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126890116</v>
+        <v>126890115</v>
       </c>
       <c r="B55" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6242,10 +6252,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>685140</v>
+        <v>685145</v>
       </c>
       <c r="R55" t="n">
-        <v>7106846</v>
+        <v>7106855</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6308,10 +6318,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126893452</v>
+        <v>126890116</v>
       </c>
       <c r="B56" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6336,21 +6346,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>685145</v>
+        <v>685140</v>
       </c>
       <c r="R56" t="n">
-        <v>7106823</v>
+        <v>7106846</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6385,30 +6391,24 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Carl Jansson, Lotta Ihse, Torbjörn Söderquist, kristina stenmarck, Jennica Andersson, Anne Siivola, Lars-Erik Nilsson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Beke Regelin, Eleonor Johansson</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6419,10 +6419,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126890322</v>
+        <v>126890175</v>
       </c>
       <c r="B57" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6450,14 +6450,14 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>685156</v>
+        <v>685138</v>
       </c>
       <c r="R57" t="n">
-        <v>7106959</v>
+        <v>7106890</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6504,12 +6504,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6520,10 +6520,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126890319</v>
+        <v>126890322</v>
       </c>
       <c r="B58" t="n">
-        <v>80123</v>
+        <v>79011</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6531,21 +6531,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6555,10 +6555,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>685113</v>
+        <v>685156</v>
       </c>
       <c r="R58" t="n">
-        <v>7106871</v>
+        <v>7106959</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6593,11 +6593,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>På sälg</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -6615,7 +6610,7 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Torbjörn Söderquist, Anne Siivola, Lotta Ihse, Jennica Andersson, Hedda Bring, Eleonor Johansson, Gunilla R Burke, kristina stenmarck, Alexandra Astafourova, Elin Kannerby, Lars-Erik Nilsson, Carl Jansson, Beke Regelin</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6626,10 +6621,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126890175</v>
+        <v>126890319</v>
       </c>
       <c r="B59" t="n">
-        <v>79020</v>
+        <v>80114</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6637,34 +6632,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>685138</v>
+        <v>685113</v>
       </c>
       <c r="R59" t="n">
-        <v>7106890</v>
+        <v>7106871</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6699,6 +6694,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -6711,12 +6711,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Torbjörn Söderquist, Anne Siivola, Lotta Ihse, Jennica Andersson, Hedda Bring, Eleonor Johansson, Gunilla R Burke, kristina stenmarck, Alexandra Astafourova, Elin Kannerby, Lars-Erik Nilsson, Carl Jansson, Beke Regelin</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6730,7 +6730,7 @@
         <v>126890106</v>
       </c>
       <c r="B60" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
         <v>126890105</v>
       </c>
       <c r="B61" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6932,7 +6932,7 @@
         <v>126890118</v>
       </c>
       <c r="B62" t="n">
-        <v>81073</v>
+        <v>81064</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7048,7 +7048,7 @@
         <v>126890114</v>
       </c>
       <c r="B63" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7164,7 +7164,7 @@
         <v>126893492</v>
       </c>
       <c r="B64" t="n">
-        <v>80123</v>
+        <v>80114</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 57334-2022 artfynd.xlsx
+++ b/artfynd/A 57334-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY64"/>
+  <dimension ref="A1:AY70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,45 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126889629</v>
+        <v>126890160</v>
       </c>
       <c r="B2" t="n">
-        <v>79020</v>
+        <v>92183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>685091</v>
+        <v>685113</v>
       </c>
       <c r="R2" t="n">
-        <v>7106949</v>
+        <v>7106928</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,12 +760,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -776,45 +776,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126889625</v>
+        <v>126890198</v>
       </c>
       <c r="B3" t="n">
-        <v>80123</v>
+        <v>92183</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>65</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>685134</v>
+        <v>685118</v>
       </c>
       <c r="R3" t="n">
-        <v>7106898</v>
+        <v>7106927</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -849,6 +849,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Tallåga</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -861,12 +866,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -877,49 +882,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126893450</v>
+        <v>126890120</v>
       </c>
       <c r="B4" t="n">
-        <v>98450</v>
+        <v>81312</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>685177</v>
+        <v>685161</v>
       </c>
       <c r="R4" t="n">
-        <v>7106857</v>
+        <v>7106837</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,30 +955,39 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Carl Jansson, Lotta Ihse, Torbjörn Söderquist, kristina stenmarck, Jennica Andersson, Anne Siivola, Lars-Erik Nilsson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Beke Regelin, Eleonor Johansson</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -988,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126890610</v>
+        <v>126891396</v>
       </c>
       <c r="B5" t="n">
-        <v>78779</v>
+        <v>80433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -999,34 +1009,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>685137</v>
+        <v>685147</v>
       </c>
       <c r="R5" t="n">
-        <v>7106950</v>
+        <v>7106885</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,18 +1080,19 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Lars-Erik Nilsson, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1089,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126890609</v>
+        <v>126890199</v>
       </c>
       <c r="B6" t="n">
-        <v>78779</v>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1100,34 +1114,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>685141</v>
+        <v>685175</v>
       </c>
       <c r="R6" t="n">
-        <v>7106811</v>
+        <v>7106946</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,12 +1188,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1190,45 +1204,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126890318</v>
+        <v>126889628</v>
       </c>
       <c r="B7" t="n">
-        <v>80152</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>685114</v>
+        <v>685180</v>
       </c>
       <c r="R7" t="n">
-        <v>7106864</v>
+        <v>7106844</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,12 +1289,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1291,53 +1305,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126891183</v>
+        <v>126889629</v>
       </c>
       <c r="B8" t="n">
-        <v>98367</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>685180</v>
+        <v>685091</v>
       </c>
       <c r="R8" t="n">
-        <v>7106957</v>
+        <v>7106949</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1378,19 +1384,18 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1401,32 +1406,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126890108</v>
+        <v>126890105</v>
       </c>
       <c r="B9" t="n">
-        <v>80123</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1436,10 +1441,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>685100</v>
+        <v>685155</v>
       </c>
       <c r="R9" t="n">
-        <v>7106931</v>
+        <v>7106940</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1482,21 +1487,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1517,45 +1507,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126890168</v>
+        <v>126890106</v>
       </c>
       <c r="B10" t="n">
-        <v>80123</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>685184</v>
+        <v>685144</v>
       </c>
       <c r="R10" t="n">
-        <v>7106798</v>
+        <v>7106929</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1602,12 +1592,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1618,32 +1608,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126890120</v>
+        <v>126890107</v>
       </c>
       <c r="B11" t="n">
-        <v>80995</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1653,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>685161</v>
+        <v>685123</v>
       </c>
       <c r="R11" t="n">
-        <v>7106837</v>
+        <v>7106920</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1699,21 +1689,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1734,48 +1709,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126891396</v>
+        <v>126890113</v>
       </c>
       <c r="B12" t="n">
-        <v>80124</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>685147</v>
+        <v>685107</v>
       </c>
       <c r="R12" t="n">
-        <v>7106885</v>
+        <v>7106875</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1816,19 +1788,33 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1839,53 +1825,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126890596</v>
+        <v>126890114</v>
       </c>
       <c r="B13" t="n">
-        <v>57823</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>685137</v>
+        <v>685143</v>
       </c>
       <c r="R13" t="n">
-        <v>7106950</v>
+        <v>7106862</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1929,15 +1907,30 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1948,45 +1941,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126890186</v>
+        <v>126890121</v>
       </c>
       <c r="B14" t="n">
-        <v>80123</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>685113</v>
+        <v>685160</v>
       </c>
       <c r="R14" t="n">
-        <v>7106891</v>
+        <v>7106836</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2021,11 +2014,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2034,16 +2022,31 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2054,32 +2057,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126890112</v>
+        <v>126890123</v>
       </c>
       <c r="B15" t="n">
-        <v>80123</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2089,10 +2092,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>685116</v>
+        <v>685169</v>
       </c>
       <c r="R15" t="n">
-        <v>7106932</v>
+        <v>7106843</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2138,17 +2141,17 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2170,14 +2173,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126890153</v>
+        <v>126890150</v>
       </c>
       <c r="B16" t="n">
-        <v>79020</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2205,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>685129</v>
+        <v>685135</v>
       </c>
       <c r="R16" t="n">
-        <v>7106929</v>
+        <v>7106863</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2271,45 +2274,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126889636</v>
+        <v>126890151</v>
       </c>
       <c r="B17" t="n">
-        <v>98367</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>685270</v>
+        <v>685110</v>
       </c>
       <c r="R17" t="n">
-        <v>7106941</v>
+        <v>7106911</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2356,12 +2359,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2372,10 +2375,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126890124</v>
+        <v>126890152</v>
       </c>
       <c r="B18" t="n">
-        <v>98450</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2383,34 +2386,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>685176</v>
+        <v>685118</v>
       </c>
       <c r="R18" t="n">
-        <v>7106857</v>
+        <v>7106922</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2457,12 +2460,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2473,10 +2476,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126890160</v>
+        <v>126890153</v>
       </c>
       <c r="B19" t="n">
-        <v>91593</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2484,21 +2487,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2508,10 +2511,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>685113</v>
+        <v>685129</v>
       </c>
       <c r="R19" t="n">
-        <v>7106928</v>
+        <v>7106929</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2574,14 +2577,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126890113</v>
+        <v>126890175</v>
       </c>
       <c r="B20" t="n">
-        <v>79020</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2605,14 +2608,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>685107</v>
+        <v>685138</v>
       </c>
       <c r="R20" t="n">
-        <v>7106875</v>
+        <v>7106890</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2656,30 +2659,15 @@
       <c r="AG20" t="b">
         <v>0</v>
       </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2690,32 +2678,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126890144</v>
+        <v>126890195</v>
       </c>
       <c r="B21" t="n">
-        <v>80123</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2725,10 +2713,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>685136</v>
+        <v>685114</v>
       </c>
       <c r="R21" t="n">
-        <v>7106853</v>
+        <v>7106926</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2791,45 +2779,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126890177</v>
+        <v>126890321</v>
       </c>
       <c r="B22" t="n">
-        <v>98367</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>685125</v>
+        <v>685165</v>
       </c>
       <c r="R22" t="n">
-        <v>7106947</v>
+        <v>7106856</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2876,12 +2864,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2892,14 +2880,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126889628</v>
+        <v>126890322</v>
       </c>
       <c r="B23" t="n">
-        <v>79020</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2923,14 +2911,14 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>685180</v>
+        <v>685156</v>
       </c>
       <c r="R23" t="n">
-        <v>7106844</v>
+        <v>7106959</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2977,12 +2965,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -2993,45 +2981,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126891171</v>
+        <v>126890626</v>
       </c>
       <c r="B24" t="n">
-        <v>57823</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>685135</v>
+        <v>685132</v>
       </c>
       <c r="R24" t="n">
-        <v>7106966</v>
+        <v>7106962</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3078,12 +3066,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3094,32 +3082,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126891639</v>
+        <v>126891646</v>
       </c>
       <c r="B25" t="n">
-        <v>80123</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3129,10 +3117,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>685148</v>
+        <v>685108</v>
       </c>
       <c r="R25" t="n">
-        <v>7106890</v>
+        <v>7106883</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3195,10 +3183,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126890601</v>
+        <v>126891641</v>
       </c>
       <c r="B26" t="n">
-        <v>57663</v>
+        <v>79084</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3206,34 +3194,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>685168</v>
+        <v>685169</v>
       </c>
       <c r="R26" t="n">
-        <v>7106800</v>
+        <v>7106940</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3280,12 +3268,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3296,45 +3284,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126893495</v>
+        <v>126890585</v>
       </c>
       <c r="B27" t="n">
-        <v>98367</v>
+        <v>79946</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219790</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>685133</v>
+        <v>685124</v>
       </c>
       <c r="R27" t="n">
-        <v>7106886</v>
+        <v>7106964</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3375,19 +3363,18 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3398,32 +3385,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126890152</v>
+        <v>126893454</v>
       </c>
       <c r="B28" t="n">
-        <v>79020</v>
+        <v>80336</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3433,10 +3420,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>685118</v>
+        <v>685149</v>
       </c>
       <c r="R28" t="n">
-        <v>7106922</v>
+        <v>7106891</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3471,6 +3458,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3488,7 +3480,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3499,10 +3491,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126890151</v>
+        <v>126889623</v>
       </c>
       <c r="B29" t="n">
-        <v>79020</v>
+        <v>80432</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3510,34 +3502,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>685110</v>
+        <v>685088</v>
       </c>
       <c r="R29" t="n">
-        <v>7106911</v>
+        <v>7106936</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3584,12 +3576,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3600,10 +3592,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126890121</v>
+        <v>126889624</v>
       </c>
       <c r="B30" t="n">
-        <v>79020</v>
+        <v>80432</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3611,34 +3603,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>685160</v>
+        <v>685145</v>
       </c>
       <c r="R30" t="n">
-        <v>7106836</v>
+        <v>7106886</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3682,30 +3674,15 @@
       <c r="AG30" t="b">
         <v>0</v>
       </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3716,10 +3693,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126889624</v>
+        <v>126889625</v>
       </c>
       <c r="B31" t="n">
-        <v>80123</v>
+        <v>80432</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3751,10 +3728,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>685145</v>
+        <v>685134</v>
       </c>
       <c r="R31" t="n">
-        <v>7106886</v>
+        <v>7106898</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3817,49 +3794,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126893453</v>
+        <v>126890108</v>
       </c>
       <c r="B32" t="n">
-        <v>98450</v>
+        <v>80432</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>685142</v>
+        <v>685100</v>
       </c>
       <c r="R32" t="n">
-        <v>7106872</v>
+        <v>7106931</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3894,30 +3867,39 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Carl Jansson, Lotta Ihse, Torbjörn Söderquist, kristina stenmarck, Jennica Andersson, Anne Siivola, Lars-Erik Nilsson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Beke Regelin, Eleonor Johansson</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3928,32 +3910,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126890119</v>
+        <v>126890112</v>
       </c>
       <c r="B33" t="n">
-        <v>98450</v>
+        <v>80432</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3963,10 +3945,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>685161</v>
+        <v>685116</v>
       </c>
       <c r="R33" t="n">
-        <v>7106834</v>
+        <v>7106932</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4009,6 +3991,21 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4029,32 +4026,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126890198</v>
+        <v>126890144</v>
       </c>
       <c r="B34" t="n">
-        <v>91593</v>
+        <v>80432</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>65</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4064,10 +4061,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>685118</v>
+        <v>685136</v>
       </c>
       <c r="R34" t="n">
-        <v>7106927</v>
+        <v>7106853</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4100,11 +4097,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Tallåga</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4135,10 +4127,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126890183</v>
+        <v>126890167</v>
       </c>
       <c r="B35" t="n">
-        <v>57660</v>
+        <v>80432</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4146,46 +4138,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>685138</v>
+        <v>685168</v>
       </c>
       <c r="R35" t="n">
-        <v>7106859</v>
+        <v>7106810</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4218,11 +4198,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Hackhål</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4253,10 +4228,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126889623</v>
+        <v>126890168</v>
       </c>
       <c r="B36" t="n">
-        <v>80123</v>
+        <v>80432</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4284,14 +4259,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>685088</v>
+        <v>685184</v>
       </c>
       <c r="R36" t="n">
-        <v>7106936</v>
+        <v>7106798</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4338,12 +4313,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4354,10 +4329,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126891641</v>
+        <v>126890186</v>
       </c>
       <c r="B37" t="n">
-        <v>78778</v>
+        <v>80432</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4365,34 +4340,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>685169</v>
+        <v>685113</v>
       </c>
       <c r="R37" t="n">
-        <v>7106940</v>
+        <v>7106891</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4427,6 +4402,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4439,12 +4419,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4455,10 +4435,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126890167</v>
+        <v>126890187</v>
       </c>
       <c r="B38" t="n">
-        <v>80123</v>
+        <v>80432</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4490,10 +4470,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>685168</v>
+        <v>685113</v>
       </c>
       <c r="R38" t="n">
-        <v>7106810</v>
+        <v>7106903</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4556,10 +4536,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126890626</v>
+        <v>126890319</v>
       </c>
       <c r="B39" t="n">
-        <v>79020</v>
+        <v>80432</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4567,34 +4547,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>685132</v>
+        <v>685113</v>
       </c>
       <c r="R39" t="n">
-        <v>7106962</v>
+        <v>7106871</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4629,6 +4609,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -4641,12 +4626,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4657,10 +4642,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126890195</v>
+        <v>126891639</v>
       </c>
       <c r="B40" t="n">
-        <v>79020</v>
+        <v>80432</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4668,34 +4653,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>685114</v>
+        <v>685148</v>
       </c>
       <c r="R40" t="n">
-        <v>7106926</v>
+        <v>7106890</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4742,12 +4727,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4758,10 +4743,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126890321</v>
+        <v>126893449</v>
       </c>
       <c r="B41" t="n">
-        <v>79020</v>
+        <v>80432</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4769,34 +4754,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>685165</v>
+        <v>685120</v>
       </c>
       <c r="R41" t="n">
-        <v>7106856</v>
+        <v>7106831</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4831,6 +4816,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -4843,12 +4833,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -4859,32 +4849,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126890199</v>
+        <v>126893455</v>
       </c>
       <c r="B42" t="n">
-        <v>92622</v>
+        <v>80432</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4894,10 +4884,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>685175</v>
+        <v>685123</v>
       </c>
       <c r="R42" t="n">
-        <v>7106946</v>
+        <v>7106871</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4932,6 +4922,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -4949,7 +4944,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -4960,10 +4955,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126890187</v>
+        <v>126893457</v>
       </c>
       <c r="B43" t="n">
-        <v>80123</v>
+        <v>80432</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4995,10 +4990,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>685113</v>
+        <v>685071</v>
       </c>
       <c r="R43" t="n">
-        <v>7106903</v>
+        <v>7106901</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5033,6 +5028,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5050,7 +5050,7 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5061,10 +5061,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126890107</v>
+        <v>126893492</v>
       </c>
       <c r="B44" t="n">
-        <v>79020</v>
+        <v>80432</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5072,34 +5072,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>685123</v>
+        <v>685137</v>
       </c>
       <c r="R44" t="n">
-        <v>7106920</v>
+        <v>7106892</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5146,12 +5146,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5162,45 +5162,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126890585</v>
+        <v>126890318</v>
       </c>
       <c r="B45" t="n">
-        <v>79638</v>
+        <v>80461</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>6462</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>685124</v>
+        <v>685114</v>
       </c>
       <c r="R45" t="n">
-        <v>7106964</v>
+        <v>7106864</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5247,12 +5247,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5263,49 +5263,57 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126893456</v>
+        <v>126890183</v>
       </c>
       <c r="B46" t="n">
-        <v>98450</v>
+        <v>57950</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>685136</v>
+        <v>685138</v>
       </c>
       <c r="R46" t="n">
-        <v>7106940</v>
+        <v>7106859</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5342,7 +5350,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Hackhål</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5351,7 +5359,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5363,7 +5370,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Carl Jansson, Lotta Ihse, Torbjörn Söderquist, kristina stenmarck, Jennica Andersson, Anne Siivola, Lars-Erik Nilsson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Beke Regelin, Eleonor Johansson</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5374,45 +5381,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126890193</v>
+        <v>126890601</v>
       </c>
       <c r="B47" t="n">
-        <v>98450</v>
+        <v>57953</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>685111</v>
+        <v>685168</v>
       </c>
       <c r="R47" t="n">
-        <v>7106903</v>
+        <v>7106800</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5447,11 +5454,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ca 150-200 plantor</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5464,12 +5466,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5480,45 +5482,53 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126890122</v>
+        <v>126890596</v>
       </c>
       <c r="B48" t="n">
-        <v>98450</v>
+        <v>58114</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>685170</v>
+        <v>685137</v>
       </c>
       <c r="R48" t="n">
-        <v>7106842</v>
+        <v>7106950</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5565,12 +5575,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5581,10 +5591,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126890123</v>
+        <v>126891171</v>
       </c>
       <c r="B49" t="n">
-        <v>79020</v>
+        <v>58114</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5592,34 +5602,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>685169</v>
+        <v>685135</v>
       </c>
       <c r="R49" t="n">
-        <v>7106843</v>
+        <v>7106966</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5663,30 +5673,15 @@
       <c r="AG49" t="b">
         <v>0</v>
       </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5697,45 +5692,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126890150</v>
+        <v>126889636</v>
       </c>
       <c r="B50" t="n">
-        <v>79020</v>
+        <v>99035</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>685135</v>
+        <v>685270</v>
       </c>
       <c r="R50" t="n">
-        <v>7106863</v>
+        <v>7106941</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5782,12 +5777,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5798,10 +5793,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126890110</v>
+        <v>126889637</v>
       </c>
       <c r="B51" t="n">
-        <v>98367</v>
+        <v>99035</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5829,14 +5824,14 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>685096</v>
+        <v>685141</v>
       </c>
       <c r="R51" t="n">
-        <v>7106922</v>
+        <v>7106899</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5883,12 +5878,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5899,45 +5894,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126891646</v>
+        <v>126890110</v>
       </c>
       <c r="B52" t="n">
-        <v>79020</v>
+        <v>99035</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>685108</v>
+        <v>685096</v>
       </c>
       <c r="R52" t="n">
-        <v>7106883</v>
+        <v>7106922</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5984,12 +5979,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -6000,32 +5995,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126893455</v>
+        <v>126890177</v>
       </c>
       <c r="B53" t="n">
-        <v>80123</v>
+        <v>99035</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6035,10 +6030,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>685123</v>
+        <v>685125</v>
       </c>
       <c r="R53" t="n">
-        <v>7106871</v>
+        <v>7106947</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6073,11 +6068,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6095,7 +6085,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Carl Jansson, Lotta Ihse, Torbjörn Söderquist, kristina stenmarck, Jennica Andersson, Anne Siivola, Lars-Erik Nilsson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Beke Regelin, Eleonor Johansson</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6106,45 +6096,53 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126890115</v>
+        <v>126891183</v>
       </c>
       <c r="B54" t="n">
-        <v>98450</v>
+        <v>99035</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>685145</v>
+        <v>685180</v>
       </c>
       <c r="R54" t="n">
-        <v>7106855</v>
+        <v>7106957</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6185,18 +6183,19 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6207,45 +6206,49 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126890116</v>
+        <v>126891184</v>
       </c>
       <c r="B55" t="n">
-        <v>98450</v>
+        <v>99035</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>685140</v>
+        <v>685167</v>
       </c>
       <c r="R55" t="n">
-        <v>7106846</v>
+        <v>7106901</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6286,18 +6289,19 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6308,49 +6312,53 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126893452</v>
+        <v>126891650</v>
       </c>
       <c r="B56" t="n">
-        <v>98450</v>
+        <v>99035</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>685145</v>
+        <v>685142</v>
       </c>
       <c r="R56" t="n">
-        <v>7106823</v>
+        <v>7106896</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6387,7 +6395,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>20 st</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6403,12 +6411,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Carl Jansson, Lotta Ihse, Torbjörn Söderquist, kristina stenmarck, Jennica Andersson, Anne Siivola, Lars-Erik Nilsson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Beke Regelin, Eleonor Johansson</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6419,32 +6427,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126890322</v>
+        <v>126893495</v>
       </c>
       <c r="B57" t="n">
-        <v>79020</v>
+        <v>99035</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6454,10 +6462,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>685156</v>
+        <v>685133</v>
       </c>
       <c r="R57" t="n">
-        <v>7106959</v>
+        <v>7106886</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6498,18 +6506,19 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6520,45 +6529,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126890319</v>
+        <v>126890115</v>
       </c>
       <c r="B58" t="n">
-        <v>80123</v>
+        <v>99118</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>685113</v>
+        <v>685145</v>
       </c>
       <c r="R58" t="n">
-        <v>7106871</v>
+        <v>7106855</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6593,11 +6602,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>På sälg</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -6610,12 +6614,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6626,45 +6630,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126890175</v>
+        <v>126890116</v>
       </c>
       <c r="B59" t="n">
-        <v>79020</v>
+        <v>99118</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>685138</v>
+        <v>685140</v>
       </c>
       <c r="R59" t="n">
-        <v>7106890</v>
+        <v>7106846</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6711,12 +6715,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6727,32 +6731,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126890106</v>
+        <v>126890119</v>
       </c>
       <c r="B60" t="n">
-        <v>79020</v>
+        <v>99118</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6762,10 +6766,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>685144</v>
+        <v>685161</v>
       </c>
       <c r="R60" t="n">
-        <v>7106929</v>
+        <v>7106834</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6828,32 +6832,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126890105</v>
+        <v>126890122</v>
       </c>
       <c r="B61" t="n">
-        <v>79020</v>
+        <v>99118</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6863,10 +6867,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>685155</v>
+        <v>685170</v>
       </c>
       <c r="R61" t="n">
-        <v>7106940</v>
+        <v>7106842</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6929,32 +6933,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126890118</v>
+        <v>126890124</v>
       </c>
       <c r="B62" t="n">
-        <v>81073</v>
+        <v>99118</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>229558</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Barkporlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pertusaria sommerfeltii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Flörke ex Sommerf.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6964,10 +6968,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>685153</v>
+        <v>685176</v>
       </c>
       <c r="R62" t="n">
-        <v>7106835</v>
+        <v>7106857</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7010,21 +7014,6 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -7045,45 +7034,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126890114</v>
+        <v>126890193</v>
       </c>
       <c r="B63" t="n">
-        <v>79020</v>
+        <v>99118</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>685143</v>
+        <v>685111</v>
       </c>
       <c r="R63" t="n">
-        <v>7106862</v>
+        <v>7106903</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7118,6 +7107,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ca 150-200 plantor</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -7126,31 +7120,16 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7161,45 +7140,49 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126893492</v>
+        <v>126893450</v>
       </c>
       <c r="B64" t="n">
-        <v>80123</v>
+        <v>99118</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>685137</v>
+        <v>685177</v>
       </c>
       <c r="R64" t="n">
-        <v>7106892</v>
+        <v>7106857</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7234,27 +7217,684 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>126893452</v>
+      </c>
+      <c r="B65" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Lill-lögdåberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>685145</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7106823</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Alexandra Astafourova</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>126893453</v>
+      </c>
+      <c r="B66" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Lill-lögdåberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>685142</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7106872</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Alexandra Astafourova</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>126893456</v>
+      </c>
+      <c r="B67" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Lill-lögdåberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>685136</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7106940</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Alexandra Astafourova</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>126890609</v>
+      </c>
+      <c r="B68" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Lill Lögdåberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>685141</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7106811</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>126890610</v>
+      </c>
+      <c r="B69" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Lill Lögdåberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>685137</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7106950</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>126890118</v>
+      </c>
+      <c r="B70" t="n">
+        <v>81390</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>229558</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Barkporlav</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Pertusaria sommerfeltii</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Flörke ex Sommerf.) Fr.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Norrholmsjö, Ång</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>685153</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7106835</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr">
         <is>
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>

--- a/artfynd/A 57334-2022 artfynd.xlsx
+++ b/artfynd/A 57334-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY70"/>
+  <dimension ref="A1:AZ70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126890160</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126890198</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
       <c r="AY4" t="inlineStr">
         <is>
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126890120</t>
         </is>
       </c>
     </row>
@@ -1100,6 +1120,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126891396</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1201,6 +1226,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126890199</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1302,6 +1332,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126889628</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1403,6 +1438,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126889629</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1504,6 +1544,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126890105</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1605,6 +1650,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126890106</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1706,6 +1756,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126890107</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1822,6 +1877,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126890113</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1938,6 +1998,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126890114</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2054,6 +2119,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126890121</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2170,6 +2240,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126890123</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2271,6 +2346,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126890150</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2372,6 +2452,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126890151</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2473,6 +2558,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126890152</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2574,6 +2664,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126890153</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2675,6 +2770,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126890175</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2776,6 +2876,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126890195</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2877,6 +2982,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126890321</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2978,6 +3088,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126890322</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3079,6 +3194,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126890626</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3180,6 +3300,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126891646</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3281,6 +3406,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126891641</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3382,6 +3512,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126890585</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3488,6 +3623,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126893454</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3589,6 +3729,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126889623</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3690,6 +3835,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126889624</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3791,6 +3941,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126889625</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3907,6 +4062,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126890108</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4023,6 +4183,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126890112</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4124,6 +4289,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126890144</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4225,6 +4395,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126890167</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4326,6 +4501,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126890168</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4432,6 +4612,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126890186</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4533,6 +4718,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126890187</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4639,6 +4829,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126890319</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4740,6 +4935,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126891639</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4846,6 +5046,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126893449</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4952,6 +5157,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126893455</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5058,6 +5268,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126893457</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5159,6 +5374,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126893492</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5260,6 +5480,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126890318</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5378,6 +5603,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126890183</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5479,6 +5709,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126890601</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5588,6 +5823,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126890596</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5689,6 +5929,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126891171</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5790,6 +6035,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126889636</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5891,6 +6141,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126889637</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5992,6 +6247,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126890110</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6091,6 +6351,11 @@
       <c r="AY53" t="inlineStr">
         <is>
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126890177</t>
         </is>
       </c>
     </row>
@@ -6201,6 +6466,11 @@
       <c r="AY54" t="inlineStr">
         <is>
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126891183</t>
         </is>
       </c>
     </row>
@@ -6309,6 +6579,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126891184</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6424,6 +6699,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126891650</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6526,6 +6806,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126893495</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6627,6 +6912,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126890115</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6728,6 +7018,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126890116</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6829,6 +7124,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126890119</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6930,6 +7230,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126890122</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7031,6 +7336,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126890124</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7137,6 +7447,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126890193</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7248,6 +7563,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126893450</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7359,6 +7679,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126893452</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7470,6 +7795,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126893453</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7581,6 +7911,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126893456</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7682,6 +8017,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126890609</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7783,6 +8123,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126890610</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7899,8 +8244,84 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126890118</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>